--- a/Dataset/Test_Set.xlsx
+++ b/Dataset/Test_Set.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,992 +436,4370 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Example</t>
+          <t>Word Sense</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Non-literal Word Sense</t>
+          <t>Verb</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Literal Word Sense</t>
+          <t>Non-Literal Usage</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Verb</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Is FOS</t>
+          <t>Literal Usage</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hatod og patay</t>
+          <t>lunod patay</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Si Juan hatod og patay sa iyang paryente nga namatay.; Ang mga tawo nga hatod og patay kasagaran nagpakita ug respeto sa namatay.; Si Pedro hatod og patay sa iyang kauban sa trabaho.; Ang mga kauban sa barangay naghatod og patay sa ilang lider.; Si Maria hatod og patay sa iyang silingan nga namatay.</t>
+          <t>dihard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to attend a funeral or memorial service</t>
+          <t>['lunod', 'patay']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to attend a funeral or memorial service</t>
+          <t>Si Maria lunod patay sa pagpanalipod sa iyang mga kauban.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['hatod', 'patay']</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
+          <t>Ang balita miingon nga dunay usa ka tawo nga lunod patay nga nakit-an sa lanaw kagahapon.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>makabugto og panty</t>
+          <t>gibati og kaanyag</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Si Ana makabugto og panty sa iyang pagka-sexy.; Ang artista nga iyang nakita sa sine makabugto og panty gyud.; Si Pedro ganahan kaayo sa iyang uyab kay makabugto og panty.; Ang mga modelo sa fashion show kasagaran makabugto og panty sa ilang porma.; Si Maria makaingon nga makabugto og panty ang iyang crush.</t>
+          <t>prima donna</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>physically or sexually attractive, a hottie; a physically or sexually attractive person</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>physically or sexually attractive, a hottie; a physically or sexually attractive person</t>
+          <t>Si Ana gibati og kaanyag, maong pirmi siya nagbuot-buot.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['makabugto']</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
+          <t>"Gibati gyud ni Carla og kaanyag sa iyang bag-ong sinina, maong nagpakita siya sa iyang mga higala."</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>basa og baba</t>
+          <t>buhi pay ginamos</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Si Maria basa og baba kay pirmi lang mag-yawyaw bisan wala’y pulos.; Ang mga bata nga basa og baba kasagaran maglikay sa mga tahimik nga lugar.; Si Juan basa og baba ug permi magdala ug kasaba sa opisina.; Ang iyang mga amiga permi magbinuang sa iyang basa og baba nga kinaiya.; Ang mga tawo nga basa og baba kasagaran dili ganahan makakita sa mga tahimik nga tao.</t>
+          <t>patay nga sama sa usa ka dughan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> noisy; talkative</t>
+          <t>['ginamos']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> noisy; talkative</t>
+          <t>Ang mga tawo nga buhi pay ginamos kasagaran naglisod sa kinabuhi.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['baba']</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
+          <t>Nagbitay ang mga isda sa init nga adlaw, apan buhi pay ginamos ang ilang hitsura.</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>murag namiya og tai</t>
+          <t>lisod pukawon ang gamata</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>"Siya kalit lang murag namiya og tai, wala na gani nagpahibalo."; "Ang bata murag namiya og tai, kalit lang nawala."; "Si Pedro murag namiya og tai, wala na gani nagpahibalo sa iyang mga kauban."; "Ang silingan murag namiya og tai, kalit lang wala."; "Si Ana murag namiya og tai, wala na gani nagpahibalo sa iyang mga plano."</t>
+          <t>gigamit sa pagsulti sa nagmata o sa usa ka tawo nga dili magmata</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(simile, idiomatic) someone who leaves unexpectedly without sa word</t>
+          <t>['pukawon', 'gamata']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(simile, idiomatic) someone who leaves unexpectedly without sa word</t>
+          <t>Ang mga estudyante nga late na matulog, lisod pukawon ang gamata.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
+          <t>Pagmata na, Toto, lisod pukawon ang gamata kung naa pay iring nga nagkatulog sa imong tiyan.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ander da bunal</t>
+          <t>minyo og lawas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Si Juan kay ander da bunal, bisan unsa isugo sa iyang asawa kay tumanon.; Ang mga ander da bunal kasagaran magpailalom sa mga buot-buoton nga asawa.; Si Pedro nga ander da bunal kay wala'y laing mabuhat kundi musunod sa misis.; Ang ander da bunal nga bana kay kasagaran magpaubos ug musunod sa asawa.; Ang relasyon nila kay ander da bunal, maong klaro kaayo kinsa ang nagbuot.</t>
+          <t>nga adunay lawas sa amahan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>henpecked, Pussywhipped, a henpecked husband or boyfriend</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>henpecked, Pussywhipped, a henpecked husband or boyfriend</t>
+          <t>Ang iyang amiga giingnan nga minyo og lawas tungod sa kadako sa iyang tiyan.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['bunal']</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
+          <t>Sa simbahan, ang magtiayon gikasal ug nagminyo og lawas aron maglumon sa ilang pagmamahalan.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dili na nimo mabalik ang baha sa bukid</t>
+          <t>walay man kardaba mamunga og tundan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Si Pedro giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga naghinuktok na lang siya.; Ang mga estudyante nakabalo nga dili na nimo mabalik ang baha sa bukid, mao nga nagplano na sila pag-ayo.; Si Ana nakasabot nga dili na nimo mabalik ang baha sa bukid, mao nga nag-move on na siya.; Ang iyang pamilya giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga nagplano na sila og tarong.; Si Maria giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga nagpadayon na sa iyang mga plano.</t>
+          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>what's done is done</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>what's done is done</t>
+          <t>Ang mga tawo giingnan nga walay man kardaba mamunga og tundan, mao nga magmatngon sila sa ilang mga buhaton.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
+          <t>Sa among umahan, makita gyud nimo nga walay man kardaba mamunga og tundan bisan unsaon pa nimo pagsulay.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gibati og kaanyag</t>
+          <t>manglutasay</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Si Ana gibati og kaanyag, maong pirmi siya nagbuot-buot.; Ang mga tawo nga gibati og kaanyag kasagaran magdala ug samok sa grupo.; Si Maria gibati og kaanyag, bisan unsa nga sugo, dili gyud mutuman.; Ang iyang amiga gibati og kaanyag, maong pirmi mag-away sa iyang bana.; Si Pedro gibati og kaanyag, maong pirmi magbuot sa ilang opisina.</t>
+          <t>usa ka manunulak sa mga bukog</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> prima donna; entitled person,  entitled</t>
+          <t>['manglutasay']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> prima donna; entitled person,  entitled</t>
+          <t>Si Maria nalipay kay ang iyang kauban dili manglutasay.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
+          <t>Nagtapok ang mga bata sa silong sa balay aron magduwa og mga luto-lutoan, ug makita nimo nga manglutasay sila ug mga puto't kutsara.</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dula og panit</t>
+          <t>nakalugsong</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi lang mag-dula og panit, bisan walay buhaton nga maayo.; Ang mga bata nga dula og panit kasagaran wala’y klaro nga padulngan.; Si Juan dula og panit, pirmi lang magtambay ug magbuot-buot.; Ang iyang barkada kay dula og panit, bisan unsa na lang nga kalipay ang gihimo.; Si Maria nagbuot-buot kay gusto siya magdula og panit pirmi.</t>
+          <t>sa pag-adto gikan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to masturbate, jack off, to fap</t>
+          <t>['nakalugsong']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to masturbate, jack off, to fap</t>
+          <t>Ang mga trabahante nakalugsong gikan sa taas ug giuli ang mga gamit.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>['dula']</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
+          <t>Ang bata nakalugsong sa bukid human magdula didto.</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bag-ong haon</t>
+          <t>batang murag korek</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ang iyang bag-ong haon nga cellphone kay nindot kaayo ug daghan ug features.; Ang bag-ong haon nga kotse ni Pedro kay makahatag ug dako nga garbo.; Si Ana permi mangita ug bag-ong haon nga mga gamit para sa balay.; Ang mga bata nagpaabot sa bag-ong haon nga mga dulaan nga gi-order online.; Ang bag-ong haon nga balay ni Maria kay puno sa modernong mga kagamitan.</t>
+          <t>dili-matag-as</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> recently produced, brand new, hot off the press,  a new model of something</t>
+          <t>['batang']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> recently produced, brand new, hot off the press,  a new model of something</t>
+          <t>Si Pedro batang murag korek kay bisan gamay pa, maayo na kaayo sa klase.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>['bag-ong', 'haon']</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
+          <t>Ang batang murag korek ang gisul-ob ni Juan sa iyang Halloween party.</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>makawat</t>
+          <t>hatod og patay</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ang bata ni Maria makawat kaayo, bisan kinsa lang pwede makagunit niya.; Si Pedro makawat kaayo, dali ra siya madala bisan kinsa.; Ang anak ni Juan makawat, bisan kinsa ra magpadede niya.; Si Ana makawat nga bata, dili siya mohilak bisan kinsa ang magbitbit.; Ang ilang baby makawat kaayo, bisan kinsa nga tawo dili niya kahadlukan.</t>
+          <t>sa pagtambong sa usa ka paglubong o seremonya sa paghinumdom</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>can be stolen, (idiomatic, of a baby) lets new people hold him or her; doesn't cry when held by others or taken away from parents, especially the mother</t>
+          <t>['hatod', 'patay']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>can be stolen, (idiomatic, of a baby) lets new people hold him or her; doesn't cry when held by others or taken away from parents, especially the mother</t>
+          <t>Si Pedro hatod og patay sa iyang kauban sa trabaho.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>['makawat']</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
+          <t>Nag-hatod og patay ang mga mag-uuma ngadto sa paglubong sa talis.</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ayaw pagbuot kay lain-lain ta og lubot</t>
+          <t>magtumba og baka</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ayaw pagbuot kay lain-lain ta og lubot, respetaray lang ta sa atong mga opinion.; Bisan unsa ka kapugos, ayaw pagbuot kay lain-lain ta og lubot.; Dili ta angay maghusga, kay lain-lain ta og lubot.; Ang matag usa lain-lain og gusto, mao nga ayaw pagbuot kay lain-lain ta og lubot.; Dili tanan magkauyon, kay lain-lain ta og lubot.</t>
+          <t>sa pag-ihaw sa usa ka vaca</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>don't tell me what to do</t>
+          <t>['magtumba']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>don't tell me what to do</t>
+          <t>Ang ilang pamilya magtumba og baka kung naa’y dako nga celebration.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>['ayaw', 'lubot']</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
+          <t>Ang manggugubat magtumba og baka para sa karne nga ilang ipamaligya sa merkado.</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>maabot sa luwa</t>
+          <t>nakalugsong</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ang lugar nga ilang giadtoan kay maabot ra sa luwa, dili layo.; Ang iyang balay maabot ra sa luwa gikan sa simbahan.; Si Pedro pirmi lang maglakaw kay ang eskwelahan maabot ra sa luwa.; Ang mga tindahan nga ilang gusto adtoan kay maabot ra sa luwa gikan sa ilang lugar.; Si Maria nag-invite ug friends kay ilang balay maabot ra sa luwa.</t>
+          <t>sa pag-adto gikan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> near not far</t>
+          <t>['nakalugsong']</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> near not far</t>
+          <t>Nakalugsong na mi ug gidalit ang among mga ani sa lungsod.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>['maabot', 'luwa']</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
+          <t>Naglakaw mi sa bukid ug nakalugsong mi ngadto sa suba para maligo.</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
+          <t>kuyog baboy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Si Ana nakasala sa iyang trabaho, bisan ang kabaw nga naay upat ka tiil masipyat.; Ang iyang amigo nakalimot sa meeting, bisan ang kabaw nga naay upat ka tiil masipyat.; Si Pedro nasipyat sa exam, bisan ang kabaw nga naay upat ka tiil masipyat.; Ang mga tawo kasagaran maghimo og sayop, bisan ang kabaw nga naay upat ka tiil masipyat.; Si Maria nasipyat sa pagplano, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+          <t>usa ka tagalong</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>we all make mistakes; nobody's perfect</t>
+          <t>['kuyog']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>we all make mistakes; nobody's perfect</t>
+          <t>Ang mga tawo nga kuyog baboy kasagaran magpalisod sa ilang mga kauban.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>['naay', 'masipyat']</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
+          <t>Miadto sila sa umahan uban sa ilang kuyog baboy nga gihiktan sa usa ka pisi.</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>bato og kasingkasing</t>
+          <t>dili na nimo mabalik ang baha sa bukid</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ang iyang amo kay bato og kasingkasing, wala gyud malumo bisan naghangyo na.; Si Juan bato og kasingkasing, wala gyud motabang bisan klaro nga nagkinahanglan ug tabang.; Ang mga tao nga bato og kasingkasing kasagaran maglisod sa relasyon sa uban.; Si Pedro bato og kasingkasing, dili gyud siya malumo bisan sa mga bata.; Ang iyang inahan bato og kasingkasing, dili malumo bisan klaro nga luoy na kaayo.</t>
+          <t>Ang nahimo nahimo na</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pitiless; heartless</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pitiless; heartless</t>
+          <t>Si Pedro giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga naghinuktok na lang siya.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>['bato']</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
+          <t>Sa pag-ulan ug kusug, nakita namo nga dili na nimo mabalik ang baha sa bukid human kini mokalas padulong sa ubos.</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dugay pay manguros</t>
+          <t>gidaman</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ang iyang trabaho dugay pay manguros, pirmi lang maghinay-hinay.; Si Juan dugay pay manguros kung magtrabaho sa opisina.; Ang mga tawo nga dugay pay manguros kasagaran maglisod sa ilang mga deadline.; Si Pedro dugay pay manguros, bisan unsa nga butang, hinay kaayo mahuman.; Ang iyang proyekto dugay pay manguros, walay klaro nga mahuman.</t>
+          <t>sa pag-aturog o pag-aturog</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a piece of cake, cakewalk</t>
+          <t>['gidaman']</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> a piece of cake, cakewalk</t>
+          <t>"Gidaman na si Juan, sige lang siya og panaway."</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>['manguros']</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
+          <t>"Gidaman si Maria kagabii, milakaw siya paingon sa gawas nga walay kabalo."</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>agi sa bangag sa dagom</t>
+          <t>abot sa dalunggan ang ngisi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Si Pedro agi sa bangag sa dagom aron lang makapasar sa eksam.; Ang ilang proyekto agi sa bangag sa dagom sa kalisod.; Ang iyang negosyo agi sa bangag sa dagom bago niyag napalambo.; Si Ana agi sa bangag sa dagom sa iyang pag-eskwela ug pagtrabaho.; Ang ilang relasyon agi sa bangag sa dagom sa daghang pagsulay.</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> experience hardships in achieving one's goal or dream</t>
+          <t>['abot', 'dalunggan', 'ngisi']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> experience hardships in achieving one's goal or dream</t>
+          <t>Pagkahuman sa eksam, abot sa dalunggan ang ngisi ni Juan kay nakapasar siya.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>['agi', 'bangag']</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
+          <t>Nagtan-aw ko sa litrato nga gipakita ni Ana, abot sa dalunggan ang ngisi niya sa kalipay.</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hangyo kabayo</t>
+          <t>hilawas</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Si Juan hangyo kabayo, maong nakuha niya ang diskwento.; Ang iyang amiga hangyo kabayo, bisan unsa nga butang iyang makuha.; Si Pedro hangyo kabayo, maong naangkon niya ang iyang gusto.; Ang mga tawo nga hangyo kabayo kasagaran magmalampuson sa ilang mga plano.; Si Maria hangyo kabayo, maong walay makatanggi sa iyang mga pangutana.</t>
+          <t>coitus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>a shrewd way of acquiring something</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>a shrewd way of acquiring something</t>
+          <t>Ang hilawas nga relasyon sa diha nga walay commitment kay lisod.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>['hangyo']</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
+          <t>Nagkinahanglan ko ug hilawas nga pagkaon aron magpabiling lig-on ug himsog ang lawas.</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>mamalit og kaso</t>
+          <t>buotan ra og matulog</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Si Ana mamalit og kaso aron lang magka-datu.; Ang abogado mamalit og kaso bisan asa nga hospital.; Si Pedro mamalit og kaso aron makakwarta sa mga biktima sa aksidente.; Ang mga tawo nga mamalit og kaso kasagaran mga abogado nga gustong magpasikat.; Si Juan mamalit og kaso aron lang magka-daghan ang iyang kliyente.</t>
+          <t>malinong</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>to be an ambulance chaser, to engage in ambulance chasing</t>
+          <t>['matulog']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>to be an ambulance chaser, to engage in ambulance chasing</t>
+          <t>Ang iyang anak buotan ra og matulog, kay pirmi lang mangaway sa mga silingan.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
+          <t>Gabiina na kaayo ug buotan ra og matulog ang bata sa ilang kwarto.</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>maghilak ang adlaw</t>
+          <t>minyo og lawas</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Si Ana nagtan-aw sa bintana samtang naghilak ang adlaw.; Ang iyang pamilya nag-istorya samtang naghilak ang adlaw.; Si Pedro nagbasa ug libro samtang naghilak ang adlaw.; Ang mga tawo nag-relax sa balay samtang naghilak ang adlaw.; Si Juan naghunahuna sa iyang mga pangandoy samtang naghilak ang adlaw.</t>
+          <t>nga adunay lawas sa amahan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> boring; monotonous; uneventful</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> boring; monotonous; uneventful</t>
+          <t>Si Pedro nangita ug exercise routine kay minyo og lawas na siya.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>['maghilak']</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
+          <t>Si Juan ug Maria nagplano nga mag-minyo og lawas sa sunod buwan ngadto sa simbahan sa ilang baryo.</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dili tanang butang sili nga mohalang dayon</t>
+          <t>ayaw pagbuot, tagsa-tagsa tag lubot</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Si Pedro naghinuktok nga dili tanang butang sili nga mohalang dayon, kinahanglan gyud og pagpaningkamot.; Ang mga estudyante giingnan nga dili tanang butang sili nga mohalang dayon, kinahanglan magtuon pag-ayo.; Si Ana nakasabot nga dili tanang butang sili nga mohalang dayon, mao nga nagplano og maayo.; Ang mga tawo nga dili tanang butang sili nga mohalang dayon kasagaran magmalampuson sa ilang mga plano.; Si Maria giingnan nga dili tanang butang sili nga mohalang dayon, kinahanglan gyud og pagpaningkamot.</t>
+          <t>ayaw ako isulti kon unsay buhaton</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>not everything happens in an instant, it doesn't happen overnight; Rome wasn't built in a day</t>
+          <t>['ayaw', 'lubot']</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>not everything happens in an instant, it doesn't happen overnight; Rome wasn't built in a day</t>
+          <t>Bisan unsa ka kapugos, ayaw pagbuot, tagsa-tagsa tag lubot.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>['butang', 'mohalang']</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>1</v>
+          <t>Ang kalainan sa atong pamaagi kay angay lang respetohon, ayaw pagbuot, tagsa-tagsa tag lubot sa desisyon.</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>giluto sa kaugalingong mantika</t>
+          <t>hunaw</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Si Pedro giluto sa kaugalingong mantika sa iyang mga sala.; Ang iyang kauban giluto sa kaugalingong mantika tungod sa iyang binuhatan.; Si Maria giluto sa kaugalingong mantika sa iyang mga desisyon.; Ang mga tawo nga magbuhat ug dautan kasagaran giluto sa kaugalingong mantika.; Si Juan giluto sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to dig one's own grave</t>
+          <t>['hunaw']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> to dig one's own grave</t>
+          <t>Ang iyang kauban naghunaw sa mga problema aron dili siya maapil.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>['giluto']</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
+          <t>Nagpareha sila paghuman sa trabaho ug naghunaw sa ilang kamot sa kusina aron limpyo.</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>walay man kardaba mamunga og tundan</t>
+          <t>hugot sa bakos</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Si Pedro nasayod nga walay man kardaba mamunga og tundan, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga tawo giingnan nga walay man kardaba mamunga og tundan, mao nga magmatngon sila sa ilang mga buhaton.; Si Ana nakasabot nga walay man kardaba mamunga og tundan, mao nga nagbantay siya sa iyang mga desisyon.; Ang mga estudyante giingnan nga walay man kardaba mamunga og tundan, mao nga magtuon sila pag-ayo.; Si Maria giingnan nga walay man kardaba mamunga og tundan, mao nga nagmatngon siya sa iyang mga lihok.</t>
+          <t>aron sa pag-apig sa usa sa iyang kurug</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>the apple does not fall far from the tree</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>the apple does not fall far from the tree</t>
+          <t>Si Ana hugot sa bakos kay gusto niya makatipid para sa future.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
+          <t>Gipahugot ni Juan ang iyang bakos kay nawad-an siya ug timbang.</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>toyi</t>
+          <t>kapugngan pa ang baha, dili ang biga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ang iyang joke bahin sa toyi kay nakapatawa sa tanan.; Ang mga istorya nila bahin sa toyi kay walay kinutuban nga katawa.; Sa dihang nagbinuang siya, nagtoyi lang iyang mga amigo.; Ang ilang duwa nga toyi kay naghatag ug dako nga kalipay.; Ang iyang mga joke kay kasagaran tungkol sa toyi.</t>
+          <t>dili mapugngan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(humorous, euphemistic) coitus; sexual intercourse, (humorous, euphemistic) to fuck; to have sex, indefinite dative of toy</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(humorous, euphemistic) coitus; sexual intercourse, (humorous, euphemistic) to fuck; to have sex, indefinite dative of toy</t>
+          <t>Si Pedro dili mapugngan sa iyang gusto, kapugngan pa ang baha, dili ang biga.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>['toyi']</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1</v>
+          <t>Ang mga trabahante nagtrabaho dili sa pagpatigbabaw sa ilang gugma kondili sa paglimpyo ug pag-alsa sa mga debris tungod kay kapugngan pa ang baha, dili ang biga.</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>sabong</t>
+          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ang sabong sa arena kay gitan-aw sa daghang mga tawo.; Ang mga manok nga ipangsabong kay gipangandaman ug maayo.; Ang mga sabong sa probinsya kasagaran ginadumog sa mga lokal nga residente.; Ang sabong sa mga manok kay paborito nga pastime sa mga kalalakin-an.; Ang mga sabong nagpakita sa abilidad sa mga magmamantala ug pag-atiman sa ilang mga manok.</t>
+          <t>gigamit nga isulti sa usa ka tawo nga imong gilimbongan sila sa pagtan-aw sa usa ka piho nga direksyon</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>a contest, in a cockpit, between gamecocks fitted with cockspurs; a cockfight; cockfighting, (euphemistic) sexual intercourse, to pair off or pair up to fight, flower, flower, petal, flower, cockfight, attack of a cock against another
-Synonyms: salpok, pagsalpok, soap</t>
+          <t>['kitkit', 'kitkit', 'bungi']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>a contest, in a cockpit, between gamecocks fitted with cockspurs; a cockfight; cockfighting, (euphemistic) sexual intercourse, to pair off or pair up to fight, flower, flower, petal, flower, cockfight, attack of a cock against another
-Synonyms: salpok, pagsalpok, soap</t>
+          <t>Pagtan-aw nako sa iyang nawong, kitkit langaw</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>['sabong']</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
+          <t>Naglingkod ko sa lamisa unya nakit-an nako nga nagpadaplin siya, pagtana-aw, kitkit langaw; paglingi, kitkit bungi, tungod kay gapalupad-lupad ra ang mga langaw ug bungi sa paligid.</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mogawas ang pari nga walay ulo</t>
+          <t>babayeng ikogan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ayaw og kahadlok kay mogawas ang pari nga walay ulo kung magpabilin ka dinha.; Sa dihang mag-istorya sila og mga horror stories, mogawas ang pari nga walay ulo ang giingon.; Mogawas ang pari nga walay ulo kuno kung aduna'y mamatay sa baryo.; Kung magtuyok-tuyok ka sa kadalanan, mogawas ang pari nga walay ulo.; Mogawas ang pari nga walay ulo kung ang balay walay suga.</t>
+          <t>transgender</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>used to scare children from injuries</t>
+          <t>['ikogan']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>used to scare children from injuries</t>
+          <t>Ang babayeng ikogan nga si Juanita kay giilhan sa ilang baryo.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>['mogawas']</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
+          <t>Ang mga bata nalipay ug gikataw-an ang babayeng ikogan nga nahigmata pag-uli nila gikan sa kamingawan.</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>gi-indian</t>
+          <t>makagisi og pitaka</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Si Pedro gi-indian sa iyang uyab sa ilang sabot nga date.; Ang mga estudyante na gi-indian sa ilang maestra sa klase karon.; Si Maria nasuko kay gi-indian siya sa iyang amigo.; Ang iyang kauban sa trabaho gi-indian siya sa ilang meeting.; Si Juan gi-indian sa iyang kliyente sa ilang appointment.</t>
+          <t>mahal kaayo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>to fail to meet an appointment intentionally, to no-show</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>to fail to meet an appointment intentionally, to no-show</t>
+          <t>Si Pedro nagreklamo kay ang tuition fee sa eskwelahan makagisi og pitaka.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>['gi-indian']</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
+          <t>Si Juan napunitan og kutsilyo nga makagisi og pitaka samtang naglakaw sa merkado.</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ul-ol</t>
+          <t>gidaman</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ang iyang buhat kay ul-ol kaayo, wala gyud maghunahuna.; Ayaw pag-ul-ol, kinahanglan naa kay respeto sa uban.; Ang mga ul-ol nga tawo kasagaran dili makuha ang tinuod nga punto.; Ang iyang mga ul-ol nga istorya kay naghatag ug kalibog sa tanan.; Dili maayo nga magsige ka ug ul-ol kay makadaot kini sa imong reputation.</t>
+          <t>sa pag-aturog o pag-aturog</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(humorous, euphemistic) to masturbate
-Synonyms: batil, jakol, lulo, Obsolete form of ulol., pain; ache</t>
+          <t>['gidaman']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(humorous, euphemistic) to masturbate
-Synonyms: batil, jakol, lulo, Obsolete form of ulol., pain; ache</t>
+          <t>"Gidaman na pud si Pedro, daghan kaayo siya og storya."</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>['ul-ol']</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1</v>
+          <t>"Ang gidaman nga balay ni Juan dul-an sa dagat."</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ninja ray mopatay ninjo</t>
+          <t>ang kalimot walay gahom</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ayaw mo pag-away, ninja ray mopatay ninjo nga wala'y saba.; Kung magpadayon mo ug binuang, ninja ray mopatay ninjo.; Sa kalit nga pag-agi, ninja ray mopatay ninjo nga wala moy kalibutan.; Bantay mo kay ninja ray mopatay ninjo kung magpadayon mo ug binuang.; Sa dihang nahimong komprontasyon, ninja ray mopatay ninjo.</t>
+          <t>Ang pagkalimtan dili makahatag kanimo ug wala ka kaayohan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(humorous) a phrase poking fun at the Leyte and Boholano dialects of Cebuano</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(humorous) a phrase poking fun at the Leyte and Boholano dialects of Cebuano</t>
+          <t>Ang mga estudyante nga malimot maglisod sa exam, ang kalimot walay gahom.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>['mopatay']</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
+          <t>Naa koy gipangita sa akong mga gamit, apan murag ang kalimot walay gahom, kay di man gihapon nako makita.</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kalas og bugo</t>
+          <t>alsa og balay</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ayaw pag-kalas og bugo, kay sayang lang ang imong panahon.; Kalas og bugo ning pagsulay nga wala’y klaro.; Ang pagsunod-sunod nimo niya, kalas og bugo ra.; Kalas og bugo ang magdiskusyon ug walay resulta.; Ang pagduwa ug mga walay pulos nga games, kalas og bugo ra.</t>
+          <t>gisulti sa kaugalingon o sa uban kon ang pagkaon naglakip sa mung beans</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>a phrase used to tell someone that he or she is taking too long to comprehend what one is saying, used to express annoyance for failing or taking too long to get the message across</t>
+          <t>['alsa']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>a phrase used to tell someone that he or she is taking too long to comprehend what one is saying, used to express annoyance for failing or taking too long to get the message across</t>
+          <t>Bisan kapoy na, alsa og balay gihapon siya para sa kaugmaon sa iyang anak.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>['kalas']</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
+          <t>Nanginahanglan sila og dugang nga tawo kay kinahanglanon gyud nga alsa og balay karon nga adlawa.</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>binuhi</t>
+          <t>batil</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Si Pedro kay nagbuhi ug mga manok nga pangsabong.; Ang iyang mga binuhi kay mga kabaw nga gamiton sa umahan.; Ang mga binuhi nga iro sa ilang balay kay puro mga pure breed.; Ang pagbuhi ug isda sa aquarium kay isa ka relaxing nga hobby.; Ang mga binuhi nga baboy sa ilang farm kay maayo ug pag-atiman.</t>
+          <t>Usa ka matang sa tradisyonal nga sakayan sa pagsakay nga gigamit sa Dagat sa Arabia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(euphemistic) a man's penis, something or someone being raised or bred; a ward; a pet</t>
+          <t>['batil']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(euphemistic) a man's penis, something or someone being raised or bred; a ward; a pet</t>
+          <t>Ang batil nga gipanag-iya sa akong lolo kay isa ka klasik nga pamanhon.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1</v>
+          <t>Ang mga mangingisda naggamit og batil aron mangita og isda sa dagat.</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>makagisi og pitaka</t>
+          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ang restaurant nga ilang giadtoan makagisi og pitaka kaayo.; Ang iyang bag-ong sapatos makagisi og pitaka tungod sa kamahal.; Si Pedro nagreklamo kay ang tuition fee sa eskwelahan makagisi og pitaka.; Ang mga luxury items kasagaran makagisi og pitaka sa ilang presyo.; Si Maria nakapalit ug bag nga makagisi og pitaka tungod sa kamahal.</t>
+          <t>Maglakaw sa paghisgot</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> extremely expensive</t>
+          <t>['buhat', 'pasulti-on', 'sulti', 'pabuhaton']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> extremely expensive</t>
+          <t>Si Ana nagpakita sa iyang abilidad sa pagtrabaho, buhat ang pasulti-on dili sulti ang pabuhaton.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1</v>
+          <t>Nagpabuhat ko sa artista nga ang mananap ray pasulti-on dili sulti ang pabuhaton kay gusto nako nga malipay ang mga bata sa ilang show.</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baba sa atay</t>
+          <t>makagisi og pitaka</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ang baba sa atay kinahanglan ampingan ug atimanon para sa maayong panglawas.; Ang problema sa baba sa atay kasagaran makuha pinaagi sa dili maayong pagkaon.; Ang mga tambal para sa baba sa atay kay kinahanglan sa pag-maintain sa maayong kondisyon.; Ang mga problema sa baba sa atay kasagaran magsugod sa dili maayong lifestyle.; Ang pag-amping sa baba sa atay usa ka importante nga parte sa pag-atiman sa lawas.</t>
+          <t>mahal kaayo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(anatomy, idiomatic) diaphragm</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(anatomy, idiomatic) diaphragm</t>
+          <t>Ang iyang bag-ong sapatos makagisi og pitaka tungod sa kamahal.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Nakita nako nga makagisi og pitaka ang sangko na lansang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>pabuto</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>usa ka patok</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>['pabuto']</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ang mga bata malipay kaayo sa mga pabuto kada New Year.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Nagpalit kami og daghang pabuto para sa pista sa baryo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>walay man kardaba mamunga og tundan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Si Pedro nasayod nga walay man kardaba mamunga og tundan, mao nga nagbantay siya sa iyang mga desisyon.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Ang mga mag-uuma nahibulong kay bisan unsaon nila, walay man kardaba mamunga og tundan sa ilang uma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ipanabi na sa clouds</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Isulti kana sa mga marine</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>['ipanabi']</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ang iyang mga istorya pirmi ipanabi na sa clouds kay dili tinuod.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Ang mga piloto nagplano nga ipanabi na sa clouds ang mensahe nga nahuman na ang misyon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chona Mae</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tsunami!</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>['Chona']</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Ang mga bata nga nagdula sa park pirmi lang mag-Chona Mae.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>"Si Chona Mae maoy akong silingan nga pirme manghatag og pagkaon."</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>anak sa sala</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>usa ka anak nga dili-konsejero</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>['sala']</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Si Juan nga anak sa sala kay giatiman sa iyang inahan bisan walay suporta sa iyang amahan.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Ang pari mipahinumdom nga ang tanan mag-ampo ug magbansay aron dili mahulog sa pagkahimong anak sa sala.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bukhad og palad</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>mahinatagon Synonyms: manggihatagon</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>['bukhad']</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Si Ana bukhad og palad, pirmi lang maghatag bisan sa mga dili kaila.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Si Lola Pilar bukhad og palad aron makita ang basa nga sulat sa iyang gamay nga apo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>pasok, Luningning</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>miingon sa kaugalingon sa dihang pag-poking sa usa sa iyang mga winnings sa usa ka dula sa mga kard</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>['pasok']</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pasok, Luningning, ug paminawa ang mga instructions.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>"Pasok, Luningning, kay naghulat na ang imong amahan sa kusina."</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>kuskos-balungos</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>alternatibong pagsulat sa kuskos balungos</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Si Pedro kuskos-balungos pirmi, bisan gamay nga problema.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ang akong ginikanan kuskos-balungos sa banyo kada Sabado aron limpyohan pag-ayo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>miulbo ang kaspa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>sa pag-abli ngadto sa kasuko</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Si Ana miulbo ang kaspa human nabal-an nga gilimbongan siya.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Human sa dugang duha ka adlaw nga walay ligo, si Pedro nakabantay nga miulbo ang kaspa sa iyang ulo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>maghilak ang adlaw</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>mabul-og</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>['maghilak']</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nag-relax sa balay samtang naghilak ang adlaw.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ang mga bata nagdali og pauli pagkahuman nila makit-an nga maghilak ang adlaw tungod sa kusog nga ulan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>anak sa sala</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>usa ka anak nga dili-konsejero</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>['sala']</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Ang anak sa sala kasagaran maglisod sa pagsulod sa mga respetadong institusyon.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Nagbisita ang pari sa balay ug giampo ang anak sa sala nga nakabaton og sakit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ayaw pagbuot, lain-lain tag lubot</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ayaw ako isulti kon unsay buhaton</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>['ayaw', 'lubot']</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Ayaw pagbuot, lain-lain tag lubot, tanan kita adunay lain-lain nga kinabuhi nga gipili.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sa pagkalibang, ayaw pagbuot, lain-lain tag lubot, mao nga lain-lain pud ang naandan nato nga posisyon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>abot sa dunggan ang ngisi</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>nga dili gayod malipay</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>['abot', 'dunggan', 'ngisi']</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Ang among boss, abot sa dunggan ang ngisi sa dihang nadawat ang dagkong proyekto.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Ang bata napintalan og pulang lipstick nga abot sa dunggan ang ngisi, nagkatawa ang iyang mga ginikanan pagkakita niya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ander de bunal</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gi-squeeze</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>['bunal']</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Si Pedro kay ander de bunal, kay pirmi lang musunod sa iyang asawa bisan unsa pa.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Ang bata nakuyawan pagkahuman nga ander de bunal siya sa iyang amahan tungod sa iyang pagkabadlong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>walay man kardaba mamunga og tundan</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Ang mga estudyante giingnan nga walay man kardaba mamunga og tundan, mao nga magtuon sila pag-ayo.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ang akong lolo kanunay magsulti nga walay man kardaba mamunga og tundan, mao nga ang among mga punuan sa saging dris likod balay pulos gyud mga kardaba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>magbiko og pink</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>sa pagsaulog</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>['magbiko']</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Si Maria magbiko og pink sa ilang party sa balay.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>"Si Lola nagplano nga magbiko og pink alang sa umaabot nga pista."</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ang gaba dili magsaba</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ang silot tungod sa iyang mga sayop o mga paglapas moabut sa wala damha</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>['magsaba']</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga nagbuhat ug dautan maghulat sa ilang gaba kay ang gaba dili magsaba.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Naglibog si Juan kung ngano nga natagak ang baso, kay wa siya kabantay nga niabot na ang gaba, hangtod nga nasayran niya nga ang gaba dili magsaba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>binatilay</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>sa pag-aghat sa usag usa sa mga penis</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>['binatilay']</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ang binatilay nga binuhatan kay kinahanglan pugngan aron malikayan ang mga problema.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>"Ang mga bata nagkakatawa samtang nagbinatilay sa ilang likod-balay."</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>nadakpan na</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>gisultihan sa usa ka tawo nga adunay bag-ong buhok</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Nadakpan na ang mga illegal nga nagbaligya sa merkado.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ang kawatan nga nisulod sa balay gabii, nadakpan na sa mga pulis karong buntaga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>abli ang Gaisano</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>nga ang usa nga mosul-ob</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ang mga tao nga abli ang Gaisano kasagaran walay pakialam sa ilang itsura.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Nagpalit mi og bag-ong laptop kay abli ang Gaisano karong adlawa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>makawat</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>mahimong ma-stolen</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>['makawat']</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ang bata ni Maria makawat kaayo, bisan kinsa lang pwede makagunit niya.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Ang akong pitaka nga gibutang sa lamisa makawat sa mga kawatan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ander da bunal</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gi-squeeze</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>['bunal']</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Si Juan kay ander da bunal, bisan unsa isugo sa iyang asawa kay tumanon.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Ang bata mitindog aron ander da bunal ni Tatay human kini masayop sa iyang gibuhat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>bahong biyudo</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>adunay kusog nga baho nga musky o balsam</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>['bahong']</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Ang mga gamit sa balay nga wala gipanumbaling kay bahong biyudo.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Si Tatay Juan, nga usa ka biyudo, dili na makasabot sa bahong biyudo nga naggikan sa iyang mga sinina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>gigukod sa plansa</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>['gigukod']</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Si Maria gigukod sa plansa, bisan unsa nga okasyon, dili gyud magplantsa.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ang iring gigukod sa plansa kay nagdula sila sa kusina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>pangatulig luwag</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Ang iyang giingon kay murag pangatulig luwag, dili ko kasabot.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Nag-uban mi sa kusina, ug gi-pangatulig luwag nako ang sinugba aron dili masunog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ninja ray mopatay ninjo</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>usa ka pulong nga nag-aplay sa Leyte ug Boholano nga mga dialekto sa Cebuano</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>['mopatay']</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Ayaw mo pag-away, ninja ray mopatay ninjo nga wala'y saba.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Ang mga bata sa kalye nagdula og ninja-ninja, ug ingon sa usa "Ninja ray mopatay ninjo sa atong kalaban hantod sa maoy kahadlok!"</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>tunga</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>katunga</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>['tunga']</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Ang mga magtiayon nagbahin sa ilang mga responsibilidad sa tunga.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>"Pag-utong naku sa akong sandwich, akong gitunga kini aron makakaon mi duha."</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>gadalag ulan</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>usa ka lalaki nga homoseksual</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Si Pedro gadalag ulan, bisan unsa pa nga sitwasyon.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Ang ulap gadalag ulan karong adlawa, maong magdala ko og payong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>binatilay</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sa pag-aghat sa usag usa sa mga penis</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>['binatilay']</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ang binatilay nga mga tawo kay kasagaran mag-uban-uban sa ilang mga barkada.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Sa tradisyonal nga ritwal, ang binatilay gihimo isip bahin sa pagpasidungog sa ilang kaugalingong kultura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>kalas og bugo</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>usa ka pulong nga gigamit sa pagsulti sa usa ka tawo nga siya nagkinahanglan og dugay kaayo aron masabtan kon unsay gipamulong</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>['kalas']</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Ang pagsunod-sunod nimo niya, kalas og bugo ra.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Gikuhan siya og tubig aron ipaagi sa kalas og bugo nga alkantarilya.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>paabang</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>pag-abang</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Gipahimutang ang iyang balay aron ipaabang sa mga bakasyonista.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Nagpaabang sila og mga bisekleta alang sa mga bisita sa park.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>buak ang pakwan</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>aron sa pag-abli sa cherry</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Si Ana naghulat nga buak ang pakwan sa iyang first night sa kasal.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Nangita ug kutsilyo si Pedro kay gusto niyang buak ang pakwan para sa meryenda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>kuwang sa tagad</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>['tagad']</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Si Pedro kuwang sa tagad, bisan unsa nga event ganahan magpakita.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ang tanom nga wa matagda, nagpakita og mga sintomas nga kuwang sa tagad sama sa mga dili hapsay nga dahon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>hunaw</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>['hunaw']</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Si Pedro naghunaw sa iyang mga sayop kay dili siya gusto ma-blame.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Si Maria mihunaw sa iyang mga kamot human siya nag-ani sa gulay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>tuslok baki</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>usa ka dula</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>['tuslok']</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Ang mga bata nagpraktis sa tuslok baki aron mahimong champion sa dula.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>"Nakit-an nako si Lito nga nagkuha og sungkod aron magtuslok baki sa daplin sa sapa."</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>minyo og lawas</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>nga adunay lawas sa amahan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Si Ana minyo og lawas tungod sa iyang pagka-busy sa trabaho ug pamilya.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Ang bata nagdula sa buhangin ug nakapangayo sa iyang amahan og mga sungkod aron makabuhat og minyo og lawas nga kahoy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>miulbo ang kaspa</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>sa pag-abli ngadto sa kasuko</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Si Pedro miulbo ang kaspa human naay nakig-away niya.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Nagpalit si Ana ug bag-ong shampoo kay miulbo ang kaspa sa iyang ulo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ang nahimo dili mahimong malikayan</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>['mabalik']</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Ang mga tawo giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Pag-abot sa panahon sa tig-ulan, diha ra jud sa patag magtapok ang tubig kay dili na mabalik ang baha paingon sa bukid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>batil</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Usa ka matang sa tradisyonal nga sakayan sa pagsakay nga gigamit sa Dagat sa Arabia</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>['batil']</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Ang mga libro sa kasaysayan naghisgot bahin sa mga batil nga nagsuroy sa laing-laing lugar.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Gibatil nako ang akong sinina human ko manglaba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>kakha tuka</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>kamot-sa-lubong</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>['kakha', 'tuka']</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Si Juan pirmi lang kakha tuka, walay nahabilin nga budget.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ang maya nagkakha tuka sa nataran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>makabuhi og patay</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>usa ka makapatikod nga bakak o sugilanon</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>['makabuhi', 'patay']</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Si Pedro makabuhi og patay sa iyang mga jokes.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ang makalilisang nga gahum sa maayong pagkahibalo makabuhi og patay nga lawas sa kadlawon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>lunod patay</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>dihard</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>['lunod', 'patay']</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Si Pedro lunod patay sa iyang prinsipyo, dili gyud magbag-o.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Ang biktima nakit-an nga lunod patay sa dagat human sa kusog nga bagyo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>mangnukos</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>sa pag-abli sa usa ka pista</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>['mangnukos']</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Si Pedro mangnukos sa mga events nga walay imbitasyon.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Ang iring nilayat sa atop ug nagmangnukos sa ilaga nga misud sa balay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>manira sa dalan</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>aron magpabilin nga magmata hangtod sa gabii</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>"Manira sa dalan imong mga plano, walay padulngan."</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Ang mga bata nagduwa ug manira sa dalan gamit ang ilang mga ligid nga sakyanan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>abot sa dalunggan ang ngisi</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>nga dili gayod malipay</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>['abot', 'dalunggan', 'ngisi']</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Ang bata, abot sa dalunggan ang ngisi sa dihang gihatagan ug dako nga regalo.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ang babaye, abot sa dalunggan ang ngisi tungod sa iyang katawa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>walay mahay nga gauna</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ang nahimo dili mahimong malikayan</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>['mahay']</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Si Ana nakasabot nga walay mahay nga gauna, mao nga nagbantay siya sa iyang mga desisyon.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Nagtingala si Juan kung ngano nga magbuot-buot si Pedro nga mobiyahe nga walay mahay nga gauna ug wala pa man gani siya nakahibalo sa tanan nga mga detalye.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>mag-ihaw og lata</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>sa pagluto sa mga pagkaon nga tinago</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>['mag-ihaw']</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Si Pedro mag-ihaw og lata kung walay luto nga pagkaon.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Si Juan mag-ihaw og lata nga naay sulod nga mais para sa iyang proyekto sa arte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>kulang sa dukol</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>usa ka buangbuang nga tawo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>['dukol']</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Ang iyang anak kulang sa dukol, dili gyud magtinarong sa pag-eskwela.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ang bata kulang sa dukol, mao nga giingnan siya sa iyang ginikanan nga magmatngon sa sunod nga dulaan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>kakha tuka</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>kamot-sa-lubong</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>['kakha', 'tuka']</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Si Maria nagkinabuhi nga kakha tuka, walay nahabilin nga kwarta.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Ang mga langgam nagkakahituka sa mga sagbotan sa umahan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>basa og baba</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>mabangis</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>['baba']</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga basa og baba kasagaran dili ganahan makakita sa mga tahimik nga tao.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Nagbasaan sa iyang baba si Juan samtang nag-inom ug tubig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>bato og kasingkasing</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>dili-makalolooy</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>['bato']</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Si Pedro bato og kasingkasing, dili gyud siya malumo bisan sa mga bata.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Ang mga duwende nakakita og bato og kasingkasing sa tunga sa lasang ug naglibog sila unsaon kini nahimong ingon ana ang porma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mahimo nimong pagdala ang kabayo ngadto sa tubig</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>['madala', 'mainom']</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga dili magpaningkamot dili gyud magmalampuson, madala nimo ang baka sa suba apan dili nimo mainom.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Naglakaw mi sa uma ug among gisulayan nga madala nimo ang baka sa suba apan dili nimo mainom tungod ky dili siya mahaylo ug duol biskan unsang buhata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>['lingaw', 'dakpa']</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, aron malingaw ka sa kinabuhi.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Pagmata nako sa buntag, nangutana akong igsoon kung unsa'y akong buhaton. Gisulti nako siya nga, "Kung wala kay lingaw sa kinabuhi, dakpa akong utot," kay lingaw man siya mangdakop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>gwapo kon magtalikod</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>nindot nga tan-awon gikan sa likod</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>['magtalikod']</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ang mga tao nga gwapo kon magtalikod kasagaran dili magdugay sa ilang relasyon.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Si Juan gwapo kon magtalikod, kay nindot ug porma ang iyang buhok ug likod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>murag namiya og tai</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Usa ka tawo nga mibiya sa dili-iasa nga walay iyang pulong</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>"Ang silingan murag namiya og tai, kalit lang wala."</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Ang bata nagdali sa pagdagan kay murag namiya og tai sa kasilyas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>mag-ugbok og mohon</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>sa pagpakigsekso</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>['mag-ugbok']</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Si Maria ug ang iyang bana mag-ugbok og mohon sa ilang balay.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ang mga trabahante mag-ugbok og mohon aron masugdan na ang pagtukod sa bag-ong balay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>dula og panit</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>sa pag- masturba</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>['dula']</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ang iyang barkada kay dula og panit, bisan unsa na lang nga kalipay ang gihimo.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ang bata nagdula og panit sa daplin sa suba, gamit ang tanom nga iya nakuha gikan sa palibot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>dili makaon og iro</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>makalilisang</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>['makaon']</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga dili makaon og iro kasagaran walay respeto sa uban.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>"Ang among silingan dili makaon og iro kay nagaalaga ra siya og iring."</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>kulang sa tagad</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>['tagad']</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Si Juan kulang sa tagad, pirmi lang magpasikat sa mga tao.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ang bata gibati nga siya kulang sa tagad sa ilang panimalay kay busy kaayo ang iyang ginikanan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>manira sa dalan</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>aron magpabilin nga magmata hangtod sa gabii</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Ang iyang barkada manira sa dalan hangtud sa kaadlawon.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Ang mga tindero manira sa dalan kada oras alas-sais sa buntag matud sa balaod sa syudad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>makabugto og panty</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>pisikal o seksuwal nga madanihon</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>['makabugto']</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Si Ana makabugto og panty sa iyang pagka-sexy.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Nagkatawa ang mga bata og kusog nga nahugaw ang ilang duwaan nga makabugto og panty sa kalit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>sabong</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>usa ka kompetisyon</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>['sabong']</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Ang sabong sa mga manok kay paborito nga pastime sa mga kalalakin-an.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Nagbutang kog tubig ug sabong sa palanggana para sa laba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>manglutasay</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>usa ka manunulak sa mga bukog</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>['manglutasay']</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Si Pedro pirmi manglutasay ug uyab nga mga batan-on.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Ang mga bata nagdula sa suba ug naay pipila sa ilaha nga nagmanglutasay ug mga lamas sa kilid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>bag-ong haon</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>bag-o nga gihimo</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>['bag-ong', 'haon']</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Ang bag-ong haon nga balay ni Maria kay puno sa modernong mga kagamitan.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Naghuot ang kusina tungod sa bag-ong haon nga nilung-ag nga kan-on.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>istorya ilalom sa dagat</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Usa ka dakong basura</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Si Juan naglagot kay ang nadungog niya puro istorya ilalom sa dagat.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Ang mga mananagat nakadungog og istorya ilalom sa dagat mahitungod sa nawagtang nga barko nga panalipdan sa mga sirena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>gwapa kon magtalikod</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>nindot nga tan-awon gikan sa likod</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>['magtalikod']</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Si Pedro pirmi lang magbuot-buot ug sulti nga gwapa kon magtalikod.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Naglingaw-lingaw mi ug lakaw sa mall ug nakakita ko ug usa ka babaye nga gwapa kon magtalikod kay maayong pagka-ayo ang iyang tindog.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>kitang tanan magkamali</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>['naay', 'masipyat']</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Ang iyang amigo nakalimot sa meeting, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Ang kabaw na naglakaw sa uma nadakdak ug kalit kay bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>mura og halas nga nagluno</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ang usa ka tawo nga magbiya sa iyang mahugaw nga sinina sa tanang dapit sa balay</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>['nagluno']</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>"Ang kwarto sa bata mura og halas nga nagluno, walay nasunod nga kalimpyo."</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>"Tungod sa kainit sa adlaw, makit-an nimo ang halas nga nagluno sa daplin sa sapa."</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>miulbo ang kaspa</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>sa pag-abli ngadto sa kasuko</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Ang iyang boss miulbo ang kaspa tungod sa sayop nga trabaho.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Ang iyang kaspa miulbo pagpag sa paglimpyo niya sa iyang buhok.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>gadalag ulan</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>usa ka lalaki nga homoseksual</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Si Juan kay gadalag ulan, maong daghan ang naglikay niya.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Nag-andam si Maria ug payong kay ang langit kay gadalag ulan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ang masuya madeads</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>['masuya']</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Ayaw suya-suya kay ang masuya madeads.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ang masuya madeads tungod kay nasuya siya sa bag-ong kotse sa iyang silingan ug naghinanok, naapsan siya sa sakuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>gigukod sa plansa</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>['gigukod']</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga gigukod sa plansa kasagaran dili mag-atiman sa ilang kaugalingon.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Ganiha buntag, nagdali ko ug gamay, maong ang akong kamiseta gigukod sa plansa aron mawala ang tupi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>kapugngan pa ang baha, dili ang biga</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>dili mapugngan</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Si Maria adunay dakong pangandoy nga dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Pag-abot sa kusog nga ulan, kapugngan pa ang baha, dili ang biga sa yuta nga grabe kaayo ang pag-inilog ug pag-atake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>gadalag uwan</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>usa ka lalaki nga homoseksual</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Si Maria gadalag uwan, pero walay mopauli sa iyang pagkatawo.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Ang madan-ag nga panganod sa langit gadalag uwan nga naghatag og lapad nga ngitngit nga pangandoy sa mga uma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>kinsa man na imong sala</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>gigamit sa pagsulti sa usa ka tawo nga sila lamang ang may sala sa ilang kaugalingon alang sa ilang kaugalingong mga problema</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>['sala']</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Kinsa man na imong sala nga naghulat sa gawas?</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>"Sa interogasyon, gipangutana siya sa pulis, 'Kinsa man na imong sala nga imong giangkon?'"</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>mogawas ang pari nga walay ulo</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>['mogawas']</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Sa dihang mag-istorya sila og mga horror stories, mogawas ang pari nga walay ulo ang giingon.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Pag-abli sa karaang simbahan sa kagabhion, nakurat sila kay tinuod nga mogawas ang pari nga walay ulo sa altar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>hilawas</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>coitus</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Ang hilawas nga binuhatan kay kasagaran nagdala ug problema sa kinabuhi.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Ang hilawas sa lami nga prutas kay makapabulahan sa lawas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>mabaw og kibot</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>dali nga madaot</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>['kibot']</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Si Ana mabaw og kibot, dali ra kaayo masuko.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Si Lito mabaw og kibot, dali ra kaayo siya makurat basta naay kalit nga buto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>kitang tanan magkamali</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>['naay', 'masipyat']</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Si Maria nasipyat sa pagplano, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Ang kabaw nga naay upat ka tiil masipyat sa pagtabok sa pilapila ug nakasulod kini sa umahan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>hinaw</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>['hinaw']</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Si Juan naghinaw sa iyang sala sa trabaho.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Naghinaw si Maria sa iyang mga kamot human sa pagtrabaho sa garden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>kuskos-balungos</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>alternatibong pagsulat sa kuskos balungos</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Si Ana pirmi lang kuskos-balungos kung naay buhaton nga dili siya ganahan.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Gikuha ni Maria ang kutsilyo ug gigamit kini alang sa kuskos-balungos sa kinay sa isda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>makamala og sapa</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ang usa ka tawo nga may dagkong tiil</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>['makamala']</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Ang iyang amigo makamala og sapa tungod sa kadako sa tiil.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Ang mag-uuma makamala og sapa kay aron makuha ang mga kahoy nga natumba.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>gadalag uwan</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>usa ka lalaki nga homoseksual</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Ang iyang silingan gadalag uwan, pero respetado gihapon sa ilang lugar.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Naglakaw kami sa kalsada ug nakita namo nga ang bata gadalag uwan aron dili mabasa sa kalit nga pag-abot sa ulan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>basa ang tingog</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>dili-matud-an sa tingog</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>['tingog']</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Si Pedro basa ang tingog tungod sa iyang sip-on.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Uwanon kaayo karon mao nga basa ang tingog sa mga bata nga nagdula sa gawas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>higda sa lubi</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>pag-ula</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>['higda']</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Ang iyang mga kauban pirmi lang mag-higda sa lubi kung mag-party.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ang bata nagdula ug higda sa lubi sa baybayon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>mangnukos</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>sa pag-abli sa usa ka pista</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>['mangnukos']</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Ang iyang kauban sa trabaho pirmi lang mangnukos sa mga party.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Ang iring nanagan kay gidunggab, ug ang iro mangnukos kaniya mikanaug sa karsada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>abli ang Gaisano</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>nga ang usa nga mosul-ob</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Si Juan wala kabantay nga abli ang Gaisano, maong giingnan siya sa iyang higala.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>"Daghan taw sa mall kay abli ang Gaisano karon."</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>gisulod sa bulsa</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>sa paglimbong</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>['gisulod']</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Si Juan gisulod sa bulsa sa iyang kauban, maong nawala ang iyang kwarta.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Gisulod ni Ana ang iyang sinsiyo sa bulsa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>kuskos-balungos</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>alternatibong pagsulat sa kuskos balungos</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga kuskos-balungos kasagaran magpaluya sa ilang mga kauban.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Nagpainit si Lola og tubig aron mag-umpisa sa iyang kuskos-balungos sa kinagamyan sa bata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>makamala og sapa</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>ang usa ka tawo nga may dagkong tiil</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>['makamala']</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga dagko ug tiil kasagaran makamala og sapa.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Ang mga bata nagdula sa daplin sa sapa ug kalit lang nga ang isa kanila makamala og sapa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>bahong biyuda</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>adunay kusog nga baho nga musky o balsam</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>['bahong', 'biyuda']</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Ang iyang kwarto kay bahong biyuda, wala gyud linisan ug maayo.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Siya bayot nga bahong biyuda ug wala na gyud motrabaho sukad namatay ang iyang bana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>mamalit og kaso</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>aron mahimong usa ka ambulance chaser</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Si Ana mamalit og kaso aron lang magka-datu.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Nagplano siya nga mamalit og kaso para sa iyang bag-ong snowboard nga gigamit sa bukid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>hatod og patay</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>sa pagtambong sa usa ka paglubong o seremonya sa paghinumdom</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>['hatod', 'patay']</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga hatod og patay kasagaran nagpakita ug respeto sa namatay.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Ang drayber mihangyo nga tabangan siya sa paghatod og patay ngadto sa sementeryo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>walay mahay nga gauna</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ang nahimo dili mahimong malikayan</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>['mahay']</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Si Maria giingnan nga walay mahay nga gauna, mao nga nagmatngon siya sa iyang mga lihok.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Sa duwa, si Juan dili mopauli dayon human matandog ang iyang mga pisi, kay walay mahay nga gauna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>mabaw og kibot</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>dali nga madaot</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>['kibot']</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Si Pedro mabaw og kibot, pirmi lang magyawyaw kung naay di siya ganahan.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Niuyog gamay ang lamesa, dayon si Ana mibalikwas ug may kadiyot nga nisiyagit kay mabaw og kibot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>gwapa kon magtalikod</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>nindot nga tan-awon gikan sa likod</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>['magtalikod']</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Ang mga tao nga gwapa kon magtalikod kasagaran maulaw kung mag-atubang.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>"Si Ana gwapa kon magtalikod kay nindot ug straight ang iyang buhok."</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>taliba</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ang mga genital sa babaye</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>['taliba']</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Ang mga volunteers nag-taliba sa event para malikayan ang mga kagubot.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Ang taliba naglingkod sa tabi sa dalan ug naghulat sa jeepney.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ang gaba dili magsaba</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ang silot tungod sa iyang mga sayop o mga paglapas moabut sa wala damha</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>['magsaba']</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Si Juan nakabalo nga ang iyang gibuhat nga dili maayo mibalik kaniya, ang gaba dili magsaba.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Pag-abot sa gabii, ang gaba sa bukid dili magsaba samtang naglakaw mi pabalik sa lungsod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>mag-ihaw og lata</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>sa pagluto sa mga pagkaon nga tinago</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>['mag-ihaw']</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Si Ana pirmi lang mag-ihaw og lata kung walay sud-an.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Nag-andam si Juan og bonfire sa ilang camp, dayon nag-ihaw siya og lata aron makaluto sa sulod niini.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>toyi</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>coitus</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>['toyi']</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Ang iyang mga joke kay kasagaran tungkol sa toyi.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Ang tigulang nagdala og toyi gikan sa iyang uma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>pangatulig luwag</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>"Si Pedro, sige lang pangatulig luwag walay unod."</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Ang anak nagreklamo nga masakit iyang tiyan human panihapon ug giingon sa iyang mama, "Ayaw sigeg kaon kung dili ka ganahan nga magpangatulig luwag."</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>gigamit nga isulti sa usa ka tawo nga imong gilimbongan sila sa pagtan-aw sa usa ka piho nga direksyon</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>['kitkit', 'kitkit', 'bungi']</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>paglingi, kitkit bungi sa kadaghan sa problema.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Naglingi siya kay gusto niyang makita unsay iyang gipakita, apan pagtuyok, nakita ra diay niyang kitkit langaw ug bungi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>lunod patay</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>dihard</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>['lunod', 'patay']</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga lunod patay kasagaran adunay baruganan nga dili matay-og.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Ang bata naglangoy-langoy sa dagat apan nawad-an og kusog ug hapit na siya lunod patay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>awas og palad</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>• awasan og palad</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>['awas']</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Ang mga awas og palad kasagaran maglisod sa pagplano sa ilang kaugmaon.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Naglakaw ko sa tapok-tapok sa tubig dayon awas og palad ang akong tinuang tubig gikan sa baso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Mahimo nimong pagdala ang kabayo ngadto sa tubig</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>['madala', 'mainom']</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Si Maria giingnan nga kinahanglan siya mag-uban sa pagpaningkamot, madala nimo ang baka sa suba apan dili nimo mainom.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Si Juan naglisod pagkupot sa baka nga iyang gidala sa suba, apan bisan unsaon niya kini pagpaligo, dili gyud mainom ang tubig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>mura og halas nga nagluno</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ang usa ka tawo nga magbiya sa iyang mahugaw nga sinina sa tanang dapit sa balay</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>['nagluno']</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>"Ang balay ni Pedro mura og halas nga nagluno, nagkatag tanan."</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Ang halas sa umah nagluno, ug morag molupad ang mga dahon sa iyang likod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>mamalit og kaso</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>aron mahimong usa ka ambulance chaser</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Si Pedro mamalit og kaso aron makakwarta sa mga biktima sa aksidente.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Nagplano si Maria nga mamalit og kaso alang sa eskuylahan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>anak sa sala</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>usa ka anak nga dili-konsejero</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>['sala']</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Ang mga anak sa sala kasagaran nagdako nga adunay mga pagsulay sa ilang kinabuhi.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Ang anak sa sala maoy ang unang nakakita sa mga insidente nga nahitabo diha sa kwarto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>agi sa bangag sa dagom</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>['agi', 'bangag']</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Si Ana agi sa bangag sa dagom sa iyang pag-eskwela ug pagtrabaho.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Si Mario nagpaningkamot nga agion ang pisi sa bangag sa dagom aron makatahi sa iyang sinina.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>kuwang sa tagad</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>['tagad']</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga kuwang sa tagad kasagaran magbuhat ug mga butang aron makuha ang atensyon.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Ang tanom namong orchid kuwang sa tagad, busa naay mga dahon nga naglaylay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>buhi pay ginamos</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>patay nga sama sa usa ka dughan</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>['ginamos']</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Si Lito buhi pay ginamos, wala na’y paglaom sa iyang kahimtang.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Nag-usisa si Mila sa ilang kusina ug nalipay siya nga mabuhi pa diay iyang ginamos nga giputos sa tupperware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>tunga</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>katunga</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>['tunga']</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Ang tunga sa kalibutan kay naa sa Asia.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Nagputos si Maria og tunga ka buok saging alang sa iyang anak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>gilawog sa tirong</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>sa pagbutang sa peligro sa usa ka tawo, ilabina</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>['gilawog']</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Si Juan gilawog sa tirong, bisan wala siya naghimo sa sayop.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Ang ilaga gilawog sa tirong aron kini dali madakop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>makamala og sapa</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ang usa ka tawo nga may dagkong tiil</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>['makamala']</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Si Juan makamala og sapa sa iyang mga tiil.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Si Maria naglakaw palibot sa bukid ug nakit-an niya ang ilang edipisyo nga makamala og sapa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>kulang sa tagad</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>['tagad']</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Si Maria kulang sa tagad, pirmi lang magbinuang aron makuha ang atensyon sa iyang mga kauban.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Ang balay ni Lolo ug Lola kulang sa tagad, mao nga hapit na mapapas ang ilang pintal ug nagkinahanglan na’g bag-ong kisame.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>giprito sa kaugalingong mantika</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Alternatibo nga porma sa giluto sa kaugalingong mantika</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>['giprito']</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Si Ana giprito sa kaugalingong mantika tungod sa iyang mga aksyon.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Nagprito si Maria ug isda gamit ang kaugalingon niyang mantika gikan sa baboy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>dili na nimo mabalik ang baha sa bukid</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ang nahimo nahimo na</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>['mabalik']</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Si Maria giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga nagpadayon na sa iyang mga plano.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Ang mga residente sa baryo nanglimpyo og nag-amping kay dili na nila mabalik ang baha sa bukid ug kinahanglan nilang moandal sa sitwasyon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>mogawas ang pari nga walay ulo</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>['mogawas']</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Kung magtuyok-tuyok ka sa kadalanan, mogawas ang pari nga walay ulo.</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Sa karaang kastilyo, matud pa sa mga lumolupyo, usahay mogawas ang pari nga walay ulo kung gabii.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ipanabi na sa clouds</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Isulti kana sa mga marine</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>['ipanabi']</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Ang imong mga plano, ipanabi na sa clouds kay maabot ra na.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Ang detalye sa imong presentation, ipanabi na sa clouds aron ma-access sa tanan bisan asa pa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>gibati og kaanyag</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>prima donna</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Ang mga tawo nga gibati og kaanyag kasagaran magdala ug samok sa grupo.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Ang batang babaye gibati og kaanyag samtang nagtan-aw siya sa matahum nga dagat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ipanabi na sa clouds</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Isulti kana sa mga marine</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>['ipanabi']</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Bisan unsa ka lisod, ipanabi na sa clouds ang imong mga pag-ampo.</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Pagka gabii, among ipanabi na sa clouds ang among mga mensahe pinaagi sa drone nga adunay mga light display.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>molayag sa kalipay</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>sa pagpakigsekso</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>['molayag']</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Sa dihang nagmolayag sa kalipay ang grupo, nakalimot sila sa ilang mga problema.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Sa ilang bakasyon, ang barko molayag sa kalipay sa nag-aninaw nga dagat samtang ang mga pasahero nagringig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>katagakon ang mata</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>mag-ulog</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>['mata']</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Si Maria katagakon ang mata human sa pila ka gabii nga trabaho.</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Ang mata ni Juan kay katagakon kay giisip niya ang numero sa mga bituon sa langit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ang masuya madeads</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>['masuya']</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Si Juan kay permi masuya sa mga gadgets sa uban, pero ang masuya madeads.</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Siya miingon nga ang masuya madeads, og nagtuo gyud siya nga ang pagkamasuya makaresulta sa pagkamatay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>mogawas ang pari nga walay ulo</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>['mogawas']</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Mogawas ang pari nga walay ulo kung ang balay walay suga.</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sa karaang kastilyo, giingon nga sa kagabhion mogawas ang pari nga walay ulo sa daang simbahan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>basa ang tingog</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>dili-matud-an sa tingog</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>['tingog']</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Ang singer nga basa ang tingog naglisod ug kanta sa concert.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Ang papel nabasa kay nabutangan og tubig, ug ang tingog sa paghapnig sa papel nagbasa usab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>batang murag korek</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>dili-matag-as</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>['batang']</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Ang batang murag korek nga si Juan kasagaran mag-atubang sa mga problema sa balay.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>"Gipaduwaan sa amahan ang bata og korek samtang nagtan-aw siya sa mga gamit sa kusina."</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>maabot sa luwa</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>duol dili layo</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>['maabot', 'luwa']</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Si Maria nag-invite ug friends kay ilang balay maabot ra sa luwa.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Naglumlum ang itlog sa pipit ug, sa walay pagduha-duha, kini maabot ra sa luwa sa ilahang pugad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>ayaw adto og gubat kon wala kay bala</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>ayaw pagbuhat ug dili-andam</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>['ayaw', 'adto']</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Si Juan giingnan nga ayaw adto og gubat kon wala kay bala kay walay ayo.</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Si Pedro giingnan sa iyang amahan nga ayaw adto og gubat kon wala kay bala aron dili ka maglisod sa pagsabak.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Dataset/Test_Set.xlsx
+++ b/Dataset/Test_Set.xlsx
@@ -458,579 +458,579 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>lunod patay</t>
+          <t>anak sa sala</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>dihard</t>
+          <t>usa ka anak nga dili-konsejero</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['lunod', 'patay']</t>
+          <t>['sala']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Si Maria lunod patay sa pagpanalipod sa iyang mga kauban.</t>
+          <t>Ang anak sa sala nga si Maria kay ginaatiman gihapon sa iyang lola ug lolo.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ang balita miingon nga dunay usa ka tawo nga lunod patay nga nakit-an sa lanaw kagahapon.</t>
+          <t>Ang anak sa sala nagdula duol sa altar samtang nagaampo ang pari.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gibati og kaanyag</t>
+          <t>gibuhi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prima donna</t>
+          <t>ang penis sa usa ka lalaki</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['gibuhi']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Si Ana gibati og kaanyag, maong pirmi siya nagbuot-buot.</t>
+          <t>Ang mga bata nga iyang gibuhi kay nagdako nga maayong laki.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>"Gibati gyud ni Carla og kaanyag sa iyang bag-ong sinina, maong nagpakita siya sa iyang mga higala."</t>
+          <t>Si Lola ang gibuhi sa among gidala nga gamay nga iro gikan sa dalan.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>buhi pay ginamos</t>
+          <t>nadakpan na ba ang nagtupi nimo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>patay nga sama sa usa ka dughan</t>
+          <t>gisultihan sa usa ka tawo nga adunay bag-ong buhok</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['ginamos']</t>
+          <t>['nagtupi']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga buhi pay ginamos kasagaran naglisod sa kinabuhi.</t>
+          <t>Nadakpan na ba ang nagtupi nimo nga wala man nindot imong buhok?</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nagbitay ang mga isda sa init nga adlaw, apan buhi pay ginamos ang ilang hitsura.</t>
+          <t>Gidala dayon siya sa istasyon sa pulis ug giingnan nga "Nadakpan na ba ang nagtupi nimo nga wala man mangayo og permiso?"</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lisod pukawon ang gamata</t>
+          <t>buotan ra og matulog</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa nagmata o sa usa ka tawo nga dili magmata</t>
+          <t>malinong</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['pukawon', 'gamata']</t>
+          <t>['matulog']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ang mga estudyante nga late na matulog, lisod pukawon ang gamata.</t>
+          <t>Si Pedro buotan ra og matulog, kay pirmi lang magbinuang sa klase.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pagmata na, Toto, lisod pukawon ang gamata kung naa pay iring nga nagkatulog sa imong tiyan.</t>
+          <t>Si Lola kung mahigda, buotan ra og matulog kay dili siya maglihok-lihok sa gabii.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>minyo og lawas</t>
+          <t>murag langaw nga nakatugdon sa kabaw</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nga adunay lawas sa amahan</t>
+          <t>nouveau riche</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['nakatugdon']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ang iyang amiga giingnan nga minyo og lawas tungod sa kadako sa iyang tiyan.</t>
+          <t>"Siya karon murag langaw nga nakatugdon sa kabaw, taas kaayo og pride."</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sa simbahan, ang magtiayon gikasal ug nagminyo og lawas aron maglumon sa ilang pagmamahalan.</t>
+          <t>Pag-adlaw, nakita nako ang langaw nga nakatugdon sa likod sa kabaw samtang nag-id-id kini ug mga sanga.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>walay man kardaba mamunga og tundan</t>
+          <t>kang kinsa man na imong sala</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
+          <t>gigamit sa pagsulti sa usa ka tawo nga sila lamang ang may sala sa ilang kaugalingon alang sa ilang kaugalingong mga problema</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['sala']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ang mga tawo giingnan nga walay man kardaba mamunga og tundan, mao nga magmatngon sila sa ilang mga buhaton.</t>
+          <t>Kang kinsa man na imong sala nga nagdako ka ug kalit?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sa among umahan, makita gyud nimo nga walay man kardaba mamunga og tundan bisan unsaon pa nimo pagsulay.</t>
+          <t>"Giimbestigahan sa konsehal ang panghitabo, ug nangutana siya kang kinsa man na imong sala nga nahitabo ang aksidente."</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>manglutasay</t>
+          <t>ayaw adto og gubat kon wala kay bala</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>usa ka manunulak sa mga bukog</t>
+          <t>ayaw pagbuhat ug dili-andam</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['manglutasay']</t>
+          <t>['ayaw', 'adto']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Si Maria nalipay kay ang iyang kauban dili manglutasay.</t>
+          <t>Ang mga negosyante giingnan nga ayaw adto og gubat kon wala kay bala sa kompetisyon.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nagtapok ang mga bata sa silong sa balay aron magduwa og mga luto-lutoan, ug makita nimo nga manglutasay sila ug mga puto't kutsara.</t>
+          <t>Ang mga sundalo giingnan sa ilang kumander, "Ayaw adto og gubat kon wala kay bala, kay delikado ang kahimtang diha."</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nakalugsong</t>
+          <t>mag-ugbok og mohon</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sa pag-adto gikan</t>
+          <t>sa pagpakigsekso</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['nakalugsong']</t>
+          <t>['mag-ugbok']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ang mga trabahante nakalugsong gikan sa taas ug giuli ang mga gamit.</t>
+          <t>Si Ana nagplano nga mag-ugbok og mohon sa iyang birthday.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ang bata nakalugsong sa bukid human magdula didto.</t>
+          <t>Ang mga trabahante mag-ugbok og mohon aron magtukod og bag-ong balay.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>batang murag korek</t>
+          <t>mingaw pa ang panagat</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dili-matag-as</t>
+          <t>oras sa adlaw nga ang usa ka establisimento adunay pipila ka kostumer ug dili kaayo busy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['batang']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Si Pedro batang murag korek kay bisan gamay pa, maayo na kaayo sa klase.</t>
+          <t>Ang mga negosyo kasagaran mingaw pa ang panagat sa mga sayong oras.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ang batang murag korek ang gisul-ob ni Juan sa iyang Halloween party.</t>
+          <t>Ang mga manginisda nanguli na kay mingaw pa ang panagat tungod sa bagyo.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hatod og patay</t>
+          <t>dili madala og rosaryo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sa pagtambong sa usa ka paglubong o seremonya sa paghinumdom</t>
+          <t>usa ka hingpit nga walay paglaom nga kahimtang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['hatod', 'patay']</t>
+          <t>['madala']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Si Pedro hatod og patay sa iyang kauban sa trabaho.</t>
+          <t>Si Pedro nag-atubang sa mga pagsulay nga dili madala og rosaryo.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nag-hatod og patay ang mga mag-uuma ngadto sa paglubong sa talis.</t>
+          <t>Nag-ingon ang pari nga ang problema sa kalibutan dili madala og rosaryo ug mga pag-ampo lang.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>magtumba og baka</t>
+          <t>higda sa lubi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sa pag-ihaw sa usa ka vaca</t>
+          <t>pag-ula</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['magtumba']</t>
+          <t>['higda']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ang ilang pamilya magtumba og baka kung naa’y dako nga celebration.</t>
+          <t>Si Pedro pirmi lang higda sa lubi kung mag-inom.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ang manggugubat magtumba og baka para sa karne nga ilang ipamaligya sa merkado.</t>
+          <t>Ang bata nagduwa sa baybayon ug kalit lang mihigda sa lubi nga napalid sa balas.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nakalugsong</t>
+          <t>walay man kardaba mamunga og tundan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sa pag-adto gikan</t>
+          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['nakalugsong']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nakalugsong na mi ug gidalit ang among mga ani sa lungsod.</t>
+          <t>Ang mga estudyante giingnan nga walay man kardaba mamunga og tundan, mao nga magtuon sila pag-ayo.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Naglakaw mi sa bukid ug nakalugsong mi ngadto sa suba para maligo.</t>
+          <t>Ang akong lolo kanunay magsulti nga walay man kardaba mamunga og tundan, mao nga ang among mga punuan sa saging dris likod balay pulos gyud mga kardaba.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kuyog baboy</t>
+          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>usa ka tagalong</t>
+          <t>kitang tanan magkamali</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['kuyog']</t>
+          <t>['naay', 'masipyat']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga kuyog baboy kasagaran magpalisod sa ilang mga kauban.</t>
+          <t>Si Maria nasipyat sa pagplano, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Miadto sila sa umahan uban sa ilang kuyog baboy nga gihiktan sa usa ka pisi.</t>
+          <t>Ang kabaw nga naay upat ka tiil masipyat sa pagtabok sa pilapila ug nakasulod kini sa umahan.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dili na nimo mabalik ang baha sa bukid</t>
+          <t>Chona Mae</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ang nahimo nahimo na</t>
+          <t>Tsunami!</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['Chona']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Si Pedro giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga naghinuktok na lang siya.</t>
+          <t>Si Chona Mae pirmi lang magbinuang sa eskwelahan.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sa pag-ulan ug kusug, nakita namo nga dili na nimo mabalik ang baha sa bukid human kini mokalas padulong sa ubos.</t>
+          <t>Si Chona Mae akong silingan nga kanunay akong kaistorya matag buntag.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>gidaman</t>
+          <t>abli ang Gaisano</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sa pag-aturog o pag-aturog</t>
+          <t>nga ang usa nga mosul-ob</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['gidaman']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Gidaman na si Juan, sige lang siya og panaway."</t>
+          <t>Kung abli ang Gaisano, kinahanglan dayon sirad-an aron dili magkatawa ang uban.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>"Gidaman si Maria kagabii, milakaw siya paingon sa gawas nga walay kabalo."</t>
+          <t>"Dali na ta kay abli ang Gaisano ug daghan kaayong baligya nga barato."</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>abot sa dalunggan ang ngisi</t>
+          <t>batang murag korek</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nga dili gayod malipay</t>
+          <t>dili-matag-as</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['abot', 'dalunggan', 'ngisi']</t>
+          <t>['batang']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Pagkahuman sa eksam, abot sa dalunggan ang ngisi ni Juan kay nakapasar siya.</t>
+          <t>Ang batang murag korek nga si Lito pirmi lang nagbuot-buot.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nagtan-aw ko sa litrato nga gipakita ni Ana, abot sa dalunggan ang ngisi niya sa kalipay.</t>
+          <t>Ang batang nagdula sa balas falor murag korek kay tan-aw nimo layo ra siya sa uban.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hilawas</t>
+          <t>magpalapad og papel</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>coitus</t>
+          <t>aron magbaton ug dungog sa buhat sa uban</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['magpalapad']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ang hilawas nga relasyon sa diha nga walay commitment kay lisod.</t>
+          <t>Ang mga tawo nga magpalapad og papel kasagaran dili tinood nga maayong magtrabaho.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nagkinahanglan ko ug hilawas nga pagkaon aron magpabiling lig-on ug himsog ang lawas.</t>
+          <t>Ang mga bata sa klase nagpalapad og papel gamit ang pintal para sa ilang proyekto sa arte.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>buotan ra og matulog</t>
+          <t>lunod patay</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>malinong</t>
+          <t>dihard</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['matulog']</t>
+          <t>['lunod', 'patay']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ang iyang anak buotan ra og matulog, kay pirmi lang mangaway sa mga silingan.</t>
+          <t>Si Pedro lunod patay sa iyang prinsipyo, dili gyud magbag-o.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gabiina na kaayo ug buotan ra og matulog ang bata sa ilang kwarto.</t>
+          <t>Ang biktima nakit-an nga lunod patay sa dagat human sa kusog nga bagyo.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>minyo og lawas</t>
+          <t>hinaw</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nga adunay lawas sa amahan</t>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['hinaw']</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Si Pedro nangita ug exercise routine kay minyo og lawas na siya.</t>
+          <t>Ang iyang kauban naghinaw sa problema kay dili siya gusto maapil.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Si Juan ug Maria nagplano nga mag-minyo og lawas sa sunod buwan ngadto sa simbahan sa ilang baryo.</t>
+          <t>"Naghugaw ang iyang mga kamot sa pintal busa siya mihunaw dayon sa gripo."</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ayaw pagbuot, tagsa-tagsa tag lubot</t>
+          <t>kusog mokaon og gasolina</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ayaw ako isulti kon unsay buhaton</t>
+          <t>gas-gussing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['ayaw', 'lubot']</t>
+          <t>['mokaon']</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bisan unsa ka kapugos, ayaw pagbuot, tagsa-tagsa tag lubot.</t>
+          <t>Ang mga tawo nga mag-drive ug sakyanan nga kusog mokaon og gasolina kasagaran maglisod sa gasto.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ang kalainan sa atong pamaagi kay angay lang respetohon, ayaw pagbuot, tagsa-tagsa tag lubot sa desisyon.</t>
+          <t>Ang makina sa among sakyanan kusog mokaon og gasolina kung nagdagan mi sa highway.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hunaw</t>
+          <t>dula og panit</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+          <t>sa pag- masturba</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['hunaw']</t>
+          <t>['dula']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ang iyang kauban naghunaw sa mga problema aron dili siya maapil.</t>
+          <t>Ang iyang barkada kay dula og panit, bisan unsa na lang nga kalipay ang gihimo.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nagpareha sila paghuman sa trabaho ug naghunaw sa ilang kamot sa kusina aron limpyo.</t>
+          <t>Ang bata nagdula og panit sa daplin sa suba, gamit ang tanom nga iya nakuha gikan sa palibot.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hugot sa bakos</t>
+          <t>makagisi og pitaka</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>aron sa pag-apig sa usa sa iyang kurug</t>
+          <t>mahal kaayo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,483 +1040,483 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si Ana hugot sa bakos kay gusto niya makatipid para sa future.</t>
+          <t>Si Maria nakapalit ug bag nga makagisi og pitaka tungod sa kamahal.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gipahugot ni Juan ang iyang bakos kay nawad-an siya ug timbang.</t>
+          <t>Ang kawatan nakagisi og pitaka aron makuha ang sulod niining kwarta.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kapugngan pa ang baha, dili ang biga</t>
+          <t>makamala og sapa</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dili mapugngan</t>
+          <t>ang usa ka tawo nga may dagkong tiil</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['makamala']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Si Pedro dili mapugngan sa iyang gusto, kapugngan pa ang baha, dili ang biga.</t>
+          <t>Si Pedro makamala og sapa kay grabe kaayo kadako ang tiil.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ang mga trabahante nagtrabaho dili sa pagpatigbabaw sa ilang gugma kondili sa paglimpyo ug pag-alsa sa mga debris tungod kay kapugngan pa ang baha, dili ang biga.</t>
+          <t>Ang babaye makamala og sapa kay nahanaw ang tulay.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
+          <t>binatilay</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gigamit nga isulti sa usa ka tawo nga imong gilimbongan sila sa pagtan-aw sa usa ka piho nga direksyon</t>
+          <t>sa pag-aghat sa usag usa sa mga penis</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['kitkit', 'kitkit', 'bungi']</t>
+          <t>['binatilay']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Pagtan-aw nako sa iyang nawong, kitkit langaw</t>
+          <t>Ang mga batan-on nga nagdula og binatilay sa eskwelahan kay gipahimangnoan sa mga maestro.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Naglingkod ko sa lamisa unya nakit-an nako nga nagpadaplin siya, pagtana-aw, kitkit langaw; paglingi, kitkit bungi, tungod kay gapalupad-lupad ra ang mga langaw ug bungi sa paligid.</t>
+          <t>Nagpasabot ang tigulang nga ang binatilay sa una kay bahin sa ilang tradisyonal nga sayaw nga gihimo panahon sa pista.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>babayeng ikogan</t>
+          <t>sabong</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>transgender</t>
+          <t>usa ka kompetisyon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['ikogan']</t>
+          <t>['sabong']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ang babayeng ikogan nga si Juanita kay giilhan sa ilang baryo.</t>
+          <t>Ang mga sabong sa probinsya kasagaran ginadumog sa mga lokal nga residente.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ang mga bata nalipay ug gikataw-an ang babayeng ikogan nga nahigmata pag-uli nila gikan sa kamingawan.</t>
+          <t>"Ang sabong nga gigamit nako sa pagpaligo humot ug daghan ug sabon."</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>makagisi og pitaka</t>
+          <t>lunod patay</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>mahal kaayo</t>
+          <t>dihard</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['lunod', 'patay']</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Si Pedro nagreklamo kay ang tuition fee sa eskwelahan makagisi og pitaka.</t>
+          <t>Ang iyang amigo lunod patay sa iyang pagtuo bisan pa sa mga pagsulay.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Si Juan napunitan og kutsilyo nga makagisi og pitaka samtang naglakaw sa merkado.</t>
+          <t>Ang sakayan ilang gisakyan nasangit sa dagkong balod, ug nahinumdom ko sa babaye nga lunod patay sa ubos sa dagat.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>gidaman</t>
+          <t>murag langaw nga nakatugdon sa kabaw</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sa pag-aturog o pag-aturog</t>
+          <t>nouveau riche</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['gidaman']</t>
+          <t>['nakatugdon']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Gidaman na pud si Pedro, daghan kaayo siya og storya."</t>
+          <t>"Ang mga tawo nga bag-o rang nakuhaan ug jackpot murag langaw nga nakatugdon sa kabaw."</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>"Ang gidaman nga balay ni Juan dul-an sa dagat."</t>
+          <t>Ang langaw naglupad-lupad sa palibot hangtod nakatugdon sa kabaw.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ang kalimot walay gahom</t>
+          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ang pagkalimtan dili makahatag kanimo ug wala ka kaayohan</t>
+          <t>Mahimo nimong pagdala ang kabayo ngadto sa tubig</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['madala', 'mainom']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ang mga estudyante nga malimot maglisod sa exam, ang kalimot walay gahom.</t>
+          <t>Si Pedro giingnan nga bisan unsaon pagdasig, madala nimo ang baka sa suba apan dili nimo mainom.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Naa koy gipangita sa akong mga gamit, apan murag ang kalimot walay gahom, kay di man gihapon nako makita.</t>
+          <t>Nagkakaboang ang mga mag-uuma kay madala nimo ang baka sa suba apan dili nimo mainom ang hayop bisan init kaayo ang adlaw.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>alsa og balay</t>
+          <t>halinon og aping</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gisulti sa kaugalingon o sa uban kon ang pagkaon naglakip sa mung beans</t>
+          <t>maayo kaayo nga hitsura</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['alsa']</t>
+          <t>['halinon']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bisan kapoy na, alsa og balay gihapon siya para sa kaugmaon sa iyang anak.</t>
+          <t>Si Maria halinon og aping, daghan kaayo siya ug admirers.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nanginahanglan sila og dugang nga tawo kay kinahanglanon gyud nga alsa og balay karon nga adlawa.</t>
+          <t>Naghalinon og aping ang bata human siya gi-wash ug face ni Mama.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>batil</t>
+          <t>gibuhi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Usa ka matang sa tradisyonal nga sakayan sa pagsakay nga gigamit sa Dagat sa Arabia</t>
+          <t>ang penis sa usa ka lalaki</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['batil']</t>
+          <t>['gibuhi']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ang batil nga gipanag-iya sa akong lolo kay isa ka klasik nga pamanhon.</t>
+          <t>Gibuhi niya ang iyang mga tanom nga permi niyang ginatiman.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ang mga mangingisda naggamit og batil aron mangita og isda sa dagat.</t>
+          <t>"Gibuhi sa amahan ang nawong sa iyang anak gamit ang panyo."</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
+          <t>binuhi</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Maglakaw sa paghisgot</t>
+          <t>ang penis sa usa ka lalaki</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['buhat', 'pasulti-on', 'sulti', 'pabuhaton']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Si Ana nagpakita sa iyang abilidad sa pagtrabaho, buhat ang pasulti-on dili sulti ang pabuhaton.</t>
+          <t>Ang mga binuhi nga iro sa ilang balay kay puro mga pure breed.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nagpabuhat ko sa artista nga ang mananap ray pasulti-on dili sulti ang pabuhaton kay gusto nako nga malipay ang mga bata sa ilang show.</t>
+          <t>Ang binuhi nga baka kay gi-atiman pag-ayo aron magamit sa umaabot nga negosyo sa gatas.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>makagisi og pitaka</t>
+          <t>makakutaw og utok</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>mahal kaayo</t>
+          <t>makapalibog</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['makakutaw']</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ang iyang bag-ong sapatos makagisi og pitaka tungod sa kamahal.</t>
+          <t>Ang explanation sa iyang professor makakutaw og utok kaayo.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nakita nako nga makagisi og pitaka ang sangko na lansang.</t>
+          <t>Ang iyahang paghalo sa mainit nga supas makakutaw og utok kay wala pa man gud niupos ang kainit niini.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>pabuto</t>
+          <t>manglutasay</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>usa ka patok</t>
+          <t>usa ka manunulak sa mga bukog</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['pabuto']</t>
+          <t>['manglutasay']</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Ang mga bata malipay kaayo sa mga pabuto kada New Year.</t>
+          <t>Si Juan giingnan nga manglutasay kay ang iyang uyab mas bata kaayo.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nagpalit kami og daghang pabuto para sa pista sa baryo.</t>
+          <t>Ang mga bata sa baryo magdula-dula ug manglutasay sa tabing-suba.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>walay man kardaba mamunga og tundan</t>
+          <t>gi-indian</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
+          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['gi-indian']</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Si Pedro nasayod nga walay man kardaba mamunga og tundan, mao nga nagbantay siya sa iyang mga desisyon.</t>
+          <t>Si Pedro gi-indian sa iyang uyab sa ilang sabot nga date.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ang mga mag-uuma nahibulong kay bisan unsaon nila, walay man kardaba mamunga og tundan sa ilang uma.</t>
+          <t>Wala moabot si Miguel sa ila nahuman nga sabot, kay gi-indian man siya sa Mindanao para magtuon sa mga lumad nga Indian didto.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>kuwang sa tagad</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['tagad']</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ang iyang mga istorya pirmi ipanabi na sa clouds kay dili tinuod.</t>
+          <t>Si Pedro kuwang sa tagad, bisan unsa nga event ganahan magpakita.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ang mga piloto nagplano nga ipanabi na sa clouds ang mensahe nga nahuman na ang misyon.</t>
+          <t>Ang tanom nga wa matagda, nagpakita og mga sintomas nga kuwang sa tagad sama sa mga dili hapsay nga dahon.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chona Mae</t>
+          <t>taliba</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tsunami!</t>
+          <t>ang mga genital sa babaye</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['Chona']</t>
+          <t>['taliba']</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ang mga bata nga nagdula sa park pirmi lang mag-Chona Mae.</t>
+          <t>Ang mga pulis nag-taliba sa mga salida aron protektahan ang mga bisita.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>"Si Chona Mae maoy akong silingan nga pirme manghatag og pagkaon."</t>
+          <t>Ang taliba nagsugod ug talagsaon nga lihok human sa pagkahuman sa operasyon.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>anak sa sala</t>
+          <t>hatod og patay</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>usa ka anak nga dili-konsejero</t>
+          <t>sa pagtambong sa usa ka paglubong o seremonya sa paghinumdom</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['sala']</t>
+          <t>['hatod', 'patay']</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Si Juan nga anak sa sala kay giatiman sa iyang inahan bisan walay suporta sa iyang amahan.</t>
+          <t>Si Pedro hatod og patay sa iyang kauban sa trabaho.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ang pari mipahinumdom nga ang tanan mag-ampo ug magbansay aron dili mahulog sa pagkahimong anak sa sala.</t>
+          <t>Nag-hatod og patay ang mga mag-uuma ngadto sa paglubong sa talis.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>bukhad og palad</t>
+          <t>makabugto og panty</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mahinatagon Synonyms: manggihatagon</t>
+          <t>pisikal o seksuwal nga madanihon</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['bukhad']</t>
+          <t>['makabugto']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Si Ana bukhad og palad, pirmi lang maghatag bisan sa mga dili kaila.</t>
+          <t>Si Pedro ganahan kaayo sa iyang uyab kay makabugto og panty.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Si Lola Pilar bukhad og palad aron makita ang basa nga sulat sa iyang gamay nga apo.</t>
+          <t>Paglaba nako sa akong mga sinina, nasamad ang akong daliri tungod sa hugot nga elax na makabugto og panty.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pasok, Luningning</t>
+          <t>duwa og panit</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>miingon sa kaugalingon sa dihang pag-poking sa usa sa iyang mga winnings sa usa ka dula sa mga kard</t>
+          <t>sa pag- masturba</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['pasok']</t>
+          <t>['duwa']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Pasok, Luningning, ug paminawa ang mga instructions.</t>
+          <t>Ang mga bata nga nagdula sa internet pirmi lang magduwa og panit.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>"Pasok, Luningning, kay naghulat na ang imong amahan sa kusina."</t>
+          <t>Ang mga tambay sa kanto nagduwa og panit sa kadyot nga hagit sa ilang amigo.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>kuskos-balungos</t>
+          <t>istorya ilalom sa dagat</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>alternatibong pagsulat sa kuskos balungos</t>
+          <t>Usa ka dakong basura</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1526,294 +1526,294 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Si Pedro kuskos-balungos pirmi, bisan gamay nga problema.</t>
+          <t>Ang mga tawo nga dili tinuod pirmi lang mag-istorya ilalom sa dagat.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ang akong ginikanan kuskos-balungos sa banyo kada Sabado aron limpyohan pag-ayo.</t>
+          <t>Ang mga nanginhas nakadungog og istorya ilalom sa dagat samtang nagsubsob sa ilang buluhaton.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>miulbo ang kaspa</t>
+          <t>habwa ang kinaon</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sa pag-abli ngadto sa kasuko</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['habwa', 'kinaon']</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Si Ana miulbo ang kaspa human nabal-an nga gilimbongan siya.</t>
+          <t>Si Maria naghabwa ang kinaon kay nagkalibanga.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Human sa dugang duha ka adlaw nga walay ligo, si Pedro nakabantay nga miulbo ang kaspa sa iyang ulo.</t>
+          <t>Naghabwa ang bata sa kinaon gikan sa basket aron ipakaon sa mga iro.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>maghilak ang adlaw</t>
+          <t>litik</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>mabul-og</t>
+          <t>sa pag-aghat sa tudlo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['maghilak']</t>
+          <t>['litik']</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ang mga tawo nag-relax sa balay samtang naghilak ang adlaw.</t>
+          <t>Ang mga tawo nga naglitik sa ilang mga pangandoy kasagaran magmalampuson.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ang mga bata nagdali og pauli pagkahuman nila makit-an nga maghilak ang adlaw tungod sa kusog nga ulan.</t>
+          <t>Naglingkod si Juan sa lamisa ug kalit niyang gilitik ang botelya nga nagbarog.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>anak sa sala</t>
+          <t>duwa og panit</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>usa ka anak nga dili-konsejero</t>
+          <t>sa pag- masturba</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>['sala']</t>
+          <t>['duwa']</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ang anak sa sala kasagaran maglisod sa pagsulod sa mga respetadong institusyon.</t>
+          <t>Si Pedro walay laing gihimo kundi magduwa og panit pirmi.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nagbisita ang pari sa balay ug giampo ang anak sa sala nga nakabaton og sakit.</t>
+          <t>Gipakita sa maestro nga giunsa pagduwa og panit sa tambol aron makuha ang tukmang tingog.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ayaw pagbuot, lain-lain tag lubot</t>
+          <t>istorya ilalom sa dagat</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ayaw ako isulti kon unsay buhaton</t>
+          <t>Usa ka dakong basura</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>['ayaw', 'lubot']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ayaw pagbuot, lain-lain tag lubot, tanan kita adunay lain-lain nga kinabuhi nga gipili.</t>
+          <t>Ang iyang pangatarungan kay istorya ilalom sa dagat, walay klaro.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sa pagkalibang, ayaw pagbuot, lain-lain tag lubot, mao nga lain-lain pud ang naandan nato nga posisyon.</t>
+          <t>Ang mga diver nakahibalo nga lisud ang pag-istorya ilalom sa dagat tungod sa tubig.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>abot sa dunggan ang ngisi</t>
+          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nga dili gayod malipay</t>
+          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['abot', 'dunggan', 'ngisi']</t>
+          <t>['lingaw', 'dakpa']</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ang among boss, abot sa dunggan ang ngisi sa dihang nadawat ang dagkong proyekto.</t>
+          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, kay walay lain maka-entertain nimo.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ang bata napintalan og pulang lipstick nga abot sa dunggan ang ngisi, nagkatawa ang iyang mga ginikanan pagkakita niya.</t>
+          <t>Naglain akong tiyan, mao nga kung wala kay lingaw sa kinabuhi, dakpa akong utot aron makita nato ug tinuod ba.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ander de bunal</t>
+          <t>awas og palad</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>gi-squeeze</t>
+          <t>• awasan og palad</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['bunal']</t>
+          <t>['awas']</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Si Pedro kay ander de bunal, kay pirmi lang musunod sa iyang asawa bisan unsa pa.</t>
+          <t>Si Ana awas og palad, maong pirmi lang maglisod bisan taas ang sweldo.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ang bata nakuyawan pagkahuman nga ander de bunal siya sa iyang amahan tungod sa iyang pagkabadlong.</t>
+          <t>Gihugasan niya ang iyang palad ug karon nag-awas na ang tubig gikan niini.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>walay man kardaba mamunga og tundan</t>
+          <t>hangyo kabayo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
+          <t>usa ka maalamon nga paagi sa pagbaton ug usa ka butang</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['hangyo']</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ang mga estudyante giingnan nga walay man kardaba mamunga og tundan, mao nga magtuon sila pag-ayo.</t>
+          <t>Ang mga tawo nga hangyo kabayo kasagaran magmalampuson sa ilang mga plano.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ang akong lolo kanunay magsulti nga walay man kardaba mamunga og tundan, mao nga ang among mga punuan sa saging dris likod balay pulos gyud mga kardaba.</t>
+          <t>Ang bata naghangyo sa iyang ginikanan nga paliton siya og kabayo.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>magbiko og pink</t>
+          <t>kung wala kay lingaw, dakpa akong utot</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>sa pagsaulog</t>
+          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['magbiko']</t>
+          <t>['lingaw', 'dakpa']</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Si Maria magbiko og pink sa ilang party sa balay.</t>
+          <t>Kung wala kay lingaw, dakpa akong utot aron ma-testing nimo imong abilidad.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>"Si Lola nagplano nga magbiko og pink alang sa umaabot nga pista."</t>
+          <t>Paglingkod nako sa sofa, gisulti nako sa akong ig-agaw, "Kung wala kay lingaw, dakpa akong utot," aron makita namo kung makaya ba niya pagkakupot.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ang gaba dili magsaba</t>
+          <t>ander da bunal</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ang silot tungod sa iyang mga sayop o mga paglapas moabut sa wala damha</t>
+          <t>gi-squeeze</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['magsaba']</t>
+          <t>['bunal']</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga nagbuhat ug dautan maghulat sa ilang gaba kay ang gaba dili magsaba.</t>
+          <t>Ang relasyon nila kay ander da bunal, maong klaro kaayo kinsa ang nagbuot.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Naglibog si Juan kung ngano nga natagak ang baso, kay wa siya kabantay nga niabot na ang gaba, hangtod nga nasayran niya nga ang gaba dili magsaba.</t>
+          <t>Ang bata misunod sa iyang mama nga "ander da bunal" human masagpaan ug kahoy.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>binatilay</t>
+          <t>tinagoan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>sa pag-aghat sa usag usa sa mga penis</t>
+          <t>gitago</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['binatilay']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ang binatilay nga binuhatan kay kinahanglan pugngan aron malikayan ang mga problema.</t>
+          <t>Ang tinagoan nga lihim ni Juan kay nahibaw-an na sa tanan.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>"Ang mga bata nagkakatawa samtang nagbinatilay sa ilang likod-balay."</t>
+          <t>"Ang tinagoan nga kwarta sa luyo sa aparador nadiskobrehan sa iyang igsoon."</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>nadakpan na</t>
+          <t>mamalit og kaso</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>gisultihan sa usa ka tawo nga adunay bag-ong buhok</t>
+          <t>aron mahimong usa ka ambulance chaser</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,1968 +1823,1968 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Nadakpan na ang mga illegal nga nagbaligya sa merkado.</t>
+          <t>Ang mga tawo nga mamalit og kaso kasagaran mga abogado nga gustong magpasikat.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ang kawatan nga nisulod sa balay gabii, nadakpan na sa mga pulis karong buntaga.</t>
+          <t>Ang akong ig-agaw gusto mamalit og kaso aron magamit niya sa among eskwelahan nga praktis.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>abli ang Gaisano</t>
+          <t>mabaw og kibot</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nga ang usa nga mosul-ob</t>
+          <t>dali nga madaot</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['kibot']</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ang mga tao nga abli ang Gaisano kasagaran walay pakialam sa ilang itsura.</t>
+          <t>Ang iyang kauban mabaw og kibot, bisan gamay lang nga butang maglagot na.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nagpalit mi og bag-ong laptop kay abli ang Gaisano karong adlawa.</t>
+          <t>Daling mobakwi si Ana kay mabaw og kibot, labi na kon naay kalit nga tingog.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>makawat</t>
+          <t>halinon og aping</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>mahimong ma-stolen</t>
+          <t>maayo kaayo nga hitsura</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>['makawat']</t>
+          <t>['halinon']</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ang bata ni Maria makawat kaayo, bisan kinsa lang pwede makagunit niya.</t>
+          <t>Si Ana halinon og aping, daghan kaayo siya ug mga manliligaw.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ang akong pitaka nga gibutang sa lamisa makawat sa mga kawatan.</t>
+          <t>Nagposing si Ana aron makuhanan og halinon og aping nga larawan sa iyang mga album.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ander da bunal</t>
+          <t>bukad og ngabil</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>gi-squeeze</t>
+          <t>mga labi nga may lapis</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['bunal']</t>
+          <t>['bukad']</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Si Juan kay ander da bunal, bisan unsa isugo sa iyang asawa kay tumanon.</t>
+          <t>Si Juan bukad og ngabil, bisan unsa nga istorya, pirmi lang magsige ug sulti.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ang bata mitindog aron ander da bunal ni Tatay human kini masayop sa iyang gibuhat.</t>
+          <t>Ang bata kay bukad og ngabil tungod sa iyang allergies.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>bahong biyudo</t>
+          <t>mag-ihaw og lata</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>adunay kusog nga baho nga musky o balsam</t>
+          <t>sa pagluto sa mga pagkaon nga tinago</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['bahong']</t>
+          <t>['mag-ihaw']</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ang mga gamit sa balay nga wala gipanumbaling kay bahong biyudo.</t>
+          <t>Ang mga estudyante kasagaran mag-ihaw og lata kung nagtipid.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Si Tatay Juan, nga usa ka biyudo, dili na makasabot sa bahong biyudo nga naggikan sa iyang mga sinina.</t>
+          <t>Si Lito nag-andam og dapog aron mag-ihaw og lata para sa ilang campfire na aktibidad.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>gigukod sa plansa</t>
+          <t>kang kinsa man na imong sala</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
+          <t>gigamit sa pagsulti sa usa ka tawo nga sila lamang ang may sala sa ilang kaugalingon alang sa ilang kaugalingong mga problema</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['gigukod']</t>
+          <t>['sala']</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Si Maria gigukod sa plansa, bisan unsa nga okasyon, dili gyud magplantsa.</t>
+          <t>Kang kinsa man na imong sala nga gipaninguha nimo?</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ang iring gigukod sa plansa kay nagdula sila sa kusina.</t>
+          <t>"Nagpangutana si Maria, 'Kang kinsa man na imong sala nga nasudlan?' kay wala siya nakasabot sa istorya."</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>pangatulig luwag</t>
+          <t>dugay pay manguros</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+          <t>usa ka piraso sa cake</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['manguros']</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ang iyang giingon kay murag pangatulig luwag, dili ko kasabot.</t>
+          <t>Si Juan dugay pay manguros kung magtrabaho sa opisina.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nag-uban mi sa kusina, ug gi-pangatulig luwag nako ang sinugba aron dili masunog.</t>
+          <t>Buntag pa sa simbahan, dugay pay manguros ang mga tawo nga nagtipon sa una nga misa.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ninja ray mopatay ninjo</t>
+          <t>makakutaw og utok</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>usa ka pulong nga nag-aplay sa Leyte ug Boholano nga mga dialekto sa Cebuano</t>
+          <t>makapalibog</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['mopatay']</t>
+          <t>['makakutaw']</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ayaw mo pag-away, ninja ray mopatay ninjo nga wala'y saba.</t>
+          <t>Si Maria nagreklamo kay ang instructions makakutaw og utok.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ang mga bata sa kalye nagdula og ninja-ninja, ug ingon sa usa "Ninja ray mopatay ninjo sa atong kalaban hantod sa maoy kahadlok!"</t>
+          <t>Si Maria nagdagan palibot sa lamisa nga makakutaw og utok.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tunga</t>
+          <t>giluto sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>katunga</t>
+          <t>sa pag-ukit sa kaugalingong lubnganan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['tunga']</t>
+          <t>['giluto']</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ang mga magtiayon nagbahin sa ilang mga responsibilidad sa tunga.</t>
+          <t>Ang mga tawo nga magbuhat ug dautan kasagaran giluto sa kaugalingong mantika.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>"Pag-utong naku sa akong sandwich, akong gitunga kini aron makakaon mi duha."</t>
+          <t>Gihikay nila ang baboy sa pista ug giluto sa kaugalingong mantika.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>gadalag ulan</t>
+          <t>awas og palad</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>usa ka lalaki nga homoseksual</t>
+          <t>• awasan og palad</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['awas']</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Si Pedro gadalag ulan, bisan unsa pa nga sitwasyon.</t>
+          <t>Ang mga awas og palad kasagaran maglisod sa kinabuhi kay dili kabalo magtipid.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ang ulap gadalag ulan karong adlawa, maong magdala ko og payong.</t>
+          <t>Miuyog ko sa akong ulo nga dali ra kaayo nga awas ang palad sa baso.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>binatilay</t>
+          <t>magtumba og baka</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>sa pag-aghat sa usag usa sa mga penis</t>
+          <t>sa pag-ihaw sa usa ka vaca</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['binatilay']</t>
+          <t>['magtumba']</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ang binatilay nga mga tawo kay kasagaran mag-uban-uban sa ilang mga barkada.</t>
+          <t>Si Maria nalipay kay magtumba og baka ang iyang pamilya para sa pasko.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sa tradisyonal nga ritwal, ang binatilay gihimo isip bahin sa pagpasidungog sa ilang kaugalingong kultura.</t>
+          <t>Ang mga trabahador sa uma magtumba og baka karong buntaga para sa karneng iprutos.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>kalas og bugo</t>
+          <t>ang masuya madeads</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>usa ka pulong nga gigamit sa pagsulti sa usa ka tawo nga siya nagkinahanglan og dugay kaayo aron masabtan kon unsay gipamulong</t>
+          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['kalas']</t>
+          <t>['masuya']</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ang pagsunod-sunod nimo niya, kalas og bugo ra.</t>
+          <t>Ayaw suya-suya kay ang masuya madeads.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gikuhan siya og tubig aron ipaagi sa kalas og bugo nga alkantarilya.</t>
+          <t>Ang masuya madeads tungod kay nasuya siya sa bag-ong kotse sa iyang silingan ug naghinanok, naapsan siya sa sakuna.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>paabang</t>
+          <t>hunaw</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>pag-abang</t>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['hunaw']</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Gipahimutang ang iyang balay aron ipaabang sa mga bakasyonista.</t>
+          <t>Si Juan naghunaw sa iyang responsibilidad sa trabaho.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nagpaabang sila og mga bisekleta alang sa mga bisita sa park.</t>
+          <t>Si Maria naghunaw sa iyang mga kamot human sa pagkaon.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>buak ang pakwan</t>
+          <t>bunal</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>aron sa pag-abli sa cherry</t>
+          <t>ang tungkod nga gigamit sa pag-atake o pag-bully sa usa ka hayop o tawo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bunal']</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Si Ana naghulat nga buak ang pakwan sa iyang first night sa kasal.</t>
+          <t>Ang mga bunal sa mga dula sa elementarya kay kasagaran gihimo ug kahoy.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Nangita ug kutsilyo si Pedro kay gusto niyang buak ang pakwan para sa meryenda.</t>
+          <t>Ang bunal nga gigamit sa mag-uuma kay gahi ug kahoy aron dili dali maguba.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kuwang sa tagad</t>
+          <t>kalas og bugo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+          <t>usa ka pulong nga gigamit sa pagsulti sa usa ka tawo nga siya nagkinahanglan og dugay kaayo aron masabtan kon unsay gipamulong</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['tagad']</t>
+          <t>['kalas']</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Si Pedro kuwang sa tagad, bisan unsa nga event ganahan magpakita.</t>
+          <t>Ayaw pag-kalas og bugo, kay sayang lang ang imong panahon.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ang tanom nga wa matagda, nagpakita og mga sintomas nga kuwang sa tagad sama sa mga dili hapsay nga dahon.</t>
+          <t>Naglimpyo ko sa sala, unya kalas og bugo ang akong giusik kay naguba dayon ang dustpan.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>hunaw</t>
+          <t>makabugto og panty</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+          <t>pisikal o seksuwal nga madanihon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>['hunaw']</t>
+          <t>['makabugto']</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Si Pedro naghunaw sa iyang mga sayop kay dili siya gusto ma-blame.</t>
+          <t>Ang artista nga iyang nakita sa sine makabugto og panty gyud.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Si Maria mihunaw sa iyang mga kamot human siya nag-ani sa gulay.</t>
+          <t>Ang hilo sa iyang bag-ong panty nipis ra kaayo nga dili kalikayan nga makabugto og panty kung mabira.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tuslok baki</t>
+          <t>bahong biyudo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>usa ka dula</t>
+          <t>adunay kusog nga baho nga musky o balsam</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>['tuslok']</t>
+          <t>['bahong']</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ang mga bata nagpraktis sa tuslok baki aron mahimong champion sa dula.</t>
+          <t>Ang mga gamit sa balay nga wala gipanumbaling kay bahong biyudo.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>"Nakit-an nako si Lito nga nagkuha og sungkod aron magtuslok baki sa daplin sa sapa."</t>
+          <t>Si Tatay Juan, nga usa ka biyudo, dili na makasabot sa bahong biyudo nga naggikan sa iyang mga sinina.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>minyo og lawas</t>
+          <t>abot sa dunggan ang ngisi</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nga adunay lawas sa amahan</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['abot', 'dunggan', 'ngisi']</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Si Ana minyo og lawas tungod sa iyang pagka-busy sa trabaho ug pamilya.</t>
+          <t>Sa dihang gihatagan siya ug award, abot sa dunggan ang ngisi ni Carla.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ang bata nagdula sa buhangin ug nakapangayo sa iyang amahan og mga sungkod aron makabuhat og minyo og lawas nga kahoy.</t>
+          <t>Nagkatawa kaayo ang bata nga abot sa dunggan ang ngisi niya.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>miulbo ang kaspa</t>
+          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>sa pag-abli ngadto sa kasuko</t>
+          <t>gigamit nga isulti sa usa ka tawo nga imong gilimbongan sila sa pagtan-aw sa usa ka piho nga direksyon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['kitkit', 'kitkit', 'bungi']</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Si Pedro miulbo ang kaspa human naay nakig-away niya.</t>
+          <t>paglingi, kitkit bungi.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nagpalit si Ana ug bag-ong shampoo kay miulbo ang kaspa sa iyang ulo.</t>
+          <t>Sa paghigda sa ilang balay, si Lito nakadungog ug sulti ni Jayjay nga "pagtan-aw, kitkit langaw; paglingi, kitkit bungi," ug nakatawa sila kay nasakpan tuod nga adunay langaw ug asong bungi sa may bintana.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>dili na mabalik ang baha paingon sa bukid</t>
+          <t>kulang sa tagad</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['tagad']</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ang mga tawo giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na.</t>
+          <t>Ang mga tawo nga kulang sa tagad kasagaran magbuhat ug dautan para makuha ang attention sa uban.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pag-abot sa panahon sa tig-ulan, diha ra jud sa patag magtapok ang tubig kay dili na mabalik ang baha paingon sa bukid.</t>
+          <t>Ang bata kulang sa tagad kay wala siya gitagad sa mga tigulang samtang nagdula siya sa plasa.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>batil</t>
+          <t>ander da bunal</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Usa ka matang sa tradisyonal nga sakayan sa pagsakay nga gigamit sa Dagat sa Arabia</t>
+          <t>gi-squeeze</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>['batil']</t>
+          <t>['bunal']</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ang mga libro sa kasaysayan naghisgot bahin sa mga batil nga nagsuroy sa laing-laing lugar.</t>
+          <t>Ang ander da bunal nga bana kay kasagaran magpaubos ug musunod sa asawa.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gibatil nako ang akong sinina human ko manglaba.</t>
+          <t>Si Lucas kay nagu-ander da bunal nga duwa, diin ang mga bata nagbungkag ug mga bulingon nga kahoy gamit ang bunal.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kakha tuka</t>
+          <t>hangyo lubo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>kamot-sa-lubong</t>
+          <t>usa ka hangyo nga gihimo sa ingon nga paagi nga dili kini makalikay</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['kakha', 'tuka']</t>
+          <t>['hangyo', 'lubo']</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Si Juan pirmi lang kakha tuka, walay nahabilin nga budget.</t>
+          <t>Si Maria hangyo lubo, maong walay makatanggi sa iyang mga pangutana.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ang maya nagkakha tuka sa nataran.</t>
+          <t>Ang hangyo lubo ni Juan kay ang pagbahin sa iyang mga kalubian sa iyang mga silingan human sa bagyong miagi.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>makabuhi og patay</t>
+          <t>walay mahay nga gauna</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>usa ka makapatikod nga bakak o sugilanon</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['makabuhi', 'patay']</t>
+          <t>['mahay']</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Si Pedro makabuhi og patay sa iyang mga jokes.</t>
+          <t>Ang mga estudyante giingnan nga walay mahay nga gauna, mao nga magtuon sila pag-ayo.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ang makalilisang nga gahum sa maayong pagkahibalo makabuhi og patay nga lawas sa kadlawon.</t>
+          <t>Walay mahay nga gauna, mao nga si Ana karon nagbangutan tungod kay nawala ang iyang wallet.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>lunod patay</t>
+          <t>gigukod sa plansa</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>dihard</t>
+          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['lunod', 'patay']</t>
+          <t>['gigukod']</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Si Pedro lunod patay sa iyang prinsipyo, dili gyud magbag-o.</t>
+          <t>Ang mga tawo nga gigukod sa plansa kasagaran dili mag-atiman sa ilang kaugalingon.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ang biktima nakit-an nga lunod patay sa dagat human sa kusog nga bagyo.</t>
+          <t>Ganiha buntag, nagdali ko ug gamay, maong ang akong kamiseta gigukod sa plansa aron mawala ang tupi.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>mangnukos</t>
+          <t>murag gitilapan og iring</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>sa pag-abli sa usa ka pista</t>
+          <t>walay sapayan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['mangnukos']</t>
+          <t>['gitilapan']</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Si Pedro mangnukos sa mga events nga walay imbitasyon.</t>
+          <t>"Ang iyang mga gamit sa opisina murag gitilapan og iring, limpyo ug hapsay."</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ang iring nilayat sa atop ug nagmangnukos sa ilaga nga misud sa balay.</t>
+          <t>"Pagkakita nako sa lamisa, murag gitilapan og iring kay walay tanang bahaw nga niwangig."</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>manira sa dalan</t>
+          <t>makabugto og bra</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>aron magpabilin nga magmata hangtod sa gabii</t>
+          <t>pisikal o seksuwal nga madanihon</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['makabugto']</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>"Manira sa dalan imong mga plano, walay padulngan."</t>
+          <t>Si Juan ganahan kaayo sa iyang uyab kay makabugto og bra.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ang mga bata nagduwa ug manira sa dalan gamit ang ilang mga ligid nga sakyanan.</t>
+          <t>"Ayoa pag-atiman sa imong sinina kay basin makabugto og bra ang lig-ag sa washing machine."</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>abot sa dalunggan ang ngisi</t>
+          <t>gigukod sa plansa</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nga dili gayod malipay</t>
+          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['abot', 'dalunggan', 'ngisi']</t>
+          <t>['gigukod']</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ang bata, abot sa dalunggan ang ngisi sa dihang gihatagan ug dako nga regalo.</t>
+          <t>Si Pedro pirmi lang gigukod sa plansa, bisan unsa nga sinina dili mahimutang.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ang babaye, abot sa dalunggan ang ngisi tungod sa iyang katawa.</t>
+          <t>Ang shirt ni Juan gigukod sa plansa human gilabhan.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>walay mahay nga gauna</t>
+          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>['mahay']</t>
+          <t>['lingaw', 'dakpa']</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Si Ana nakasabot nga walay mahay nga gauna, mao nga nagbantay siya sa iyang mga desisyon.</t>
+          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, basi malingaw ka.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nagtingala si Juan kung ngano nga magbuot-buot si Pedro nga mobiyahe nga walay mahay nga gauna ug wala pa man gani siya nakahibalo sa tanan nga mga detalye.</t>
+          <t>Nagduwa ang mga bata og palumba sa iskina ug miingon si Juan, "Kung wala kay lingaw sa kinabuhi, dakpa akong utot, paglingaw-lingaw lang."</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>mag-ihaw og lata</t>
+          <t>pasok, Luningning</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>sa pagluto sa mga pagkaon nga tinago</t>
+          <t>miingon sa kaugalingon sa dihang pag-poking sa usa sa iyang mga winnings sa usa ka dula sa mga kard</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>['mag-ihaw']</t>
+          <t>['pasok']</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Si Pedro mag-ihaw og lata kung walay luto nga pagkaon.</t>
+          <t>Pasok, Luningning, kay daghan pa ta ug buhaton.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Si Juan mag-ihaw og lata nga naay sulod nga mais para sa iyang proyekto sa arte.</t>
+          <t>Nangabli si Luningning sa pultahan ug giingnan siya sa iyang mama, "Pasok, Luningning, kay ulan kaayo sa gawas."</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kulang sa dukol</t>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>usa ka buangbuang nga tawo</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>['dukol']</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ang iyang anak kulang sa dukol, dili gyud magtinarong sa pag-eskwela.</t>
+          <t>Si Juan nasayod nga dili na mabalik ang baha paingon sa bukid, mao nga nagpadayon na siya.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ang bata kulang sa dukol, mao nga giingnan siya sa iyang ginikanan nga magmatngon sa sunod nga dulaan.</t>
+          <t>Ang mga lumulupyo sa baryo nahibulong kay dili na mabalik ang baha paingon sa bukid bisan sa kusog nga ulan.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kakha tuka</t>
+          <t>nakalugsong</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>kamot-sa-lubong</t>
+          <t>sa pag-adto gikan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['kakha', 'tuka']</t>
+          <t>['nakalugsong']</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Si Maria nagkinabuhi nga kakha tuka, walay nahabilin nga kwarta.</t>
+          <t>Nakalugsong na mi ug gidalit ang among mga ani sa lungsod.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ang mga langgam nagkakahituka sa mga sagbotan sa umahan.</t>
+          <t>Naglakaw mi sa bukid ug nakalugsong mi ngadto sa suba para maligo.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>basa og baba</t>
+          <t>lamoy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>mabangis</t>
+          <t>pag-abot</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>['baba']</t>
+          <t>['lamoy']</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga basa og baba kasagaran dili ganahan makakita sa mga tahimik nga tao.</t>
+          <t>"Lamoya nalang na imong gibuhat, walay gamit."</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nagbasaan sa iyang baba si Juan samtang nag-inom ug tubig.</t>
+          <t>"Gi-lamoy sa bata ang dakong pan nakon."</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bato og kasingkasing</t>
+          <t>bahong biyudo</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>dili-makalolooy</t>
+          <t>adunay kusog nga baho nga musky o balsam</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>['bato']</t>
+          <t>['bahong']</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Si Pedro bato og kasingkasing, dili gyud siya malumo bisan sa mga bata.</t>
+          <t>Ang iyang sinina nga bahong biyudo kay dili nimo malapasan.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ang mga duwende nakakita og bato og kasingkasing sa tunga sa lasang ug naglibog sila unsaon kini nahimong ingon ana ang porma.</t>
+          <t>Nahibulong mi ngano'ng bahong biyudo siya apan wala diay siya'y asawa nga namatay.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
+          <t>giprito sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Mahimo nimong pagdala ang kabayo ngadto sa tubig</t>
+          <t>Alternatibo nga porma sa giluto sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>['madala', 'mainom']</t>
+          <t>['giprito']</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga dili magpaningkamot dili gyud magmalampuson, madala nimo ang baka sa suba apan dili nimo mainom.</t>
+          <t>Si Juan giprito sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Naglakaw mi sa uma ug among gisulayan nga madala nimo ang baka sa suba apan dili nimo mainom tungod ky dili siya mahaylo ug duol biskan unsang buhata.</t>
+          <t>Nagluto si Maria ug isda nga giprito sa kaugalingong mantika aron mas lami ang timpla.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
+          <t>agi sa bangag sa dagom</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
+          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>['lingaw', 'dakpa']</t>
+          <t>['agi', 'bangag']</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, aron malingaw ka sa kinabuhi.</t>
+          <t>Ang ilang proyekto agi sa bangag sa dagom sa kalisod.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pagmata nako sa buntag, nangutana akong igsoon kung unsa'y akong buhaton. Gisulti nako siya nga, "Kung wala kay lingaw sa kinabuhi, dakpa akong utot," kay lingaw man siya mangdakop.</t>
+          <t>Ipasulod ni Maria ang sinulid agi sa bangag sa dagom aron makatahi siya og sinina.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>gwapo kon magtalikod</t>
+          <t>murag namatyag iring</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
+          <t>gigamit sa paghulagway sa usa ka tawo nga nagtangis nga nagtangis o nagtangis nga nagtangis</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['magtalikod']</t>
+          <t>['namatyag']</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ang mga tao nga gwapo kon magtalikod kasagaran dili magdugay sa ilang relasyon.</t>
+          <t>"Ang bata murag namatyag iring, hilak kaayo pagnalaya."</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Si Juan gwapo kon magtalikod, kay nindot ug porma ang iyang buhok ug likod.</t>
+          <t>Ang iring sa atop murag namatyag iring, kusog kaayo ang pangubog.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>murag namiya og tai</t>
+          <t>sabong</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Usa ka tawo nga mibiya sa dili-iasa nga walay iyang pulong</t>
+          <t>usa ka kompetisyon</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['sabong']</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>"Ang silingan murag namiya og tai, kalit lang wala."</t>
+          <t>Ang mga manok nga ipangsabong kay gipangandaman ug maayo.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ang bata nagdali sa pagdagan kay murag namiya og tai sa kasilyas.</t>
+          <t>Ang akong amahan mopalit og sabon sa merkado kay nahutdan na mi sa among balay.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mag-ugbok og mohon</t>
+          <t>manira sa dalan</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>sa pagpakigsekso</t>
+          <t>aron magpabilin nga magmata hangtod sa gabii</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>['mag-ugbok']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Si Maria ug ang iyang bana mag-ugbok og mohon sa ilang balay.</t>
+          <t>"Ayaw pag manira sa dalan, naa pa kay buhaton."</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ang mga trabahante mag-ugbok og mohon aron masugdan na ang pagtukod sa bag-ong balay.</t>
+          <t>Ang mga tindahan manira sa dalan matag alas-otso sa gabi-i.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>dula og panit</t>
+          <t>kulang sa dukol</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>sa pag- masturba</t>
+          <t>usa ka buangbuang nga tawo</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['dula']</t>
+          <t>['dukol']</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Ang iyang barkada kay dula og panit, bisan unsa na lang nga kalipay ang gihimo.</t>
+          <t>Si Maria kulang sa dukol, pirmi lang magbulakbol.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ang bata nagdula og panit sa daplin sa suba, gamit ang tanom nga iya nakuha gikan sa palibot.</t>
+          <t>Ang bata kulang sa dukol sa iyang likod kay nagtambay ra sa duyan.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>dili makaon og iro</t>
+          <t>miulbo ang kaspa</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>makalilisang</t>
+          <t>sa pag-abli ngadto sa kasuko</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>['makaon']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga dili makaon og iro kasagaran walay respeto sa uban.</t>
+          <t>Si Ana miulbo ang kaspa human nabal-an nga gilimbongan siya.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>"Ang among silingan dili makaon og iro kay nagaalaga ra siya og iring."</t>
+          <t>Human sa dugang duha ka adlaw nga walay ligo, si Pedro nakabantay nga miulbo ang kaspa sa iyang ulo.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kulang sa tagad</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>['tagad']</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Si Juan kulang sa tagad, pirmi lang magpasikat sa mga tao.</t>
+          <t>Ayaw na lang pagsabot ana, ipanabi na sa clouds.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ang bata gibati nga siya kulang sa tagad sa ilang panimalay kay busy kaayo ang iyang ginikanan.</t>
+          <t>Pagka-adlaw nga hayag, naglingkod si Maria sa atop ug gusto niyang pasundayag sa iyang gibati, busa iyang giingon sa iyang kaugalingon, "Ipanabi na sa clouds ang akong kalipay."</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>manira sa dalan</t>
+          <t>lapos sa pikas dunggan</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>aron magpabilin nga magmata hangtod sa gabii</t>
+          <t>sa pagsulod sa usa ka dalunggan ug paggawas sa laing dalunggan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['lapos', 'dunggan']</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ang iyang barkada manira sa dalan hangtud sa kaadlawon.</t>
+          <t>Ang tambag sa iyang ginikanan lapos ra sa pikas dunggan.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ang mga tindero manira sa dalan kada oras alas-sais sa buntag matud sa balaod sa syudad.</t>
+          <t>Nakita namo ang gamay nga sungo nga giigo sa bala, naglapos gyud sa pikas dunggan.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>makabugto og panty</t>
+          <t>habwa ang kinaon</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>pisikal o seksuwal nga madanihon</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>['makabugto']</t>
+          <t>['habwa', 'kinaon']</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Si Ana makabugto og panty sa iyang pagka-sexy.</t>
+          <t>Si Pedro naghabwa ang kinaon kay nasuka.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Nagkatawa ang mga bata og kusog nga nahugaw ang ilang duwaan nga makabugto og panty sa kalit.</t>
+          <t>Naglimpyo si Maria sa kusina ug iyang gihabwa ang kinaon sa lamisa human sa ilang paniudto.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>sabong</t>
+          <t>bibingkang liki</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>usa ka kompetisyon</t>
+          <t>ang mga genital sa babaye</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>['sabong']</t>
+          <t>['liki']</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ang sabong sa mga manok kay paborito nga pastime sa mga kalalakin-an.</t>
+          <t>Si Pedro nagpakatawa sa mga barkada gamit ang bibingkang liki nga istorya.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nagbutang kog tubig ug sabong sa palanggana para sa laba.</t>
+          <t>Nag-andam si Lola Maria og bibingkang liki alang sa Pasko.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>manglutasay</t>
+          <t>ander de bunal</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>usa ka manunulak sa mga bukog</t>
+          <t>gi-squeeze</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>['manglutasay']</t>
+          <t>['bunal']</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi manglutasay ug uyab nga mga batan-on.</t>
+          <t>Ang mga ander de bunal kay dili na maghunahuna sa ilang kaugalingong gusto.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ang mga bata nagdula sa suba ug naay pipila sa ilaha nga nagmanglutasay ug mga lamas sa kilid.</t>
+          <t>Si Andres kay nanghita og bunal ug gahapon gi-install niya ang iyang ander de bunal sa likod sa balay.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>bag-ong haon</t>
+          <t>baba sa atay</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>bag-o nga gihimo</t>
+          <t>ang diaphragm</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>['bag-ong', 'haon']</t>
+          <t>['baba']</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ang bag-ong haon nga balay ni Maria kay puno sa modernong mga kagamitan.</t>
+          <t>Ang mga tambal para sa baba sa atay kay kinahanglan sa pag-maintain sa maayong kondisyon.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Naghuot ang kusina tungod sa bag-ong haon nga nilung-ag nga kan-on.</t>
+          <t>"Pagkalami gyud sa adobo nga akong giandam, labi na ang baba sa atay nga humok ug lami."</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>istorya ilalom sa dagat</t>
+          <t>molayag sa kalipay</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Usa ka dakong basura</t>
+          <t>sa pagpakigsekso</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['molayag']</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Si Juan naglagot kay ang nadungog niya puro istorya ilalom sa dagat.</t>
+          <t>Ang mga magkauban nagmolayag sa kalipay sa ilang outing sa beach.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ang mga mananagat nakadungog og istorya ilalom sa dagat mahitungod sa nawagtang nga barko nga panalipdan sa mga sirena.</t>
+          <t>Ang mga langgam nagmolayag sa kalipay sa kataas-kataas nga kahoy.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>gwapa kon magtalikod</t>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>['magtalikod']</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi lang magbuot-buot ug sulti nga gwapa kon magtalikod.</t>
+          <t>Ang mga estudyante nakabalo nga dili na mabalik ang baha paingon sa bukid, mao nga nagplano na sila pag-ayo.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Naglingaw-lingaw mi ug lakaw sa mall ug nakakita ko ug usa ka babaye nga gwapa kon magtalikod kay maayong pagka-ayo ang iyang tindog.</t>
+          <t>Pagkahuman sa kusog nga ulan, ang mga taga-barangay nag-istorya nga bisan unsaon pa, dili na mabalik ang baha paingon sa bukid, kay daghan kaayo ang tubig nga midiretso sa dagat.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
+          <t>lamoy</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>kitang tanan magkamali</t>
+          <t>pag-abot</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>['naay', 'masipyat']</t>
+          <t>['lamoy']</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Ang iyang amigo nakalimot sa meeting, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+          <t>"Si Ana, sige lang lamoy walay klaro."</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ang kabaw na naglakaw sa uma nadakdak ug kalit kay bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+          <t>"Ang bata malipayon nga naglamoy sa iyang paborito nga tsokolate."</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>mura og halas nga nagluno</t>
+          <t>kirig</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga magbiya sa iyang mahugaw nga sinina sa tanang dapit sa balay</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>['nagluno']</t>
+          <t>['kirig']</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>"Ang kwarto sa bata mura og halas nga nagluno, walay nasunod nga kalimpyo."</t>
+          <t>Si Juan kirig sa kahadlok pagkakita sa aksidente.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>"Tungod sa kainit sa adlaw, makit-an nimo ang halas nga nagluno sa daplin sa sapa."</t>
+          <t>Si Maria kirig samtang gidalikyat siya sa ospital tungod sa iyang sakit.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>miulbo ang kaspa</t>
+          <t>duwa og panit</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>sa pag-abli ngadto sa kasuko</t>
+          <t>sa pag- masturba</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['duwa']</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ang iyang boss miulbo ang kaspa tungod sa sayop nga trabaho.</t>
+          <t>Ang iyang mga kauban sa trabaho pirmi lang magbinuang ug magduwa og panit.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ang iyang kaspa miulbo pagpag sa paglimpyo niya sa iyang buhok.</t>
+          <t>Ang mga bata nangita og bola aron makaduwa og panit sa basketball court.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>gadalag ulan</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>usa ka lalaki nga homoseksual</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Si Juan kay gadalag ulan, maong daghan ang naglikay niya.</t>
+          <t>Kung gusto ka maabot ang imong damgo, ipanabi na sa clouds.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nag-andam si Maria ug payong kay ang langit kay gadalag ulan.</t>
+          <t>"Ang mensahe gikan sa iyang email kay ipanabi na sa clouds para dali ra mag-access bisan asa."</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ang masuya madeads</t>
+          <t>babayeng ikogan</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
+          <t>transgender</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>['masuya']</t>
+          <t>['ikogan']</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Ayaw suya-suya kay ang masuya madeads.</t>
+          <t>Si Ana nga babayeng ikogan kay walay klaro nga direksyon sa kinabuhi.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ang masuya madeads tungod kay nasuya siya sa bag-ong kotse sa iyang silingan ug naghinanok, naapsan siya sa sakuna.</t>
+          <t>Ang babayeng ikogan sa sirkus mao'y nagdala og daghang tawo kay talagsaon siya.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>gigukod sa plansa</t>
+          <t>manira sa dalan</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
+          <t>aron magpabilin nga magmata hangtod sa gabii</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>['gigukod']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga gigukod sa plansa kasagaran dili mag-atiman sa ilang kaugalingon.</t>
+          <t>Ang mga batan-on kasagaran manira sa dalan kung walay lingaw.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ganiha buntag, nagdali ko ug gamay, maong ang akong kamiseta gigukod sa plansa aron mawala ang tupi.</t>
+          <t>Ang tindero manira sa dalan kung udto kay init na kaayo.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kapugngan pa ang baha, dili ang biga</t>
+          <t>mura og halas nga nagluno</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>dili mapugngan</t>
+          <t>ang usa ka tawo nga magbiya sa iyang mahugaw nga sinina sa tanang dapit sa balay</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['nagluno']</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Si Maria adunay dakong pangandoy nga dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
+          <t>"Ang silingan namo mura og halas nga nagluno, walay tarong pagbutang sa mga gamit."</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pag-abot sa kusog nga ulan, kapugngan pa ang baha, dili ang biga sa yuta nga grabe kaayo ang pag-inilog ug pag-atake.</t>
+          <t>Ang among iring gibantayan kaayo ang halas nga nagluno sa halang nga sagbot sa among jardin.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>gadalag uwan</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>usa ka lalaki nga homoseksual</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Si Maria gadalag uwan, pero walay mopauli sa iyang pagkatawo.</t>
+          <t>Ipanabi na sa clouds ang imong mga tinguha ug siguroha nga mo-trabaho ka para ana.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ang madan-ag nga panganod sa langit gadalag uwan nga naghatag og lapad nga ngitngit nga pangandoy sa mga uma.</t>
+          <t>Nakita nako ang bata nga naglingkod sa atop sanglit gilabay niya ang iyang mensahe ug ipanabi na sa clouds.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kinsa man na imong sala</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa ka tawo nga sila lamang ang may sala sa ilang kaugalingon alang sa ilang kaugalingong mga problema</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>['sala']</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Kinsa man na imong sala nga naghulat sa gawas?</t>
+          <t>Bisan unsa ka lisod, ipanabi na sa clouds ang imong mga pag-ampo.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>"Sa interogasyon, gipangutana siya sa pulis, 'Kinsa man na imong sala nga imong giangkon?'"</t>
+          <t>Pagka gabii, among ipanabi na sa clouds ang among mga mensahe pinaagi sa drone nga adunay mga light display.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mogawas ang pari nga walay ulo</t>
+          <t>dula og panit</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
+          <t>sa pag- masturba</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>['mogawas']</t>
+          <t>['dula']</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sa dihang mag-istorya sila og mga horror stories, mogawas ang pari nga walay ulo ang giingon.</t>
+          <t>Si Juan dula og panit, pirmi lang magtambay ug magbuot-buot.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Pag-abli sa karaang simbahan sa kagabhion, nakurat sila kay tinuod nga mogawas ang pari nga walay ulo sa altar.</t>
+          <t>Si Ana migamit og kutsilyo aron dulaon ang panit sa mansanas.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>hilawas</t>
+          <t>anak sa sala</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>coitus</t>
+          <t>usa ka anak nga dili-konsejero</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['sala']</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ang hilawas nga binuhatan kay kasagaran nagdala ug problema sa kinabuhi.</t>
+          <t>Ang anak sa sala kasagaran maglisod sa pagsulod sa mga respetadong institusyon.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ang hilawas sa lami nga prutas kay makapabulahan sa lawas.</t>
+          <t>Nagbisita ang pari sa balay ug giampo ang anak sa sala nga nakabaton og sakit.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>mabaw og kibot</t>
+          <t>lapos sa pikas dunggan</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>dali nga madaot</t>
+          <t>sa pagsulod sa usa ka dalunggan ug paggawas sa laing dalunggan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>['kibot']</t>
+          <t>['lapos', 'dunggan']</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Si Ana mabaw og kibot, dali ra kaayo masuko.</t>
+          <t>Si Pedro pirmi lang lapos sa pikas dunggan ang mga lectures sa eskwela.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Si Lito mabaw og kibot, dali ra kaayo siya makurat basta naay kalit nga buto.</t>
+          <t>Si Juan nagkagubot ang buhok kay naay langaw nga misulod sa iyang dunggan ug nilapos sa pikas dunggan.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
+          <t>kakha tuka</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>kitang tanan magkamali</t>
+          <t>kamot-sa-lubong</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>['naay', 'masipyat']</t>
+          <t>['kakha', 'tuka']</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Si Maria nasipyat sa pagplano, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+          <t>Si Juan pirmi lang kakha tuka, walay nahabilin nga budget.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ang kabaw nga naay upat ka tiil masipyat sa pagtabok sa pilapila ug nakasulod kini sa umahan.</t>
+          <t>Ang maya nagkakha tuka sa nataran.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>hinaw</t>
+          <t>abot sa dalunggan ang ngisi</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>['hinaw']</t>
+          <t>['abot', 'dalunggan', 'ngisi']</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Si Juan naghinaw sa iyang sala sa trabaho.</t>
+          <t>Pagkahuman sa eksam, abot sa dalunggan ang ngisi ni Juan kay nakapasar siya.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Naghinaw si Maria sa iyang mga kamot human sa pagtrabaho sa garden.</t>
+          <t>Nagtan-aw ko sa litrato nga gipakita ni Ana, abot sa dalunggan ang ngisi niya sa kalipay.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>kuskos-balungos</t>
+          <t>ul-ol</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>alternatibong pagsulat sa kuskos balungos</t>
+          <t>sa pag- masturba Mga sinonim: batil</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ul-ol']</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Si Ana pirmi lang kuskos-balungos kung naay buhaton nga dili siya ganahan.</t>
+          <t>Ang iyang mga ul-ol nga istorya kay naghatag ug kalibog sa tanan.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Gikuha ni Maria ang kutsilyo ug gigamit kini alang sa kuskos-balungos sa kinay sa isda.</t>
+          <t>Juan miingon nga siya gikapoy human siya mag-ul-ol sulod sa iyang kwarto.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>makamala og sapa</t>
+          <t>mangayo og manghod</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga may dagkong tiil</t>
+          <t>usa ka kaso sa bata nga nag-asuso o nag-agom sa iyang mga tudlo</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>['makamala']</t>
+          <t>['mangayo']</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ang iyang amigo makamala og sapa tungod sa kadako sa tiil.</t>
+          <t>Ang mga bata nga mangayo og manghod kasagaran mga healthy nga bata.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ang mag-uuma makamala og sapa kay aron makuha ang mga kahoy nga natumba.</t>
+          <t>Ang magtiayon midesisyon nga mangayo og manghod kay gusto nila dungagan ang ilang pamilya.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>gadalag uwan</t>
+          <t>duwa og panit</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>usa ka lalaki nga homoseksual</t>
+          <t>sa pag- masturba</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['duwa']</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Ang iyang silingan gadalag uwan, pero respetado gihapon sa ilang lugar.</t>
+          <t>Si Maria naglagot kay si Juan pirmi lang magduwa og panit bisan kinahanglanon siya.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Naglakaw kami sa kalsada ug nakita namo nga ang bata gadalag uwan aron dili mabasa sa kalit nga pag-abot sa ulan.</t>
+          <t>Nagpraktis ang mga bata nga magduwa og panit para sa ilang teatro sa eskuwela.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>basa ang tingog</t>
+          <t>hilawas</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>dili-matud-an sa tingog</t>
+          <t>coitus</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>['tingog']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Si Pedro basa ang tingog tungod sa iyang sip-on.</t>
+          <t>Ang hilawas nga kinabuhi kay wala'y klaro nga padulngan.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Uwanon kaayo karon mao nga basa ang tingog sa mga bata nga nagdula sa gawas.</t>
+          <t>"Nagkinahanglan ang bata og hilawas nga panginahanglanon arun maatiman ang iyang kalawasan."</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>higda sa lubi</t>
+          <t>tuslok baki</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>pag-ula</t>
+          <t>usa ka dula</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>['higda']</t>
+          <t>['tuslok']</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ang iyang mga kauban pirmi lang mag-higda sa lubi kung mag-party.</t>
+          <t>Ang mga bata nagpraktis sa tuslok baki aron mahimong champion sa dula.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ang bata nagdula ug higda sa lubi sa baybayon.</t>
+          <t>"Nakit-an nako si Lito nga nagkuha og sungkod aron magtuslok baki sa daplin sa sapa."</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>mangnukos</t>
+          <t>manakop og ligid</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sa pag-abli sa usa ka pista</t>
+          <t>nga ang usa ka tawo naugtang sa usa ka sakyanan</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>['mangnukos']</t>
+          <t>['manakop', 'ligid']</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ang iyang kauban sa trabaho pirmi lang mangnukos sa mga party.</t>
+          <t>Si Pedro manakop og ligid kay nagdagan-dagan sa kalsada.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ang iring nanagan kay gidunggab, ug ang iro mangnukos kaniya mikanaug sa karsada.</t>
+          <t>Nagdula mi og dakop-dakop sa plaza unya nakalingkod ko para mopahuway, apan kalit nga miingon ang akong amigo nga manakop og ligid mi sa mga sakyanan nga nag-agi atubangan sa balay.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>abli ang Gaisano</t>
+          <t>kulang sa dukol</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>nga ang usa nga mosul-ob</t>
+          <t>usa ka buangbuang nga tawo</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['dukol']</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Si Juan wala kabantay nga abli ang Gaisano, maong giingnan siya sa iyang higala.</t>
+          <t>Si Pedro kulang sa dukol, maong pirmi lang magbinuang.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>"Daghan taw sa mall kay abli ang Gaisano karon."</t>
+          <t>Ang bata kulang sa dukol, mao nga ipatuli pa siya karong bulan para sakto ug kompleto.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>gisulod sa bulsa</t>
+          <t>hilawas</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>sa paglimbong</t>
+          <t>coitus</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>['gisulod']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Si Juan gisulod sa bulsa sa iyang kauban, maong nawala ang iyang kwarta.</t>
+          <t>Ang hilawas nga relasyon sa diha nga walay commitment kay lisod.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gisulod ni Ana ang iyang sinsiyo sa bulsa.</t>
+          <t>Nagkinahanglan ko ug hilawas nga pagkaon aron magpabiling lig-on ug himsog ang lawas.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>kuskos-balungos</t>
+          <t>bahong biyuda</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>alternatibong pagsulat sa kuskos balungos</t>
+          <t>adunay kusog nga baho nga musky o balsam</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bahong', 'biyuda']</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga kuskos-balungos kasagaran magpaluya sa ilang mga kauban.</t>
+          <t>Si Juan bahong biyuda kay wala gyud maligo ug maayo.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nagpainit si Lola og tubig aron mag-umpisa sa iyang kuskos-balungos sa kinagamyan sa bata.</t>
+          <t>Ang akong silingan nga si Maria, nga dugay nang biyuda, miingon nga dili siya gusto og bahong biyuda sa iyang sinina.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>makamala og sapa</t>
+          <t>pabuto</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga may dagkong tiil</t>
+          <t>usa ka patok</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>['makamala']</t>
+          <t>['pabuto']</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga dagko ug tiil kasagaran makamala og sapa.</t>
+          <t>Ang mga bata malipay kaayo sa mga pabuto kada New Year.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Ang mga bata nagdula sa daplin sa sapa ug kalit lang nga ang isa kanila makamala og sapa.</t>
+          <t>Nagpalit kami og daghang pabuto para sa pista sa baryo.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>bahong biyuda</t>
+          <t>hilawas</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>adunay kusog nga baho nga musky o balsam</t>
+          <t>coitus</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>['bahong', 'biyuda']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Ang iyang kwarto kay bahong biyuda, wala gyud linisan ug maayo.</t>
+          <t>Ang mga tawo nga maghilawas kay kasagaran mahadlok magcommit.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Siya bayot nga bahong biyuda ug wala na gyud motrabaho sukad namatay ang iyang bana.</t>
+          <t>Ang lami sa hilawas nga prutas kay wala'y sama.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>mamalit og kaso</t>
+          <t>paabang</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>aron mahimong usa ka ambulance chaser</t>
+          <t>pag-abang</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3794,753 +3794,753 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Si Ana mamalit og kaso aron lang magka-datu.</t>
+          <t>Gipahimutang ang iyang balay aron ipaabang sa mga bakasyonista.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Nagplano siya nga mamalit og kaso para sa iyang bag-ong snowboard nga gigamit sa bukid.</t>
+          <t>Nagpaabang sila og mga bisekleta alang sa mga bisita sa park.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>hatod og patay</t>
+          <t>manakop og ligid</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>sa pagtambong sa usa ka paglubong o seremonya sa paghinumdom</t>
+          <t>nga ang usa ka tawo naugtang sa usa ka sakyanan</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>['hatod', 'patay']</t>
+          <t>['manakop', 'ligid']</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga hatod og patay kasagaran nagpakita ug respeto sa namatay.</t>
+          <t>"Manakop og ligid kaayo imong mga plano, walay klaro."</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ang drayber mihangyo nga tabangan siya sa paghatod og patay ngadto sa sementeryo.</t>
+          <t>Si Juan ug iyang mga amigo nagsabot nga manakop og ligid alang sa ilang bag-ong negosyo nga vulcanizing shop.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>walay mahay nga gauna</t>
+          <t>manglutasay</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>usa ka manunulak sa mga bukog</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>['mahay']</t>
+          <t>['manglutasay']</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Si Maria giingnan nga walay mahay nga gauna, mao nga nagmatngon siya sa iyang mga lihok.</t>
+          <t>Ang iyang kauban sa trabaho manglutasay sa mga kabataan.</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sa duwa, si Juan dili mopauli dayon human matandog ang iyang mga pisi, kay walay mahay nga gauna.</t>
+          <t>Ang mga bata nagdula sa ilalom sa manglutasay aron magpa-uyog.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>mabaw og kibot</t>
+          <t>mag-ihaw og lata</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>dali nga madaot</t>
+          <t>sa pagluto sa mga pagkaon nga tinago</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>['kibot']</t>
+          <t>['mag-ihaw']</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Si Pedro mabaw og kibot, pirmi lang magyawyaw kung naay di siya ganahan.</t>
+          <t>Si Juan pirmi lang mag-ihaw og lata sa boarding house.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Niuyog gamay ang lamesa, dayon si Ana mibalikwas ug may kadiyot nga nisiyagit kay mabaw og kibot.</t>
+          <t>Gikuha ni Pedro ang kalaha aron mag-ihaw og lata sa ilang umahan.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>gwapa kon magtalikod</t>
+          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
+          <t>Maglakaw sa paghisgot</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>['magtalikod']</t>
+          <t>['buhat', 'pasulti-on', 'sulti', 'pabuhaton']</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Ang mga tao nga gwapa kon magtalikod kasagaran maulaw kung mag-atubang.</t>
+          <t>Si Pedro nagpakita nga maayo siya sa trabaho, buhat ang pasulti-on dili sulti ang pabuhaton.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>"Si Ana gwapa kon magtalikod kay nindot ug straight ang iyang buhok."</t>
+          <t>Gisuwayan ni Juan nga i-assemble ang kabayo-kabayo nga laruan gamit ang manual, buhat ang pasulti-on dili sulti ang pabuhaton.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>taliba</t>
+          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ang mga genital sa babaye</t>
+          <t>kitang tanan magkamali</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>['taliba']</t>
+          <t>['naay', 'masipyat']</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Ang mga volunteers nag-taliba sa event para malikayan ang mga kagubot.</t>
+          <t>Si Ana nakasala sa iyang trabaho, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ang taliba naglingkod sa tabi sa dalan ug naghulat sa jeepney.</t>
+          <t>Naglakaw-lakaw ang kabaw sa uma, apan bisan ang kabaw nga naay upat ka tiil masipyat, natapilok siya.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ang gaba dili magsaba</t>
+          <t>makamala og sapa</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ang silot tungod sa iyang mga sayop o mga paglapas moabut sa wala damha</t>
+          <t>ang usa ka tawo nga may dagkong tiil</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>['magsaba']</t>
+          <t>['makamala']</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Si Juan nakabalo nga ang iyang gibuhat nga dili maayo mibalik kaniya, ang gaba dili magsaba.</t>
+          <t>Si Maria nagkatawa kay ang iyang igsuon makamala og sapa sa kadako sa tiil.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Pag-abot sa gabii, ang gaba sa bukid dili magsaba samtang naglakaw mi pabalik sa lungsod.</t>
+          <t>Ang mga trabahante nagkinahanglan og kahoy nga makamala og sapa aron makabalhin ang mga gamit ngadto sa pikas nga pampang.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>mag-ihaw og lata</t>
+          <t>pangatulig luwag</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>sa pagluto sa mga pagkaon nga tinago</t>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>['mag-ihaw']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Si Ana pirmi lang mag-ihaw og lata kung walay sud-an.</t>
+          <t>Ang iyang giingon kay murag pangatulig luwag, dili ko kasabot.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nag-andam si Juan og bonfire sa ilang camp, dayon nag-ihaw siya og lata aron makaluto sa sulod niini.</t>
+          <t>Nag-uban mi sa kusina, ug gi-pangatulig luwag nako ang sinugba aron dili masunog.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>toyi</t>
+          <t>halinon og aping</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>coitus</t>
+          <t>maayo kaayo nga hitsura</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>['toyi']</t>
+          <t>['halinon']</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Ang iyang mga joke kay kasagaran tungkol sa toyi.</t>
+          <t>Ang mga artista kasagaran halinon og aping tungod sa ilang hitsura.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ang tigulang nagdala og toyi gikan sa iyang uma.</t>
+          <t>Ang iring namo halinon og aping tungod kay kanunay kini gihapuhap sa among pamilya.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>pangatulig luwag</t>
+          <t>abot na sa dukot</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+          <t>pag-iskrabe sa ubos sa bariles</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['abot', 'dukot']</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>"Si Pedro, sige lang pangatulig luwag walay unod."</t>
+          <t>Ang iyang mga problema murag abot na sa dukot, grabe na kaayo.</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ang anak nagreklamo nga masakit iyang tiyan human panihapon ug giingon sa iyang mama, "Ayaw sigeg kaon kung dili ka ganahan nga magpangatulig luwag."</t>
+          <t>Nagkuha ko og sud-an sa kaldero, pero kinahanglan gyud nga aboton ang dukot aron mahurot ang kan-on.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
+          <t>kuyog baboy</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>gigamit nga isulti sa usa ka tawo nga imong gilimbongan sila sa pagtan-aw sa usa ka piho nga direksyon</t>
+          <t>usa ka tagalong</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>['kitkit', 'kitkit', 'bungi']</t>
+          <t>['kuyog']</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>paglingi, kitkit bungi sa kadaghan sa problema.</t>
+          <t>Ang mga tawo nga kuyog baboy kasagaran magpalisod sa ilang mga kauban.</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Naglingi siya kay gusto niyang makita unsay iyang gipakita, apan pagtuyok, nakita ra diay niyang kitkit langaw ug bungi.</t>
+          <t>Miadto sila sa umahan uban sa ilang kuyog baboy nga gihiktan sa usa ka pisi.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>lunod patay</t>
+          <t>pabuto</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>dihard</t>
+          <t>usa ka patok</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>['lunod', 'patay']</t>
+          <t>['pabuto']</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga lunod patay kasagaran adunay baruganan nga dili matay-og.</t>
+          <t>Ang iyang surprise party kay murag pabuto nga naka-shock sa tanan.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Ang bata naglangoy-langoy sa dagat apan nawad-an og kusog ug hapit na siya lunod patay.</t>
+          <t>Nagpalit mi ug daghang pabuto alang sa selebrasyon sa Bag-ong Tuig.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>awas og palad</t>
+          <t>ang baka nisulod sa kulon</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>• awasan og palad</t>
+          <t>gigamit sa pagsulti sa usa nga siya usa ka bakak o ikaw mahimo sa pagsulti sa laing nagbuwa</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>['awas']</t>
+          <t>['nisulod']</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Ang mga awas og palad kasagaran maglisod sa pagplano sa ilang kaugmaon.</t>
+          <t>Ang ilang proyekto nga walay direksyon mura'g baka nga nisulod sa kulon.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Naglakaw ko sa tapok-tapok sa tubig dayon awas og palad ang akong tinuang tubig gikan sa baso.</t>
+          <t>Ang baka sa among uma nisulod sa dakong kulon sa kusina.</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
+          <t>gidaman</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Mahimo nimong pagdala ang kabayo ngadto sa tubig</t>
+          <t>sa pag-aturog o pag-aturog</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>['madala', 'mainom']</t>
+          <t>['gidaman']</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Si Maria giingnan nga kinahanglan siya mag-uban sa pagpaningkamot, madala nimo ang baka sa suba apan dili nimo mainom.</t>
+          <t>"Gidaman na ba ka? Daghan kaayo kag opinion."</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Si Juan naglisod pagkupot sa baka nga iyang gidala sa suba, apan bisan unsaon niya kini pagpaligo, dili gyud mainom ang tubig.</t>
+          <t>Pagka-buntag, iyang mama miingon nga kagabii, gidaman diay siya ug naglakaw-lakaw sa sulod sa kwarto.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>mura og halas nga nagluno</t>
+          <t>hinaw</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga magbiya sa iyang mahugaw nga sinina sa tanang dapit sa balay</t>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>['nagluno']</t>
+          <t>['hinaw']</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>"Ang balay ni Pedro mura og halas nga nagluno, nagkatag tanan."</t>
+          <t>Si Pedro naghinaw sa iyang responsibilidad pagkahuman sa proyekto.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ang halas sa umah nagluno, ug morag molupad ang mga dahon sa iyang likod.</t>
+          <t>Si Maria naghinaw sa iyang mga kamot human mokaon.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>mamalit og kaso</t>
+          <t>bahong biyuda</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>aron mahimong usa ka ambulance chaser</t>
+          <t>adunay kusog nga baho nga musky o balsam</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bahong', 'biyuda']</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Si Pedro mamalit og kaso aron makakwarta sa mga biktima sa aksidente.</t>
+          <t>Si Pedro bahong biyuda kay bisan unsaon ug ligo, dili mawala ang baho.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Nagplano si Maria nga mamalit og kaso alang sa eskuylahan.</t>
+          <t>Ang silingan nagreklamo tungod kay ang tambong nga pagkahuman sa lamay sa hintungdan nga bahong biyuda pa gihapon hangtod karon.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>anak sa sala</t>
+          <t>baba sa atay</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>usa ka anak nga dili-konsejero</t>
+          <t>ang diaphragm</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>['sala']</t>
+          <t>['baba']</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Ang mga anak sa sala kasagaran nagdako nga adunay mga pagsulay sa ilang kinabuhi.</t>
+          <t>Ang pag-amping sa baba sa atay usa ka importante nga parte sa pag-atiman sa lawas.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ang anak sa sala maoy ang unang nakakita sa mga insidente nga nahitabo diha sa kwarto.</t>
+          <t>Gisuwayan ni Pedro pagkat-on ang posisyon sa baba sa atay sa klase sa anatomiya.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>agi sa bangag sa dagom</t>
+          <t>babayeng ikogan</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
+          <t>transgender</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>['agi', 'bangag']</t>
+          <t>['ikogan']</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Si Ana agi sa bangag sa dagom sa iyang pag-eskwela ug pagtrabaho.</t>
+          <t>Si Pedro kay permi magbuang sa mga babayeng ikogan.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Si Mario nagpaningkamot nga agion ang pisi sa bangag sa dagom aron makatahi sa iyang sinina.</t>
+          <t>Ang mga sinuwaki nangga atong nakita kay babayeng ikogan.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>kuwang sa tagad</t>
+          <t>ander de bunal</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+          <t>gi-squeeze</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>['tagad']</t>
+          <t>['bunal']</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga kuwang sa tagad kasagaran magbuhat ug mga butang aron makuha ang atensyon.</t>
+          <t>Si Pedro kay ander de bunal, kay pirmi lang musunod sa iyang asawa bisan unsa pa.</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ang tanom namong orchid kuwang sa tagad, busa naay mga dahon nga naglaylay.</t>
+          <t>Ang bata nakuyawan pagkahuman nga ander de bunal siya sa iyang amahan tungod sa iyang pagkabadlong.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>buhi pay ginamos</t>
+          <t>gwapa kon magtalikod</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>patay nga sama sa usa ka dughan</t>
+          <t>nindot nga tan-awon gikan sa likod</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>['ginamos']</t>
+          <t>['magtalikod']</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Si Lito buhi pay ginamos, wala na’y paglaom sa iyang kahimtang.</t>
+          <t>Si Maria pirmi lang ginatawgon nga gwapa kon magtalikod sa iyang mga amigo.</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Nag-usisa si Mila sa ilang kusina ug nalipay siya nga mabuhi pa diay iyang ginamos nga giputos sa tupperware.</t>
+          <t>Pag-gawas ni Ana sa kwarto, giingnan siya sa iyang igsoong nga gwapa kon magtalikod kay nindot ang pagkasul-ot sa iyang sanina.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tunga</t>
+          <t>abot sa pikas bukid</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>katunga</t>
+          <t>usa ka tawo nga naghisgot nga makusog</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>['tunga']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Ang tunga sa kalibutan kay naa sa Asia.</t>
+          <t>Ang iyang reklamo abot sa pikas bukid, grabe kaayo ug kasaba.</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Nagputos si Maria og tunga ka buok saging alang sa iyang anak.</t>
+          <t>Migawas si Ana kada buntag aron mananom, ug dal-on niya ang iyang mga produkto abot sa pikas bukid alang sa pagbaligya.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>gilawog sa tirong</t>
+          <t>kapugngan pa ang baha, dili ang biga</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>sa pagbutang sa peligro sa usa ka tawo, ilabina</t>
+          <t>dili mapugngan</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>['gilawog']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Si Juan gilawog sa tirong, bisan wala siya naghimo sa sayop.</t>
+          <t>Ang iyang determinasyon dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ang ilaga gilawog sa tirong aron kini dali madakop.</t>
+          <t>Nagbungkag ang dakong kusog sa biga sa panagdait sa baryo, kapugngan pa ang baha, dili ang biga nga nagdala og kagubot sa mga tawo.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>makamala og sapa</t>
+          <t>ul-ol</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga may dagkong tiil</t>
+          <t>sa pag- masturba Mga sinonim: batil</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>['makamala']</t>
+          <t>['ul-ol']</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Si Juan makamala og sapa sa iyang mga tiil.</t>
+          <t>Ang mga ul-ol nga tawo kasagaran dili makuha ang tinuod nga punto.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Si Maria naglakaw palibot sa bukid ug nakit-an niya ang ilang edipisyo nga makamala og sapa.</t>
+          <t>Naghilum siya sa kwarto ug nag-ul-ol sa dihang walay tawo.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>kulang sa tagad</t>
+          <t>gigukod sa plansa</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>['tagad']</t>
+          <t>['gigukod']</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Si Maria kulang sa tagad, pirmi lang magbinuang aron makuha ang atensyon sa iyang mga kauban.</t>
+          <t>Ang iyang sinina pirmi lang gigukod sa plansa, maong bati tan-awon.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Ang balay ni Lolo ug Lola kulang sa tagad, mao nga hapit na mapapas ang ilang pintal ug nagkinahanglan na’g bag-ong kisame.</t>
+          <t>Ang bata mikatawa samtang gigukod sa plansa ang eroplano nga iyang gihimo gikan sa papel.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>giprito sa kaugalingong mantika</t>
+          <t>gwapa kon magtalikod</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Alternatibo nga porma sa giluto sa kaugalingong mantika</t>
+          <t>nindot nga tan-awon gikan sa likod</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>['giprito']</t>
+          <t>['magtalikod']</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Si Ana giprito sa kaugalingong mantika tungod sa iyang mga aksyon.</t>
+          <t>Ang mga tao nga gwapa kon magtalikod kasagaran maulaw kung mag-atubang.</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nagprito si Maria ug isda gamit ang kaugalingon niyang mantika gikan sa baboy.</t>
+          <t>"Si Ana gwapa kon magtalikod kay nindot ug straight ang iyang buhok."</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>dili na nimo mabalik ang baha sa bukid</t>
+          <t>dili tanang butang sili nga mohalang dayon</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ang nahimo nahimo na</t>
+          <t>Dili tanan mahitabo sa usa ka higayon</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['butang', 'mohalang']</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Si Maria giingnan nga dili na nimo mabalik ang baha sa bukid, mao nga nagpadayon na sa iyang mga plano.</t>
+          <t>Ang mga tawo nga dili tanang butang sili nga mohalang dayon kasagaran magmalampuson sa ilang mga plano.</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ang mga residente sa baryo nanglimpyo og nag-amping kay dili na nila mabalik ang baha sa bukid ug kinahanglan nilang moandal sa sitwasyon.</t>
+          <t>Nagpalit siya og daghang klase sa sili sa merkado, pero nakadiskubre siya nga dili tanang butang sili nga mohalang dayon.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>mogawas ang pari nga walay ulo</t>
+          <t>kusog mokaon og gasolina</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
+          <t>gas-gussing</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>['mogawas']</t>
+          <t>['mokaon']</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Kung magtuyok-tuyok ka sa kadalanan, mogawas ang pari nga walay ulo.</t>
+          <t>Si Maria dili ganahan ug sakyanan nga kusog mokaon og gasolina kay mahal ang maintenance.</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sa karaang kastilyo, matud pa sa mga lumolupyo, usahay mogawas ang pari nga walay ulo kung gabii.</t>
+          <t>Ang bag-ong makina nga gisulayan nila sa laboratoryo kusog mokaon og gasolina sa paspas nga dagan.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>mag-ugbok og mohon</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>sa pagpakigsekso</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['mag-ugbok']</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Ang imong mga plano, ipanabi na sa clouds kay maabot ra na.</t>
+          <t>Ang magtiayon nagdecide nga mag-ugbok og mohon sa ilang honeymoon.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ang detalye sa imong presentation, ipanabi na sa clouds aron ma-access sa tanan bisan asa pa.</t>
+          <t>Ang mga trabahante mag-ugbok og mohon para sa bag-ong balay nga tukoron.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>gibati og kaanyag</t>
+          <t>murag namiya og tai</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>prima donna</t>
+          <t>Usa ka tawo nga mibiya sa dili-iasa nga walay iyang pulong</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4550,255 +4550,255 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga gibati og kaanyag kasagaran magdala ug samok sa grupo.</t>
+          <t>"Si Pedro murag namiya og tai, wala na gani nagpahibalo sa iyang mga kauban."</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ang batang babaye gibati og kaanyag samtang nagtan-aw siya sa matahum nga dagat.</t>
+          <t>Pagkahuman kaon sa iyang pamahaw, si Jun-jun murag namiya og tai kay dali-dali nga midagan paingon sa kasilyas.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>kulang sa tagad</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['tagad']</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Bisan unsa ka lisod, ipanabi na sa clouds ang imong mga pag-ampo.</t>
+          <t>Si Maria kulang sa tagad, pirmi lang magbinuang aron makuha ang atensyon sa iyang mga kauban.</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Pagka gabii, among ipanabi na sa clouds ang among mga mensahe pinaagi sa drone nga adunay mga light display.</t>
+          <t>Ang balay ni Lolo ug Lola kulang sa tagad, mao nga hapit na mapapas ang ilang pintal ug nagkinahanglan na’g bag-ong kisame.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>molayag sa kalipay</t>
+          <t>ang kalimot walay gahom</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>sa pagpakigsekso</t>
+          <t>Ang pagkalimtan dili makahatag kanimo ug wala ka kaayohan</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>['molayag']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Sa dihang nagmolayag sa kalipay ang grupo, nakalimot sila sa ilang mga problema.</t>
+          <t>Ang mga estudyante nga malimot maglisod sa exam, ang kalimot walay gahom.</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Sa ilang bakasyon, ang barko molayag sa kalipay sa nag-aninaw nga dagat samtang ang mga pasahero nagringig.</t>
+          <t>Naa koy gipangita sa akong mga gamit, apan murag ang kalimot walay gahom, kay di man gihapon nako makita.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>katagakon ang mata</t>
+          <t>kuskos balungos</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>mag-ulog</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>['mata']</t>
+          <t>['kuskos']</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Si Maria katagakon ang mata human sa pila ka gabii nga trabaho.</t>
+          <t>Si Pedro pirmi lang kuskos balungos sa iyang trabaho.</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ang mata ni Juan kay katagakon kay giisip niya ang numero sa mga bituon sa langit.</t>
+          <t>Nagkuhaan si Maria ug dali nga kuskos balungos aron limpyohan ang lamesa.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ang masuya madeads</t>
+          <t>gidaman</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
+          <t>sa pag-aturog o pag-aturog</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>['masuya']</t>
+          <t>['gidaman']</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Si Juan kay permi masuya sa mga gadgets sa uban, pero ang masuya madeads.</t>
+          <t>"Kung mangutana ka og ing-ana, murag gidaman ka."</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Siya miingon nga ang masuya madeads, og nagtuo gyud siya nga ang pagkamasuya makaresulta sa pagkamatay.</t>
+          <t>Pagmata nako sa buntag, nakita nako ang akong igsoon nga gidaman ug naglakaw-lakaw sa sala.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>mogawas ang pari nga walay ulo</t>
+          <t>basa og baba</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
+          <t>mabangis</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>['mogawas']</t>
+          <t>['baba']</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Mogawas ang pari nga walay ulo kung ang balay walay suga.</t>
+          <t>Si Juan basa og baba ug permi magdala ug kasaba sa opisina.</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Sa karaang kastilyo, giingon nga sa kagabhion mogawas ang pari nga walay ulo sa daang simbahan.</t>
+          <t>Nagbasa og baba si Maria samtang nagbasa sa iyang paborito nga libro.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>basa ang tingog</t>
+          <t>bibingkang liki</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>dili-matud-an sa tingog</t>
+          <t>ang mga genital sa babaye</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>['tingog']</t>
+          <t>['liki']</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Ang singer nga basa ang tingog naglisod ug kanta sa concert.</t>
+          <t>Ang bibingkang liki kay uso kaayo sa mga binuang ug katawa sa mga barkada.</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Ang papel nabasa kay nabutangan og tubig, ug ang tingog sa paghapnig sa papel nagbasa usab.</t>
+          <t>Gipalit nako ang bibingkang liki sa merkado kay paborito gyud ni nako nga pagkaon.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>batang murag korek</t>
+          <t>magtumba og baka</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>dili-matag-as</t>
+          <t>sa pag-ihaw sa usa ka vaca</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>['batang']</t>
+          <t>['magtumba']</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Ang batang murag korek nga si Juan kasagaran mag-atubang sa mga problema sa balay.</t>
+          <t>Ang ilang pamilya magtumba og baka kung naa’y dako nga celebration.</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>"Gipaduwaan sa amahan ang bata og korek samtang nagtan-aw siya sa mga gamit sa kusina."</t>
+          <t>Ang manggugubat magtumba og baka para sa karne nga ilang ipamaligya sa merkado.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>maabot sa luwa</t>
+          <t>walay mahay nga gauna</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>duol dili layo</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>['maabot', 'luwa']</t>
+          <t>['mahay']</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Si Maria nag-invite ug friends kay ilang balay maabot ra sa luwa.</t>
+          <t>Si Pedro nakasabot nga walay mahay nga gauna, mao nga nagmatngon siya sa iyang mga desisyon.</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Naglumlum ang itlog sa pipit ug, sa walay pagduha-duha, kini maabot ra sa luwa sa ilahang pugad.</t>
+          <t>Nagbasa si Ana ug libro ug nakahuna-huna, "Walay mahay nga gauna," samtang nagtan-aw siya sa mga mahay sa mga bakante nga panid sa sinugdanan.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ayaw adto og gubat kon wala kay bala</t>
+          <t>manira sa dalan</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ayaw pagbuhat ug dili-andam</t>
+          <t>aron magpabilin nga magmata hangtod sa gabii</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>['ayaw', 'adto']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Si Juan giingnan nga ayaw adto og gubat kon wala kay bala kay walay ayo.</t>
+          <t>"Si Ana, sige lang manira sa dalan walay klaro."</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Si Pedro giingnan sa iyang amahan nga ayaw adto og gubat kon wala kay bala aron dili ka maglisod sa pagsabak.</t>
+          <t>"Ang mga estudyante manira sa dalan aron dili maligsan samtang nagduwa."</t>
         </is>
       </c>
     </row>

--- a/Dataset/Test_Set.xlsx
+++ b/Dataset/Test_Set.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,4347 +458,3294 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>anak sa sala</t>
+          <t>dula og panit</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>usa ka anak nga dili-konsejero</t>
+          <t>sa pag- masturba</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['sala']</t>
+          <t>['dula']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ang anak sa sala nga si Maria kay ginaatiman gihapon sa iyang lola ug lolo.</t>
+          <t>Si Maria nagbuot-buot kay gusto siya magdula og panit pirmi.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ang anak sa sala nagdula duol sa altar samtang nagaampo ang pari.</t>
+          <t>Ang akong manghod nagdula og panit sa iyang baboy-baboy nga dulaan.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gibuhi</t>
+          <t>murag gitilapan og iring</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ang penis sa usa ka lalaki</t>
+          <t>walay sapayan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['gibuhi']</t>
+          <t>['gitilapan']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ang mga bata nga iyang gibuhi kay nagdako nga maayong laki.</t>
+          <t>"Ang iyang mga gamit sa opisina murag gitilapan og iring, limpyo ug hapsay."</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Si Lola ang gibuhi sa among gidala nga gamay nga iro gikan sa dalan.</t>
+          <t>"Pagkakita nako sa lamisa, murag gitilapan og iring kay walay tanang bahaw nga niwangig."</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nadakpan na ba ang nagtupi nimo</t>
+          <t>litik</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gisultihan sa usa ka tawo nga adunay bag-ong buhok</t>
+          <t>sa pag-aghat sa tudlo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['nagtupi']</t>
+          <t>['litik']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nadakpan na ba ang nagtupi nimo nga wala man nindot imong buhok?</t>
+          <t>Ang mga tawo nga naglitik sa ilang mga pangandoy kasagaran magmalampuson.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gidala dayon siya sa istasyon sa pulis ug giingnan nga "Nadakpan na ba ang nagtupi nimo nga wala man mangayo og permiso?"</t>
+          <t>Naglingkod si Juan sa lamisa ug kalit niyang gilitik ang botelya nga nagbarog.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>buotan ra og matulog</t>
+          <t>gi-indian</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>malinong</t>
+          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['matulog']</t>
+          <t>['gi-indian']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Si Pedro buotan ra og matulog, kay pirmi lang magbinuang sa klase.</t>
+          <t>Ang iyang kauban sa trabaho gi-indian siya sa ilang meeting.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Si Lola kung mahigda, buotan ra og matulog kay dili siya maglihok-lihok sa gabii.</t>
+          <t>Ang tribo nga among gi-adtoan sa bukid, gi-indian sa mga lumad.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>murag langaw nga nakatugdon sa kabaw</t>
+          <t>pangatulig luwag</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nouveau riche</t>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['nakatugdon']</t>
+          <t>['pangatulig']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"Siya karon murag langaw nga nakatugdon sa kabaw, taas kaayo og pride."</t>
+          <t>"Ayaw pag pangatulig luwag, klaroha imong mga desisyon."</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pag-adlaw, nakita nako ang langaw nga nakatugdon sa likod sa kabaw samtang nag-id-id kini ug mga sanga.</t>
+          <t>Nagpangatulig luwag ang bata tungod kay busog kaayo siya human mikaon og daghang lugaw.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kang kinsa man na imong sala</t>
+          <t>hatod og patay</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa ka tawo nga sila lamang ang may sala sa ilang kaugalingon alang sa ilang kaugalingong mga problema</t>
+          <t>sa pagtambong sa usa ka paglubong o seremonya sa paghinumdom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['sala']</t>
+          <t>['hatod', 'patay']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kang kinsa man na imong sala nga nagdako ka ug kalit?</t>
+          <t>Ang mga tawo nga hatod og patay kasagaran nagpakita ug respeto sa namatay.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>"Giimbestigahan sa konsehal ang panghitabo, ug nangutana siya kang kinsa man na imong sala nga nahitabo ang aksidente."</t>
+          <t>Ang drayber mihangyo nga tabangan siya sa paghatod og patay ngadto sa sementeryo.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ayaw adto og gubat kon wala kay bala</t>
+          <t>hunaw</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ayaw pagbuhat ug dili-andam</t>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['ayaw', 'adto']</t>
+          <t>['hunaw']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ang mga negosyante giingnan nga ayaw adto og gubat kon wala kay bala sa kompetisyon.</t>
+          <t>Ang iyang kauban naghunaw sa mga problema aron dili siya maapil.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ang mga sundalo giingnan sa ilang kumander, "Ayaw adto og gubat kon wala kay bala, kay delikado ang kahimtang diha."</t>
+          <t>Nagpareha sila paghuman sa trabaho ug naghunaw sa ilang kamot sa kusina aron limpyo.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mag-ugbok og mohon</t>
+          <t>ul-ol</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sa pagpakigsekso</t>
+          <t>sa pag- masturba Mga sinonim: batil</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['mag-ugbok']</t>
+          <t>['ul-ol']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Si Ana nagplano nga mag-ugbok og mohon sa iyang birthday.</t>
+          <t>Ang iyang buhat kay ul-ol kaayo, wala gyud maghunahuna.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ang mga trabahante mag-ugbok og mohon aron magtukod og bag-ong balay.</t>
+          <t>Migawas sa ilang klase, nag-ul-ol siya sa ilang balay alang sa pagkat-on sa leksyon.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mingaw pa ang panagat</t>
+          <t>nadakpan na</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>oras sa adlaw nga ang usa ka establisimento adunay pipila ka kostumer ug dili kaayo busy</t>
+          <t>gisultihan sa usa ka tawo nga adunay bag-ong buhok</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['nadakpan']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ang mga negosyo kasagaran mingaw pa ang panagat sa mga sayong oras.</t>
+          <t>Nadakpan na si Pedro nga nagsige ug pangawat sa tindahan.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ang mga manginisda nanguli na kay mingaw pa ang panagat tungod sa bagyo.</t>
+          <t>Nadakpan na ang kawatan nga nisulod sa balay gabii.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dili madala og rosaryo</t>
+          <t>paabang</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>usa ka hingpit nga walay paglaom nga kahimtang</t>
+          <t>pag-abang</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['madala']</t>
+          <t>['paabang']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Si Pedro nag-atubang sa mga pagsulay nga dili madala og rosaryo.</t>
+          <t>Ang mga kwartong ipaabang kay dali ra kaayo mahurot ug ma-book.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nag-ingon ang pari nga ang problema sa kalibutan dili madala og rosaryo ug mga pag-ampo lang.</t>
+          <t>"Nagpaabang sila sa ilang balay samtang nagbakasyon."</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>higda sa lubi</t>
+          <t>gigukod sa sudlay</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pag-ula</t>
+          <t>nga walay buhok</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['higda']</t>
+          <t>['gigukod']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi lang higda sa lubi kung mag-inom.</t>
+          <t>Si Ana pirmi lang gigukod sa sudlay, kay dili siya ganahan mag-comb sa iyang buhok.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ang bata nagduwa sa baybayon ug kalit lang mihigda sa lubi nga napalid sa balas.</t>
+          <t>Si Maria naglupad-lupad ang buhok samtang gigukod sa sudlay sa iyang manghod.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>walay man kardaba mamunga og tundan</t>
+          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
+          <t>Maglakaw sa paghisgot</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['pasulti-on, pabuhaton']</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ang mga estudyante giingnan nga walay man kardaba mamunga og tundan, mao nga magtuon sila pag-ayo.</t>
+          <t>Si Juan giingnan nga buhat ang pasulti-on dili sulti ang pabuhaton sa iyang trabaho.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ang akong lolo kanunay magsulti nga walay man kardaba mamunga og tundan, mao nga ang among mga punuan sa saging dris likod balay pulos gyud mga kardaba.</t>
+          <t>"Sa klase sa sining, gipahimo sa maestro ang mga estudyante ug kaugalingong mga proyekto aron buhat ang pasulti-on dili sulti ang pabuhaton."</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
+          <t>abot sa pikas bukid</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>kitang tanan magkamali</t>
+          <t>usa ka tawo nga naghisgot nga makusog</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['naay', 'masipyat']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Si Maria nasipyat sa pagplano, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
+          <t>Ang istorya ni Pedro abot sa pikas bukid bisan dili tinuod.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ang kabaw nga naay upat ka tiil masipyat sa pagtabok sa pilapila ug nakasulod kini sa umahan.</t>
+          <t>Naglakaw mi ug dugay hangtod nga among naabtan ang pikas bukid.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chona Mae</t>
+          <t>miulbo ang kaspa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tsunami!</t>
+          <t>sa pag-abli ngadto sa kasuko</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['Chona']</t>
+          <t>['miulbo']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Si Chona Mae pirmi lang magbinuang sa eskwelahan.</t>
+          <t>Si Ana miulbo ang kaspa human nabal-an nga gilimbongan siya.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Si Chona Mae akong silingan nga kanunay akong kaistorya matag buntag.</t>
+          <t>Human sa dugang duha ka adlaw nga walay ligo, si Pedro nakabantay nga miulbo ang kaspa sa iyang ulo.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>abli ang Gaisano</t>
+          <t>pangatulig luwag</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nga ang usa nga mosul-ob</t>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['pangatulig']</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kung abli ang Gaisano, kinahanglan dayon sirad-an aron dili magkatawa ang uban.</t>
+          <t>"Pangatulig luwag kaayo imong mga istorya, walay klaro."</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>"Dali na ta kay abli ang Gaisano ug daghan kaayong baligya nga barato."</t>
+          <t>Sa pagkahuman sa panihapon, gikuha ni Lola ang pangatulig luwag aron masimhot ang baho sa nilung-ag nga mais.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>batang murag korek</t>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dili-matag-as</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['batang']</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ang batang murag korek nga si Lito pirmi lang nagbuot-buot.</t>
+          <t>Ang mga estudyante nakabalo nga dili na mabalik ang baha paingon sa bukid, mao nga nagplano na sila pag-ayo.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ang batang nagdula sa balas falor murag korek kay tan-aw nimo layo ra siya sa uban.</t>
+          <t>Pagkahuman sa kusog nga ulan, ang mga taga-barangay nag-istorya nga bisan unsaon pa, dili na mabalik ang baha paingon sa bukid, kay daghan kaayo ang tubig nga midiretso sa dagat.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>magpalapad og papel</t>
+          <t>manira sa dalan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>aron magbaton ug dungog sa buhat sa uban</t>
+          <t>aron magpabilin nga magmata hangtod sa gabii</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['magpalapad']</t>
+          <t>['manira']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga magpalapad og papel kasagaran dili tinood nga maayong magtrabaho.</t>
+          <t>"Ayaw pag manira sa dalan, klaroha imong mga desisyon."</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ang mga bata sa klase nagpalapad og papel gamit ang pintal para sa ilang proyekto sa arte.</t>
+          <t>"Ang negosyante manira sa dalan aron duna sila'y halin bisan sa gabii."</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>lunod patay</t>
+          <t>gilawog sa tirong</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dihard</t>
+          <t>sa pagbutang sa peligro sa usa ka tawo, ilabina</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['lunod', 'patay']</t>
+          <t>['gilawog']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Si Pedro lunod patay sa iyang prinsipyo, dili gyud magbag-o.</t>
+          <t>Si Juan gilawog sa tirong, bisan wala siya naghimo sa sayop.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ang biktima nakit-an nga lunod patay sa dagat human sa kusog nga bagyo.</t>
+          <t>Ang ilaga gilawog sa tirong aron kini dali madakop.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hinaw</t>
+          <t>murag namatyag iring</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+          <t>gigamit sa paghulagway sa usa ka tawo nga nagtangis nga nagtangis o nagtangis nga nagtangis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['hinaw']</t>
+          <t>['namatyag']</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Ang iyang kauban naghinaw sa problema kay dili siya gusto maapil.</t>
+          <t>"Ang bata murag namatyag iring, hilak kaayo pagnalaya."</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>"Naghugaw ang iyang mga kamot sa pintal busa siya mihunaw dayon sa gripo."</t>
+          <t>Ang iring sa atop murag namatyag iring, kusog kaayo ang pangubog.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kusog mokaon og gasolina</t>
+          <t>manglutasay</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gas-gussing</t>
+          <t>usa ka manunulak sa mga bukog</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['mokaon']</t>
+          <t>['manglutasay']</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga mag-drive ug sakyanan nga kusog mokaon og gasolina kasagaran maglisod sa gasto.</t>
+          <t>Ang iyang kauban sa trabaho manglutasay sa mga kabataan.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ang makina sa among sakyanan kusog mokaon og gasolina kung nagdagan mi sa highway.</t>
+          <t>Ang mga bata nagdula sa ilalom sa manglutasay aron magpa-uyog.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>dula og panit</t>
+          <t>habwa ang kinaon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sa pag- masturba</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['dula']</t>
+          <t>['habwa', 'kinaon']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ang iyang barkada kay dula og panit, bisan unsa na lang nga kalipay ang gihimo.</t>
+          <t>Si Maria naghabwa ang kinaon kay nagkalibanga.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ang bata nagdula og panit sa daplin sa suba, gamit ang tanom nga iya nakuha gikan sa palibot.</t>
+          <t>Naghabwa ang bata sa kinaon gikan sa basket aron ipakaon sa mga iro.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>makagisi og pitaka</t>
+          <t>gadalag ulan</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>mahal kaayo</t>
+          <t>usa ka lalaki nga homoseksual</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['nagdala']</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Si Maria nakapalit ug bag nga makagisi og pitaka tungod sa kamahal.</t>
+          <t>Ang mga tawo nga gadalag ulan kasagaran naglisod sa pagdawat sa uban.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ang kawatan nakagisi og pitaka aron makuha ang sulod niining kwarta.</t>
+          <t>Ang itom nga panganod sa langit gadalag ulan nga kusog kaayo.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>makamala og sapa</t>
+          <t>kuskos-balungos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga may dagkong tiil</t>
+          <t>alternatibong pagsulat sa kuskos balungos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['makamala']</t>
+          <t>['kuskos']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Si Pedro makamala og sapa kay grabe kaayo kadako ang tiil.</t>
+          <t>Si Ana pirmi lang kuskos-balungos kung naay buhaton nga dili siya ganahan.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ang babaye makamala og sapa kay nahanaw ang tulay.</t>
+          <t>Gikuha ni Maria ang kutsilyo ug gigamit kini alang sa kuskos-balungos sa kinay sa isda.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>binatilay</t>
+          <t>taliba</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sa pag-aghat sa usag usa sa mga penis</t>
+          <t>ang mga genital sa babaye</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['binatilay']</t>
+          <t>['taliba']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ang mga batan-on nga nagdula og binatilay sa eskwelahan kay gipahimangnoan sa mga maestro.</t>
+          <t>Ang mga guwardiya nag-taliba sa building adlaw ug gabii.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nagpasabot ang tigulang nga ang binatilay sa una kay bahin sa ilang tradisyonal nga sayaw nga gihimo panahon sa pista.</t>
+          <t>Ang taliba sa eskuylahan nagreport nga walay kakulian ang mga estudyante karong adlawa.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>sabong</t>
+          <t>manakop og ligid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>usa ka kompetisyon</t>
+          <t>nga ang usa ka tawo naugtang sa usa ka sakyanan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['sabong']</t>
+          <t>['manakop']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ang mga sabong sa probinsya kasagaran ginadumog sa mga lokal nga residente.</t>
+          <t>Si Pedro manakop og ligid kay nagdagan-dagan sa kalsada.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>"Ang sabong nga gigamit nako sa pagpaligo humot ug daghan ug sabon."</t>
+          <t>Nagdula mi og dakop-dakop sa plaza unya nakalingkod ko para mopahuway, apan kalit nga miingon ang akong amigo nga manakop og ligid mi sa mga sakyanan nga nag-agi atubangan sa balay.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>lunod patay</t>
+          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dihard</t>
+          <t>Maglakaw sa paghisgot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['lunod', 'patay']</t>
+          <t>['pasulti-on, pabuhaton']</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ang iyang amigo lunod patay sa iyang pagtuo bisan pa sa mga pagsulay.</t>
+          <t>Ang mga tawo nga buhat ang pasulti-on dili sulti ang pabuhaton kasagaran magmalampuson.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ang sakayan ilang gisakyan nasangit sa dagkong balod, ug nahinumdom ko sa babaye nga lunod patay sa ubos sa dagat.</t>
+          <t>Si Mario ang nagtrabaho sa proyekto, mao nga buhat ang pasulti-on dili sulti ang pabuhaton aron klaro ang panabang.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>murag langaw nga nakatugdon sa kabaw</t>
+          <t>lunod patay</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nouveau riche</t>
+          <t>dihard</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['nakatugdon']</t>
+          <t>['lunod', 'patay']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>"Ang mga tawo nga bag-o rang nakuhaan ug jackpot murag langaw nga nakatugdon sa kabaw."</t>
+          <t>Ang iyang amigo lunod patay sa iyang pagtuo bisan pa sa mga pagsulay.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ang langaw naglupad-lupad sa palibot hangtod nakatugdon sa kabaw.</t>
+          <t>Ang sakayan ilang gisakyan nasangit sa dagkong balod, ug nahinumdom ko sa babaye nga lunod patay sa ubos sa dagat.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
+          <t>manira sa dalan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mahimo nimong pagdala ang kabayo ngadto sa tubig</t>
+          <t>aron magpabilin nga magmata hangtod sa gabii</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['madala', 'mainom']</t>
+          <t>['manira']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Si Pedro giingnan nga bisan unsaon pagdasig, madala nimo ang baka sa suba apan dili nimo mainom.</t>
+          <t>Si Pedro pirmi manira sa dalan kada gabii.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nagkakaboang ang mga mag-uuma kay madala nimo ang baka sa suba apan dili nimo mainom ang hayop bisan init kaayo ang adlaw.</t>
+          <t>Si Juan manira sa dalan aron mabantayan ang kalihokan sa mga dumuloong.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>halinon og aping</t>
+          <t>gwapo kon magtalikod</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>maayo kaayo nga hitsura</t>
+          <t>nindot nga tan-awon gikan sa likod</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['halinon']</t>
+          <t>['magtalikod']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Si Maria halinon og aping, daghan kaayo siya ug admirers.</t>
+          <t>Ang mga tao nga gwapo kon magtalikod kasagaran dili magdugay sa ilang relasyon.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Naghalinon og aping ang bata human siya gi-wash ug face ni Mama.</t>
+          <t>Si Juan gwapo kon magtalikod, kay nindot ug porma ang iyang buhok ug likod.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>gibuhi</t>
+          <t>mangnukos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ang penis sa usa ka lalaki</t>
+          <t>sa pag-abli sa usa ka pista</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['gibuhi']</t>
+          <t>['mangnukos']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Gibuhi niya ang iyang mga tanom nga permi niyang ginatiman.</t>
+          <t>Si Juan giingnan nga dili mangnukos sa party sa iyang amiga.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>"Gibuhi sa amahan ang nawong sa iyang anak gamit ang panyo."</t>
+          <t>Ang iro misugod ug mangnukos sa iring nga mikarat sa atop.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>binuhi</t>
+          <t>murag langaw nga nakatugdon sa kabaw</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ang penis sa usa ka lalaki</t>
+          <t>nouveau riche</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['nakatugdon']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ang mga binuhi nga iro sa ilang balay kay puro mga pure breed.</t>
+          <t>"Ang mga bag-o rang nigraduate ug ni trabaho, murag langaw nga nakatugdon sa kabaw."</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ang binuhi nga baka kay gi-atiman pag-ayo aron magamit sa umaabot nga negosyo sa gatas.</t>
+          <t>Natagbaw ang langaw ug tuas siya sa likod sa kabaw, murag langaw nga nakatugdon sa kabaw nga nagpangita ug pahulay.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>makakutaw og utok</t>
+          <t>gidaman</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>makapalibog</t>
+          <t>sa pag-aturog o pag-aturog</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['makakutaw']</t>
+          <t>['gidaman']</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Ang explanation sa iyang professor makakutaw og utok kaayo.</t>
+          <t>"Kung mangutana ka og ing-ana, murag gidaman ka."</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ang iyahang paghalo sa mainit nga supas makakutaw og utok kay wala pa man gud niupos ang kainit niini.</t>
+          <t>Pagmata nako sa buntag, nakita nako ang akong igsoon nga gidaman ug naglakaw-lakaw sa sala.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>manglutasay</t>
+          <t>ang baka nisulod sa kulon</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>usa ka manunulak sa mga bukog</t>
+          <t>gigamit sa pagsulti sa usa nga siya usa ka bakak o ikaw mahimo sa pagsulti sa laing nagbuwa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['manglutasay']</t>
+          <t>['nisulod']</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Si Juan giingnan nga manglutasay kay ang iyang uyab mas bata kaayo.</t>
+          <t>Sa dihang nagluto siya, naay baka nisulod sa kulon nga nagkalata.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ang mga bata sa baryo magdula-dula ug manglutasay sa tabing-suba.</t>
+          <t>Naglibog ko pagtan-aw sa kusina kay ang baka gyud tinuod nga nisulod sa kulon.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gi-indian</t>
+          <t>walay aso makumkom</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
+          <t>walay sekreto nga magpabilin nga sekreto</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['gi-indian']</t>
+          <t>['makumkom']</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Si Pedro gi-indian sa iyang uyab sa ilang sabot nga date.</t>
+          <t>Si Ana nakasabot nga walay aso makumkom, mao nga nagbantay siya sa iyang mga desisyon.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wala moabot si Miguel sa ila nahuman nga sabot, kay gi-indian man siya sa Mindanao para magtuon sa mga lumad nga Indian didto.</t>
+          <t>Ang tinuod, bisan unsa ka kusog sa imong pagpaningkamot, walay aso makumkom basta maayo ang hangin.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kuwang sa tagad</t>
+          <t>ul-ol</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+          <t>sa pag- masturba Mga sinonim: batil</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['tagad']</t>
+          <t>['ul-ol']</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Si Pedro kuwang sa tagad, bisan unsa nga event ganahan magpakita.</t>
+          <t>Ang iyang mga ul-ol nga istorya kay naghatag ug kalibog sa tanan.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ang tanom nga wa matagda, nagpakita og mga sintomas nga kuwang sa tagad sama sa mga dili hapsay nga dahon.</t>
+          <t>Juan miingon nga siya gikapoy human siya mag-ul-ol sulod sa iyang kwarto.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>taliba</t>
+          <t>giprito sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ang mga genital sa babaye</t>
+          <t>Alternatibo nga porma sa giluto sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['taliba']</t>
+          <t>['giprito']</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ang mga pulis nag-taliba sa mga salida aron protektahan ang mga bisita.</t>
+          <t>Si Juan giprito sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ang taliba nagsugod ug talagsaon nga lihok human sa pagkahuman sa operasyon.</t>
+          <t>Nagluto si Maria ug isda nga giprito sa kaugalingong mantika aron mas lami ang timpla.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>hatod og patay</t>
+          <t>maghilak ang adlaw</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>sa pagtambong sa usa ka paglubong o seremonya sa paghinumdom</t>
+          <t>mabul-og</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['hatod', 'patay']</t>
+          <t>['maghilak']</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Si Pedro hatod og patay sa iyang kauban sa trabaho.</t>
+          <t>Ang mga tawo nag-relax sa balay samtang naghilak ang adlaw.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nag-hatod og patay ang mga mag-uuma ngadto sa paglubong sa talis.</t>
+          <t>Ang mga bata nagdali og pauli pagkahuman nila makit-an nga maghilak ang adlaw tungod sa kusog nga ulan.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>makabugto og panty</t>
+          <t>higda sa lubi</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pisikal o seksuwal nga madanihon</t>
+          <t>pag-ula</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['makabugto']</t>
+          <t>['higda']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Si Pedro ganahan kaayo sa iyang uyab kay makabugto og panty.</t>
+          <t>Si Juan higda sa lubi, pirmi lang maghubog-hubog.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paglaba nako sa akong mga sinina, nasamad ang akong daliri tungod sa hugot nga elax na makabugto og panty.</t>
+          <t>Ang bata nakatulog ug higda sa lubi human magdula sa daplin sa baybayon.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>duwa og panit</t>
+          <t>pangatulig luwag</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sa pag- masturba</t>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['duwa']</t>
+          <t>['pangatulig']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ang mga bata nga nagdula sa internet pirmi lang magduwa og panit.</t>
+          <t>"Pangatulig luwag imong mga ideas, kinahanglan pa nimo ug focus."</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ang mga tambay sa kanto nagduwa og panit sa kadyot nga hagit sa ilang amigo.</t>
+          <t>"Sa kalit nga pangatulig luwag, nawad-an siya ug gana sa iyang gipangluto nga lugaw."</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>istorya ilalom sa dagat</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Usa ka dakong basura</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga dili tinuod pirmi lang mag-istorya ilalom sa dagat.</t>
+          <t>Ang iyang mga istorya pirmi ipanabi na sa clouds kay dili tinuod.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ang mga nanginhas nakadungog og istorya ilalom sa dagat samtang nagsubsob sa ilang buluhaton.</t>
+          <t>Ang mga piloto nagplano nga ipanabi na sa clouds ang mensahe nga nahuman na ang misyon.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>habwa ang kinaon</t>
+          <t>lisod pukawon ang gamata</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>pag-awhag</t>
+          <t>gigamit sa pagsulti sa nagmata o sa usa ka tawo nga dili magmata</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['habwa', 'kinaon']</t>
+          <t>['pukawon']</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Si Maria naghabwa ang kinaon kay nagkalibanga.</t>
+          <t>Bisan unsaon, lisod pukawon ang gamata kung kapoy ang lawas.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Naghabwa ang bata sa kinaon gikan sa basket aron ipakaon sa mga iro.</t>
+          <t>Matag buntag, lisod pukawon ang gamata kay grabe ka duol ang ilang pagkatulog.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>litik</t>
+          <t>abot sa dalunggan ang ngisi</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sa pag-aghat sa tudlo</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['litik']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga naglitik sa ilang mga pangandoy kasagaran magmalampuson.</t>
+          <t>Ang bata, abot sa dalunggan ang ngisi sa dihang gihatagan ug dako nga regalo.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Naglingkod si Juan sa lamisa ug kalit niyang gilitik ang botelya nga nagbarog.</t>
+          <t>Ang babaye, abot sa dalunggan ang ngisi tungod sa iyang katawa.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>duwa og panit</t>
+          <t>bukhad og palad</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sa pag- masturba</t>
+          <t>mahinatagon Synonyms: manggihatagon</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>['duwa']</t>
+          <t>['bukhad']</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Si Pedro walay laing gihimo kundi magduwa og panit pirmi.</t>
+          <t>Ang mga tao nga bukhad og palad kasagaran daghan ug mga amigo.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gipakita sa maestro nga giunsa pagduwa og panit sa tambol aron makuha ang tukmang tingog.</t>
+          <t>Si Lola Juanita mihapit sa manghuhula aron pabasaon ang iyang bukhad nga palad.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>istorya ilalom sa dagat</t>
+          <t>dili makaon og iro</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Usa ka dakong basura</t>
+          <t>makalilisang</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['makaon']</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ang iyang pangatarungan kay istorya ilalom sa dagat, walay klaro.</t>
+          <t>Ang iyang batasan dili makaon og iro, maong walay ganahan makighangyo niya.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ang mga diver nakahibalo nga lisud ang pag-istorya ilalom sa dagat tungod sa tubig.</t>
+          <t>Ang mga pagkaon nga gibutang sa lamesa dili makaon og iro kay peligroso kini sa ilang panglawas.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
+          <t>ayaw adto og gubat kon wala kay bala</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
+          <t>ayaw pagbuhat ug dili-andam</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['lingaw', 'dakpa']</t>
+          <t>['adto']</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, kay walay lain maka-entertain nimo.</t>
+          <t>Ang mga negosyante giingnan nga ayaw adto og gubat kon wala kay bala sa kompetisyon.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Naglain akong tiyan, mao nga kung wala kay lingaw sa kinabuhi, dakpa akong utot aron makita nato ug tinuod ba.</t>
+          <t>Ang mga sundalo giingnan sa ilang kumander, "Ayaw adto og gubat kon wala kay bala, kay delikado ang kahimtang diha."</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>awas og palad</t>
+          <t>taga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>• awasan og palad</t>
+          <t>pag-slash</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['awas']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Si Ana awas og palad, maong pirmi lang maglisod bisan taas ang sweldo.</t>
+          <t>Ang mga kawatan nahadlok kay basin mataga sila sa mga tag-iya sa balay.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gihugasan niya ang iyang palad ug karon nag-awas na ang tubig gikan niini.</t>
+          <t>Ang mananagat mihawid ug isda ug gitaga kini gamit ang sundang.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>hangyo kabayo</t>
+          <t>dili tanang butang sili nga mohalang dayon</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>usa ka maalamon nga paagi sa pagbaton ug usa ka butang</t>
+          <t>Dili tanan mahitabo sa usa ka higayon</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>['hangyo']</t>
+          <t>['mohalang']</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga hangyo kabayo kasagaran magmalampuson sa ilang mga plano.</t>
+          <t>Ang mga tawo nga dili tanang butang sili nga mohalang dayon kasagaran magmalampuson sa ilang mga plano.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ang bata naghangyo sa iyang ginikanan nga paliton siya og kabayo.</t>
+          <t>Nagpalit siya og daghang klase sa sili sa merkado, pero nakadiskubre siya nga dili tanang butang sili nga mohalang dayon.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>kung wala kay lingaw, dakpa akong utot</t>
+          <t>molayag sa kalipay</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
+          <t>sa pagpakigsekso</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['lingaw', 'dakpa']</t>
+          <t>['molayag']</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kung wala kay lingaw, dakpa akong utot aron ma-testing nimo imong abilidad.</t>
+          <t>Ang mga amigo nagmolayag sa kalipay sa ilang road trip.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Paglingkod nako sa sofa, gisulti nako sa akong ig-agaw, "Kung wala kay lingaw, dakpa akong utot," aron makita namo kung makaya ba niya pagkakupot.</t>
+          <t>Ang mga bata nagmolayag sa kalipay samtang nagdula sa dagat sa buntag.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ander da bunal</t>
+          <t>ul-ol</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gi-squeeze</t>
+          <t>sa pag- masturba Mga sinonim: batil</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['bunal']</t>
+          <t>['ul-ol']</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Ang relasyon nila kay ander da bunal, maong klaro kaayo kinsa ang nagbuot.</t>
+          <t>Dili maayo nga magsige ka ug ul-ol kay makadaot kini sa imong reputation.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ang bata misunod sa iyang mama nga "ander da bunal" human masagpaan ug kahoy.</t>
+          <t>"Ang bata natapolan ug dili gusto magtuon, murag ul-ol gyud siya."</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tinagoan</t>
+          <t>gigukod sa plansa</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>gitago</t>
+          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['gigukod']</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ang tinagoan nga lihim ni Juan kay nahibaw-an na sa tanan.</t>
+          <t>Ang mga tawo nga gigukod sa plansa kasagaran dili mag-atiman sa ilang kaugalingon.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>"Ang tinagoan nga kwarta sa luyo sa aparador nadiskobrehan sa iyang igsoon."</t>
+          <t>Ganiha buntag, nagdali ko ug gamay, maong ang akong kamiseta gigukod sa plansa aron mawala ang tupi.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>mamalit og kaso</t>
+          <t>gwapa kon magtalikod</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>aron mahimong usa ka ambulance chaser</t>
+          <t>nindot nga tan-awon gikan sa likod</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['magtalikod']</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga mamalit og kaso kasagaran mga abogado nga gustong magpasikat.</t>
+          <t>Ang mga tao nga gwapa kon magtalikod kasagaran maulaw kung mag-atubang.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ang akong ig-agaw gusto mamalit og kaso aron magamit niya sa among eskwelahan nga praktis.</t>
+          <t>"Si Ana gwapa kon magtalikod kay nindot ug straight ang iyang buhok."</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>mabaw og kibot</t>
+          <t>tuslok baki</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>dali nga madaot</t>
+          <t>usa ka dula</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>['kibot']</t>
+          <t>['tuslok']</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ang iyang kauban mabaw og kibot, bisan gamay lang nga butang maglagot na.</t>
+          <t>Ang tuslok baki kay usa ka traditional nga dula nga gipasa-pasa sa mga henerasyon.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Daling mobakwi si Ana kay mabaw og kibot, labi na kon naay kalit nga tingog.</t>
+          <t>Nagkagubot ang mga bata samtang nagtan-aw kung kinsa ang makatama sa baki sa ilang gipagawas nga tuslok.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>halinon og aping</t>
+          <t>kusog mokaon og gasolina</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>maayo kaayo nga hitsura</t>
+          <t>gas-gussing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>['halinon']</t>
+          <t>['mokaon']</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Si Ana halinon og aping, daghan kaayo siya ug mga manliligaw.</t>
+          <t>Ang iyang motor kusog mokaon og gasolina, pirmi lang magpailis.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nagposing si Ana aron makuhanan og halinon og aping nga larawan sa iyang mga album.</t>
+          <t>Nag-obserbar si Juan nga kusog mokaon og gasolina ang ilang makinarya sa umahan tungod kay daghan kaayong trabaho sa ting-ani.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>bukad og ngabil</t>
+          <t>magtumba og baka</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>mga labi nga may lapis</t>
+          <t>sa pag-ihaw sa usa ka vaca</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['bukad']</t>
+          <t>['magtumba']</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Si Juan bukad og ngabil, bisan unsa nga istorya, pirmi lang magsige ug sulti.</t>
+          <t>Si Maria nalipay kay magtumba og baka ang iyang pamilya para sa pasko.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ang bata kay bukad og ngabil tungod sa iyang allergies.</t>
+          <t>Ang mga trabahador sa uma magtumba og baka karong buntaga para sa karneng iprutos.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>mag-ihaw og lata</t>
+          <t>hangyo lubo</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>sa pagluto sa mga pagkaon nga tinago</t>
+          <t>usa ka hangyo nga gihimo sa ingon nga paagi nga dili kini makalikay</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['mag-ihaw']</t>
+          <t>['hangyo', 'lubo']</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ang mga estudyante kasagaran mag-ihaw og lata kung nagtipid.</t>
+          <t>Si Maria hangyo lubo, maong walay makatanggi sa iyang mga pangutana.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Si Lito nag-andam og dapog aron mag-ihaw og lata para sa ilang campfire na aktibidad.</t>
+          <t>Ang hangyo lubo ni Juan kay ang pagbahin sa iyang mga kalubian sa iyang mga silingan human sa bagyong miagi.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kang kinsa man na imong sala</t>
+          <t>kapugngan pa ang baha, dili ang biga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa ka tawo nga sila lamang ang may sala sa ilang kaugalingon alang sa ilang kaugalingong mga problema</t>
+          <t>dili mapugngan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['sala']</t>
+          <t>['kapugngan']</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Kang kinsa man na imong sala nga gipaninguha nimo?</t>
+          <t>Si Maria adunay dakong pangandoy nga dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>"Nagpangutana si Maria, 'Kang kinsa man na imong sala nga nasudlan?' kay wala siya nakasabot sa istorya."</t>
+          <t>Pag-abot sa kusog nga ulan, kapugngan pa ang baha, dili ang biga sa yuta nga grabe kaayo ang pag-inilog ug pag-atake.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>dugay pay manguros</t>
+          <t>buotan ra og matulog</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>usa ka piraso sa cake</t>
+          <t>malinong</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>['manguros']</t>
+          <t>['matulog']</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Si Juan dugay pay manguros kung magtrabaho sa opisina.</t>
+          <t>Ang mga bata nga buotan ra og matulog kasagaran magdala ug kasamok sa balay.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Buntag pa sa simbahan, dugay pay manguros ang mga tawo nga nagtipon sa una nga misa.</t>
+          <t>Si Lito, bisag buotan ra og matulog, abtik kaayo sa pagtrabaho kung alerto na.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>makakutaw og utok</t>
+          <t>magpalapad og papel</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>makapalibog</t>
+          <t>aron magbaton ug dungog sa buhat sa uban</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['makakutaw']</t>
+          <t>['magpalapad']</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Si Maria nagreklamo kay ang instructions makakutaw og utok.</t>
+          <t>Ang iyang kauban sa trabaho pirmi magpalapad og papel sa mga achievements sa uban.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Si Maria nagdagan palibot sa lamisa nga makakutaw og utok.</t>
+          <t>Nagpalit siya og balayronon sa papel sa tindahan kay magpalapad siya og papel alang sa iyang project sa eskuwela.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>giluto sa kaugalingong mantika</t>
+          <t>sabong</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sa pag-ukit sa kaugalingong lubnganan</t>
+          <t>usa ka kompetisyon</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['giluto']</t>
+          <t>['sabong']</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga magbuhat ug dautan kasagaran giluto sa kaugalingong mantika.</t>
+          <t>Ang mga manok nga ipangsabong kay gipangandaman ug maayo.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gihikay nila ang baboy sa pista ug giluto sa kaugalingong mantika.</t>
+          <t>Ang akong amahan mopalit og sabon sa merkado kay nahutdan na mi sa among balay.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>awas og palad</t>
+          <t>maabot sa luwa</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>• awasan og palad</t>
+          <t>duol dili layo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['awas']</t>
+          <t>['maabot']</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ang mga awas og palad kasagaran maglisod sa kinabuhi kay dili kabalo magtipid.</t>
+          <t>Ang lugar nga ilang giadtoan kay maabot ra sa luwa, dili layo.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Miuyog ko sa akong ulo nga dali ra kaayo nga awas ang palad sa baso.</t>
+          <t>Ang tubig nga akong gitilaw kay lami, hangtod maabot ra gyud sa luwa.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>magtumba og baka</t>
+          <t>agi sa bangag sa dagom</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>sa pag-ihaw sa usa ka vaca</t>
+          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['magtumba']</t>
+          <t>['agi']</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Si Maria nalipay kay magtumba og baka ang iyang pamilya para sa pasko.</t>
+          <t>Ang iyang negosyo agi sa bangag sa dagom bago niyag napalambo.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ang mga trabahador sa uma magtumba og baka karong buntaga para sa karneng iprutos.</t>
+          <t>Nagtan-aw siya unsaon pag-agi sa sinulid sa bangag sa dagom aron masugdan ang pagpanahi.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ang masuya madeads</t>
+          <t>ang baka nisulod sa kulon</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
+          <t>gigamit sa pagsulti sa usa nga siya usa ka bakak o ikaw mahimo sa pagsulti sa laing nagbuwa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['masuya']</t>
+          <t>['nisulod']</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Ayaw suya-suya kay ang masuya madeads.</t>
+          <t>Sa dihang nag-away sila, mura'g baka nga nisulod sa kulon ang kasaba.</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ang masuya madeads tungod kay nasuya siya sa bag-ong kotse sa iyang silingan ug naghinanok, naapsan siya sa sakuna.</t>
+          <t>Gikugang si Mama pagtan-aw niya nga ang baka tinuod gyud nga nisulod sa kulon.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>hunaw</t>
+          <t>ang masuya madeads</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['hunaw']</t>
+          <t>['masuya']</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Si Juan naghunaw sa iyang responsibilidad sa trabaho.</t>
+          <t>Si Juan kay permi masuya sa mga gadgets sa uban, pero ang masuya madeads.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Si Maria naghunaw sa iyang mga kamot human sa pagkaon.</t>
+          <t>Siya miingon nga ang masuya madeads, og nagtuo gyud siya nga ang pagkamasuya makaresulta sa pagkamatay.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>bunal</t>
+          <t>abot sa dunggan ang ngisi</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ang tungkod nga gigamit sa pag-atake o pag-bully sa usa ka hayop o tawo</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>['bunal']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ang mga bunal sa mga dula sa elementarya kay kasagaran gihimo ug kahoy.</t>
+          <t>Abot sa dunggan ang ngisi ni Manang Ines pagkakita sa iyang mga apo.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ang bunal nga gigamit sa mag-uuma kay gahi ug kahoy aron dili dali maguba.</t>
+          <t>Gani, abot sa dunggan ang ngisi ni Juan kay naputlan siya ug tabil sa iyang ngipon.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kalas og bugo</t>
+          <t>makabugto og bra</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>usa ka pulong nga gigamit sa pagsulti sa usa ka tawo nga siya nagkinahanglan og dugay kaayo aron masabtan kon unsay gipamulong</t>
+          <t>pisikal o seksuwal nga madanihon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['kalas']</t>
+          <t>['makabugto']</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ayaw pag-kalas og bugo, kay sayang lang ang imong panahon.</t>
+          <t>Si Juan ganahan kaayo sa iyang uyab kay makabugto og bra.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Naglimpyo ko sa sala, unya kalas og bugo ang akong giusik kay naguba dayon ang dustpan.</t>
+          <t>"Ayoa pag-atiman sa imong sinina kay basin makabugto og bra ang lig-ag sa washing machine."</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>makabugto og panty</t>
+          <t>kulang sa dukol</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>pisikal o seksuwal nga madanihon</t>
+          <t>usa ka buangbuang nga tawo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>['makabugto']</t>
+          <t>['dukol']</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ang artista nga iyang nakita sa sine makabugto og panty gyud.</t>
+          <t>Si Juan kulang sa dukol, pirmi lang magtambay sa kanto.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ang hilo sa iyang bag-ong panty nipis ra kaayo nga dili kalikayan nga makabugto og panty kung mabira.</t>
+          <t>Si bata kulang sa dukol kay walay nag-amuma sa iya kabuang.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bahong biyudo</t>
+          <t>gi-indian</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>adunay kusog nga baho nga musky o balsam</t>
+          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>['bahong']</t>
+          <t>['gi-indian']</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ang mga gamit sa balay nga wala gipanumbaling kay bahong biyudo.</t>
+          <t>Ang mga estudyante na gi-indian sa ilang maestra sa klase karon.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Si Tatay Juan, nga usa ka biyudo, dili na makasabot sa bahong biyudo nga naggikan sa iyang mga sinina.</t>
+          <t>Siya gi-indian ang hilaw nga manok gamit ang tradisyonal nga resipe sa tribu.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>abot sa dunggan ang ngisi</t>
+          <t>habwa ang kinaon</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nga dili gayod malipay</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>['abot', 'dunggan', 'ngisi']</t>
+          <t>['habwa', 'kinaon']</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sa dihang gihatagan siya ug award, abot sa dunggan ang ngisi ni Carla.</t>
+          <t>Ang iyang amiga naghabwa ang kinaon kay nasubraan ug kaon.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nagkatawa kaayo ang bata nga abot sa dunggan ang ngisi niya.</t>
+          <t>Ang bata naghabwa sa sudlanan aron makuha ang kinaon.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
+          <t>kulang sa dukol</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>gigamit nga isulti sa usa ka tawo nga imong gilimbongan sila sa pagtan-aw sa usa ka piho nga direksyon</t>
+          <t>usa ka buangbuang nga tawo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['kitkit', 'kitkit', 'bungi']</t>
+          <t>['dukol']</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>paglingi, kitkit bungi.</t>
+          <t>Ang iyang anak kulang sa dukol, dili gyud magtinarong sa pag-eskwela.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sa paghigda sa ilang balay, si Lito nakadungog ug sulti ni Jayjay nga "pagtan-aw, kitkit langaw; paglingi, kitkit bungi," ug nakatawa sila kay nasakpan tuod nga adunay langaw ug asong bungi sa may bintana.</t>
+          <t>Ang bata kulang sa dukol, mao nga giingnan siya sa iyang ginikanan nga magmatngon sa sunod nga dulaan.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>kulang sa tagad</t>
+          <t>ayaw pagbuot kay lain-lain ta og lubot</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+          <t>ayaw ako isulti kon unsay buhaton</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['tagad']</t>
+          <t>['pagbuot']</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga kulang sa tagad kasagaran magbuhat ug dautan para makuha ang attention sa uban.</t>
+          <t>Ayaw pagbuot kay lain-lain ta og lubot, respetaray lang ta sa atong mga opinion.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ang bata kulang sa tagad kay wala siya gitagad sa mga tigulang samtang nagdula siya sa plasa.</t>
+          <t>Pagmeeting sa klase, nananghid si Junjun nga dili siya makagymnastics kay ingon niya, "Ayaw pagbuot kay lain-lain ta og lubot," nagsakit iyang lubot paglingkod.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ander da bunal</t>
+          <t>kuwang sa tagad</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>gi-squeeze</t>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>['bunal']</t>
+          <t>['tagad']</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ang ander da bunal nga bana kay kasagaran magpaubos ug musunod sa asawa.</t>
+          <t>Si Juan pirmi lang magpakita sa mga tao kay kuwang sa tagad.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Si Lucas kay nagu-ander da bunal nga duwa, diin ang mga bata nagbungkag ug mga bulingon nga kahoy gamit ang bunal.</t>
+          <t>Ang bata nga nahibilin sa balay gamay ra kaayo ang nadawat nga kalooy, kuwang sa tagad sa iyang mga ginikanan.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>hangyo lubo</t>
+          <t>gisulod sa bulsa</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>usa ka hangyo nga gihimo sa ingon nga paagi nga dili kini makalikay</t>
+          <t>sa paglimbong</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['hangyo', 'lubo']</t>
+          <t>['gisulod']</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Si Maria hangyo lubo, maong walay makatanggi sa iyang mga pangutana.</t>
+          <t>Si Maria gisulod sa bulsa, maong nag-antos siya sa iyang mga desisyon.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ang hangyo lubo ni Juan kay ang pagbahin sa iyang mga kalubian sa iyang mga silingan human sa bagyong miagi.</t>
+          <t>Gisulod ni Juan ang sensilyo sa iyang bulsa aron dili kini mawala.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>walay mahay nga gauna</t>
+          <t>gadalag uwan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>usa ka lalaki nga homoseksual</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['mahay']</t>
+          <t>['nagdala']</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ang mga estudyante giingnan nga walay mahay nga gauna, mao nga magtuon sila pag-ayo.</t>
+          <t>Ang iyang silingan gadalag uwan, pero respetado gihapon sa ilang lugar.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Walay mahay nga gauna, mao nga si Ana karon nagbangutan tungod kay nawala ang iyang wallet.</t>
+          <t>Naglakaw kami sa kalsada ug nakita namo nga ang bata gadalag uwan aron dili mabasa sa kalit nga pag-abot sa ulan.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>gigukod sa plansa</t>
+          <t>maabot sa luwa</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
+          <t>duol dili layo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['gigukod']</t>
+          <t>['maabot']</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga gigukod sa plansa kasagaran dili mag-atiman sa ilang kaugalingon.</t>
+          <t>Si Pedro pirmi lang maglakaw kay ang eskwelahan maabot ra sa luwa.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ganiha buntag, nagdali ko ug gamay, maong ang akong kamiseta gigukod sa plansa aron mawala ang tupi.</t>
+          <t>Ang lamesa natapsingan sa luwa ni Karen samtang siya nagtabi-tabi.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>murag gitilapan og iring</t>
+          <t>walay aso makumkom</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>walay sapayan</t>
+          <t>walay sekreto nga magpabilin nga sekreto</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['gitilapan']</t>
+          <t>['makumkom']</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>"Ang iyang mga gamit sa opisina murag gitilapan og iring, limpyo ug hapsay."</t>
+          <t>Si Pedro nasayod nga walay aso makumkom, mao nga nagmatngon siya sa iyang mga lihok.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>"Pagkakita nako sa lamisa, murag gitilapan og iring kay walay tanang bahaw nga niwangig."</t>
+          <t>Nagpayong si Anna duol sa siga apan nag-ingon siya nga walay aso makumkom tungod kay ihipan kini sa hangin.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>makabugto og bra</t>
+          <t>hangyo kabayo</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>pisikal o seksuwal nga madanihon</t>
+          <t>usa ka maalamon nga paagi sa pagbaton ug usa ka butang</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>['makabugto']</t>
+          <t>['hangyo']</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Si Juan ganahan kaayo sa iyang uyab kay makabugto og bra.</t>
+          <t>Ang iyang amiga hangyo kabayo, bisan unsa nga butang iyang makuha.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>"Ayoa pag-atiman sa imong sinina kay basin makabugto og bra ang lig-ag sa washing machine."</t>
+          <t>Paghangyo siya sa presyo sa kabayo nga iyang gustong paliton.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>gigukod sa plansa</t>
+          <t>awas og palad</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
+          <t>• awasan og palad</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['gigukod']</t>
+          <t>['awas']</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi lang gigukod sa plansa, bisan unsa nga sinina dili mahimutang.</t>
+          <t>Ang mga awas og palad kasagaran maglisod sa kinabuhi kay dili kabalo magtipid.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ang shirt ni Juan gigukod sa plansa human gilabhan.</t>
+          <t>Miuyog ko sa akong ulo nga dali ra kaayo nga awas ang palad sa baso.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
+          <t>dili na nimo mabalik ang baha sa bukid</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
+          <t>Ang nahimo nahimo na</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>['lingaw', 'dakpa']</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, basi malingaw ka.</t>
+          <t>Si Ana nakasabot nga dili na nimo mabalik ang baha sa bukid, mao nga nag-move on na siya.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nagduwa ang mga bata og palumba sa iskina ug miingon si Juan, "Kung wala kay lingaw sa kinabuhi, dakpa akong utot, paglingaw-lingaw lang."</t>
+          <t>Nagbaha sa bukid tungod sa kusog nga ulan, ug bisan unsaon pa nimo og paningkamot, dili na nimo mabalik ang baha sa bukid nga ubos.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>pasok, Luningning</t>
+          <t>ang gaba dili magsaba</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>miingon sa kaugalingon sa dihang pag-poking sa usa sa iyang mga winnings sa usa ka dula sa mga kard</t>
+          <t>ang silot tungod sa iyang mga sayop o mga paglapas moabut sa wala damha</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>['pasok']</t>
+          <t>['magsaba']</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Pasok, Luningning, kay daghan pa ta ug buhaton.</t>
+          <t>Si Pedro nabulabog kay nasuko ang iyang giilad, ang gaba dili magsaba.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nangabli si Luningning sa pultahan ug giingnan siya sa iyang mama, "Pasok, Luningning, kay ulan kaayo sa gawas."</t>
+          <t>Sa kalit nga pagtandog sa kanal, nabali ang sungkod ni Lito ug nahangit siya, gipakita nga ang gaba dili magsaba.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>dili na mabalik ang baha paingon sa bukid</t>
+          <t>kuyog baboy</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>usa ka tagalong</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['kuyog']</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Si Juan nasayod nga dili na mabalik ang baha paingon sa bukid, mao nga nagpadayon na siya.</t>
+          <t>Si Maria pirmi lang kuyog baboy, bisan asa moadto iyang best friend naa gyud.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ang mga lumulupyo sa baryo nahibulong kay dili na mabalik ang baha paingon sa bukid bisan sa kusog nga ulan.</t>
+          <t>Naglaag mi sa uma ug nagdala mi og kuyog baboy aron makalingaw ang mga bata.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>nakalugsong</t>
+          <t>gwapo kon magtalikod</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>sa pag-adto gikan</t>
+          <t>nindot nga tan-awon gikan sa likod</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['nakalugsong']</t>
+          <t>['magtalikod']</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Nakalugsong na mi ug gidalit ang among mga ani sa lungsod.</t>
+          <t>Ang iyang amigo gwapo kon magtalikod, pero bati diay pagtan-aw sa iyang nawong.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Naglakaw mi sa bukid ug nakalugsong mi ngadto sa suba para maligo.</t>
+          <t>Nagpicture ko sa akong iro sa dagat, ug gwapo kon magtalikod kay nindot kaayo iyang itom nga balhibo sa likod.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>lamoy</t>
+          <t>gi-indian</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>pag-abot</t>
+          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>['lamoy']</t>
+          <t>['gi-indian']</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>"Lamoya nalang na imong gibuhat, walay gamit."</t>
+          <t>Si Juan gi-indian sa iyang kliyente sa ilang appointment.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>"Gi-lamoy sa bata ang dakong pan nakon."</t>
+          <t>Siya gidala sa pagtuon ang mga katigulangan nga gi-indian ni Magellan sa Sugbo kaniadto.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>bahong biyudo</t>
+          <t>ayaw pagbuot, lain-lain tag lubot</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>adunay kusog nga baho nga musky o balsam</t>
+          <t>ayaw ako isulti kon unsay buhaton</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>['bahong']</t>
+          <t>['pagbuot']</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Ang iyang sinina nga bahong biyudo kay dili nimo malapasan.</t>
+          <t>Lain-lain tag lubot, mao nga kinahanglan respetuhon ang desisyon sa uban.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nahibulong mi ngano'ng bahong biyudo siya apan wala diay siya'y asawa nga namatay.</t>
+          <t>Sa klase sa Biology, gitun-an namo nga lain-lain og porma ang lubot sa matag matang sa hayop.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>giprito sa kaugalingong mantika</t>
+          <t>kuwang sa tagad</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Alternatibo nga porma sa giluto sa kaugalingong mantika</t>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>['giprito']</t>
+          <t>['tagad']</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Si Juan giprito sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
+          <t>Si Pedro kuwang sa tagad, bisan unsa nga event ganahan magpakita.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nagluto si Maria ug isda nga giprito sa kaugalingong mantika aron mas lami ang timpla.</t>
+          <t>Ang tanom nga wa matagda, nagpakita og mga sintomas nga kuwang sa tagad sama sa mga dili hapsay nga dahon.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>agi sa bangag sa dagom</t>
+          <t>gigukod sa sudlay</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
+          <t>nga walay buhok</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>['agi', 'bangag']</t>
+          <t>['gigukod']</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ang ilang proyekto agi sa bangag sa dagom sa kalisod.</t>
+          <t>Si Pedro pirmi lang gigukod sa sudlay, bisan unsa nga event, dili mag-comb.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ipasulod ni Maria ang sinulid agi sa bangag sa dagom aron makatahi siya og sinina.</t>
+          <t>Anaa sa lamesa ang sudlay nga gigukod sa mga bata samtang nagdula sila.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>murag namatyag iring</t>
+          <t>makakutaw og utok</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>gigamit sa paghulagway sa usa ka tawo nga nagtangis nga nagtangis o nagtangis nga nagtangis</t>
+          <t>makapalibog</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['namatyag']</t>
+          <t>['makakutaw']</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>"Ang bata murag namatyag iring, hilak kaayo pagnalaya."</t>
+          <t>Ang explanation sa iyang professor makakutaw og utok kaayo.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ang iring sa atop murag namatyag iring, kusog kaayo ang pangubog.</t>
+          <t>Ang iyahang paghalo sa mainit nga supas makakutaw og utok kay wala pa man gud niupos ang kainit niini.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>sabong</t>
+          <t>pangatulig luwag</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>usa ka kompetisyon</t>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>['sabong']</t>
+          <t>['pangatulig']</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ang mga manok nga ipangsabong kay gipangandaman ug maayo.</t>
+          <t>"Pangatulig luwag imong mga plano, walay klaro."</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ang akong amahan mopalit og sabon sa merkado kay nahutdan na mi sa among balay.</t>
+          <t>Ang iyang pangatulig luwag kay naguba tungod sa karaan na kaayo nga kaldero.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>manira sa dalan</t>
+          <t>pangatulig luwag</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>aron magpabilin nga magmata hangtod sa gabii</t>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['pangatulig']</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>"Ayaw pag manira sa dalan, naa pa kay buhaton."</t>
+          <t>Ang iyang plano kay murag pangatulig luwag, walay klaro nga direksyon.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ang mga tindahan manira sa dalan matag alas-otso sa gabi-i.</t>
+          <t>"Human sila pagkutaw sa sabaw, nag-pangatulig luwag dayon aron limpyo ang gamit."</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kulang sa dukol</t>
+          <t>gwapo kon magtalikod</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>usa ka buangbuang nga tawo</t>
+          <t>nindot nga tan-awon gikan sa likod</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['dukol']</t>
+          <t>['magtalikod']</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Si Maria kulang sa dukol, pirmi lang magbulakbol.</t>
+          <t>Si Juan gwapo kon magtalikod, pero dili na kaayo pag-atubang.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ang bata kulang sa dukol sa iyang likod kay nagtambay ra sa duyan.</t>
+          <t>Nagkatawa si Ana kay ang iyang iro gwapo kon magtalikod sa iyang fluffy nga ikog.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>miulbo ang kaspa</t>
+          <t>mogawas ang pari nga walay ulo</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>sa pag-abli ngadto sa kasuko</t>
+          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['mogawas']</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Si Ana miulbo ang kaspa human nabal-an nga gilimbongan siya.</t>
+          <t>Mogawas ang pari nga walay ulo kuno kung aduna'y mamatay sa baryo.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Human sa dugang duha ka adlaw nga walay ligo, si Pedro nakabantay nga miulbo ang kaspa sa iyang ulo.</t>
+          <t>Sa halangdong sugilanon, kon malangan ang mga novena sa alas dose sa kagabhion, mosulod ang pari nga walay ulo sa simbahan ug mopahimangno sa mga tawo.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>gibati og kaanyag</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>prima donna</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['gibati']</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Ayaw na lang pagsabot ana, ipanabi na sa clouds.</t>
+          <t>Si Ana gibati og kaanyag, maong pirmi siya nagbuot-buot.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pagka-adlaw nga hayag, naglingkod si Maria sa atop ug gusto niyang pasundayag sa iyang gibati, busa iyang giingon sa iyang kaugalingon, "Ipanabi na sa clouds ang akong kalipay."</t>
+          <t>"Gibati gyud ni Carla og kaanyag sa iyang bag-ong sinina, maong nagpakita siya sa iyang mga higala."</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>lapos sa pikas dunggan</t>
+          <t>murag langaw nga nakatugdon sa kabaw</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>sa pagsulod sa usa ka dalunggan ug paggawas sa laing dalunggan</t>
+          <t>nouveau riche</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>['lapos', 'dunggan']</t>
+          <t>['nakatugdon']</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ang tambag sa iyang ginikanan lapos ra sa pikas dunggan.</t>
+          <t>"Si Ana, gikan sa pagka-pobre, murag langaw nga nakatugdon sa kabaw karon."</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Nakita namo ang gamay nga sungo nga giigo sa bala, naglapos gyud sa pikas dunggan.</t>
+          <t>"Nagtan-aw ko sa uma ug nakita nako nga murag langaw nga nakatugdon sa kabaw."</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>habwa ang kinaon</t>
+          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>pag-awhag</t>
+          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>['habwa', 'kinaon']</t>
+          <t>['dakpa']</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Si Pedro naghabwa ang kinaon kay nasuka.</t>
+          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, tan-awon nato unsay imong mahimo.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Naglimpyo si Maria sa kusina ug iyang gihabwa ang kinaon sa lamisa human sa ilang paniudto.</t>
+          <t>Naglingkod siya sa sala, dayon gisulti niya, "Kung wala kay lingaw sa kinabuhi, dakpa akong utot," samtang nangipi siya paglingaw-lingaw.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>bibingkang liki</t>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ang mga genital sa babaye</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>['liki']</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Si Pedro nagpakatawa sa mga barkada gamit ang bibingkang liki nga istorya.</t>
+          <t>Ang mga tawo giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nag-andam si Lola Maria og bibingkang liki alang sa Pasko.</t>
+          <t>Pag-abot sa panahon sa tig-ulan, diha ra jud sa patag magtapok ang tubig kay dili na mabalik ang baha paingon sa bukid.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ander de bunal</t>
+          <t>murag namiya og tai</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gi-squeeze</t>
+          <t>Usa ka tawo nga mibiya sa dili-iasa nga walay iyang pulong</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>['bunal']</t>
+          <t>['namiya']</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ang mga ander de bunal kay dili na maghunahuna sa ilang kaugalingong gusto.</t>
+          <t>"Si Ana murag namiya og tai, wala na gani nagpahibalo sa iyang mga plano."</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Si Andres kay nanghita og bunal ug gahapon gi-install niya ang iyang ander de bunal sa likod sa balay.</t>
+          <t>"Nakita nako si Tomas nga nagdali-dali padung sa banyo, murag namiya og tai."</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>baba sa atay</t>
+          <t>gilawog sa tirong</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ang diaphragm</t>
+          <t>sa pagbutang sa peligro sa usa ka tawo, ilabina</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>['baba']</t>
+          <t>['gilawog']</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ang mga tambal para sa baba sa atay kay kinahanglan sa pag-maintain sa maayong kondisyon.</t>
+          <t>Si Pedro gilawog sa tirong sa iyang kauban, maong nasakpan sa ilang boss.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>"Pagkalami gyud sa adobo nga akong giandam, labi na ang baba sa atay nga humok ug lami."</t>
+          <t>Gibantayan namo ang iring samtang gilawog namo kini sa tirong diha sa suba.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>molayag sa kalipay</t>
+          <t>mangayo og manghod</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>sa pagpakigsekso</t>
+          <t>usa ka kaso sa bata nga nag-asuso o nag-agom sa iyang mga tudlo</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>['molayag']</t>
+          <t>['mangayo']</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ang mga magkauban nagmolayag sa kalipay sa ilang outing sa beach.</t>
+          <t>Si Pedro nakakita sa iyang anak nga mangayo og manghod sa iyang tiil.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ang mga langgam nagmolayag sa kalipay sa kataas-kataas nga kahoy.</t>
+          <t>"Mangayo og manghod si Maria kay gusto siya ug uska mubo nga bunal sa nakatigulang."</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>dili na mabalik ang baha paingon sa bukid</t>
+          <t>gwapa kon magtalikod</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>nindot nga tan-awon gikan sa likod</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['magtalikod']</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ang mga estudyante nakabalo nga dili na mabalik ang baha paingon sa bukid, mao nga nagplano na sila pag-ayo.</t>
+          <t>Ang iyang kauban sa trabaho gwapa kon magtalikod, pero pag-atubang, dili na diay.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pagkahuman sa kusog nga ulan, ang mga taga-barangay nag-istorya nga bisan unsaon pa, dili na mabalik ang baha paingon sa bukid, kay daghan kaayo ang tubig nga midiretso sa dagat.</t>
+          <t>Sa daghan nilang mga selfie, gwapa kon magtalikod si Ana, apan mas gwapa pag-atubang.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>lamoy</t>
+          <t>mangayo og manghod</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>pag-abot</t>
+          <t>usa ka kaso sa bata nga nag-asuso o nag-agom sa iyang mga tudlo</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>['lamoy']</t>
+          <t>['mangayo']</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>"Si Ana, sige lang lamoy walay klaro."</t>
+          <t>Si Juan nalipay kay ang iyang baby nakakat-on nga mangayo og manghod.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>"Ang bata malipayon nga naglamoy sa iyang paborito nga tsokolate."</t>
+          <t>"Si Maria nangayo og manghod kay kini ang gipangita sa ilahang tapok."</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kirig</t>
+          <t>agi sa bangag sa dagom</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>pag-awhag</t>
+          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>['kirig']</t>
+          <t>['agi']</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Si Juan kirig sa kahadlok pagkakita sa aksidente.</t>
+          <t>Ang ilang relasyon agi sa bangag sa dagom sa daghang pagsulay.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Si Maria kirig samtang gidalikyat siya sa ospital tungod sa iyang sakit.</t>
+          <t>Ang karayom wala pa maagi ug hilo kay gahi jud ang pag-agi sa bangag sa dagom.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>duwa og panit</t>
+          <t>makabugto og panty</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>sa pag- masturba</t>
+          <t>pisikal o seksuwal nga madanihon</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>['duwa']</t>
+          <t>['makabugto']</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ang iyang mga kauban sa trabaho pirmi lang magbinuang ug magduwa og panit.</t>
+          <t>Si Pedro ganahan kaayo sa iyang uyab kay makabugto og panty.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ang mga bata nangita og bola aron makaduwa og panit sa basketball court.</t>
+          <t>Paglaba nako sa akong mga sinina, nasamad ang akong daliri tungod sa hugot nga elax na makabugto og panty.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>paabang</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>pag-abang</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['paabang']</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Kung gusto ka maabot ang imong damgo, ipanabi na sa clouds.</t>
+          <t>Ang ilang negosyo nga paabang og sakyanan kay booming na kaayo karon.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>"Ang mensahe gikan sa iyang email kay ipanabi na sa clouds para dali ra mag-access bisan asa."</t>
+          <t>Nagpaabang sila og kwarto sa ilang balay alang sa mga turista.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>babayeng ikogan</t>
+          <t>hunaw</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>transgender</t>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>['ikogan']</t>
+          <t>['hunaw']</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Si Ana nga babayeng ikogan kay walay klaro nga direksyon sa kinabuhi.</t>
+          <t>Si Maria naghunaw sa iyang mga sala aron dili siya mahatagan ug parusa.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ang babayeng ikogan sa sirkus mao'y nagdala og daghang tawo kay talagsaon siya.</t>
+          <t>Gihunaw ni Juan ang iyang mga kamot human sa pagkaon.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>manira sa dalan</t>
+          <t>lisod pukawon ang gamata</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>aron magpabilin nga magmata hangtod sa gabii</t>
+          <t>gigamit sa pagsulti sa nagmata o sa usa ka tawo nga dili magmata</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['pukawon']</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ang mga batan-on kasagaran manira sa dalan kung walay lingaw.</t>
+          <t>Lisod pukawon ang gamata, labi na kung bugnaw ang panahon.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ang tindero manira sa dalan kung udto kay init na kaayo.</t>
+          <t>"Nakita nako nga lisod pukawon ang gamata kay nagkatulog pa gyud siya ug maayo."</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>mura og halas nga nagluno</t>
+          <t>kirig</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga magbiya sa iyang mahugaw nga sinina sa tanang dapit sa balay</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>['nagluno']</t>
+          <t>['kirig']</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>"Ang silingan namo mura og halas nga nagluno, walay tarong pagbutang sa mga gamit."</t>
+          <t>Si Juan kirig sa kahadlok pagkakita sa aksidente.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ang among iring gibantayan kaayo ang halas nga nagluno sa halang nga sagbot sa among jardin.</t>
+          <t>Si Maria kirig samtang gidalikyat siya sa ospital tungod sa iyang sakit.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>ang baka nisulod sa kulon</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>gigamit sa pagsulti sa usa nga siya usa ka bakak o ikaw mahimo sa pagsulti sa laing nagbuwa</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['nisulod']</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ipanabi na sa clouds ang imong mga tinguha ug siguroha nga mo-trabaho ka para ana.</t>
+          <t>Ang pagplano nila nga walay klaro mura'g baka nga nisulod sa kulon.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nakita nako ang bata nga naglingkod sa atop sanglit gilabay niya ang iyang mensahe ug ipanabi na sa clouds.</t>
+          <t>Ang bata nalipay kay nakita niya nga ang baka nisulod sa kulon sa pagdula-dula.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>mag-ugbok og mohon</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>sa pagpakigsekso</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['mag-ugbok']</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Bisan unsa ka lisod, ipanabi na sa clouds ang imong mga pag-ampo.</t>
+          <t>Si Maria ug ang iyang bana mag-ugbok og mohon sa ilang balay.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Pagka gabii, among ipanabi na sa clouds ang among mga mensahe pinaagi sa drone nga adunay mga light display.</t>
+          <t>Ang mga trabahante mag-ugbok og mohon aron masugdan na ang pagtukod sa bag-ong balay.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>dula og panit</t>
+          <t>mag-ugbok og mohon</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>sa pag- masturba</t>
+          <t>sa pagpakigsekso</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>['dula']</t>
+          <t>['mag-ugbok']</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Si Juan dula og panit, pirmi lang magtambay ug magbuot-buot.</t>
+          <t>Si Pedro nagplano nga mag-ugbok og mohon human sa kasal.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Si Ana migamit og kutsilyo aron dulaon ang panit sa mansanas.</t>
+          <t>Ang mga mag-uuma mag-ugbok og mohon aron markahan ang yuta nga ilang bungahon.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>anak sa sala</t>
+          <t>ayaw pagbuot kay lain-lain ta og lubot</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>usa ka anak nga dili-konsejero</t>
+          <t>ayaw ako isulti kon unsay buhaton</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>['sala']</t>
+          <t>['pagbuot']</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ang anak sa sala kasagaran maglisod sa pagsulod sa mga respetadong institusyon.</t>
+          <t>Dili tanan magkauyon, kay lain-lain ta og lubot.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nagbisita ang pari sa balay ug giampo ang anak sa sala nga nakabaton og sakit.</t>
+          <t>Sa baki sa klase, si Ma'am Ana nagtudlo nga lain-lain ta og lubot depende sa atong klase sa pagkaon ug mga gawi.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>lapos sa pikas dunggan</t>
+          <t>agi sa bangag sa dagom</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>sa pagsulod sa usa ka dalunggan ug paggawas sa laing dalunggan</t>
+          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>['lapos', 'dunggan']</t>
+          <t>['agi']</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi lang lapos sa pikas dunggan ang mga lectures sa eskwela.</t>
+          <t>Si Pedro agi sa bangag sa dagom aron lang makapasar sa eksam.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Si Juan nagkagubot ang buhok kay naay langaw nga misulod sa iyang dunggan ug nilapos sa pikas dunggan.</t>
+          <t>Si Maria naglisod og pagsulod sa pisi agi sa bangag sa dagom samtang nagpanahi siya og sinina.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>kakha tuka</t>
+          <t>abot sa dunggan ang ngisi</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>kamot-sa-lubong</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>['kakha', 'tuka']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Si Juan pirmi lang kakha tuka, walay nahabilin nga budget.</t>
+          <t>Abot sa dunggan ang ngisi ni Lito pagkakita sa iyang paboritong artista.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ang maya nagkakha tuka sa nataran.</t>
+          <t>Nagpanglingo si Ana kay abot sa dunggan ang iyang ngisi sa paglingaw sa sayop nga katawa ni Juan.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>abot sa dalunggan ang ngisi</t>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>nga dili gayod malipay</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>['abot', 'dalunggan', 'ngisi']</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Pagkahuman sa eksam, abot sa dalunggan ang ngisi ni Juan kay nakapasar siya.</t>
+          <t>Si Ana nakasabot nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na sa iyang kinabuhi.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Nagtan-aw ko sa litrato nga gipakita ni Ana, abot sa dalunggan ang ngisi niya sa kalipay.</t>
+          <t>Human sa kusog nga ulan, nasayod na ang mga residente nga dili na gyud mabalik ang baha paingon sa bukid, busa nanginahanglan gyud silang mag-andam sa umaabot nga panahon.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ul-ol</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>sa pag- masturba Mga sinonim: batil</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>['ul-ol']</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ang iyang mga ul-ol nga istorya kay naghatag ug kalibog sa tanan.</t>
+          <t>Ang imong mga plano, ipanabi na sa clouds kay maabot ra na.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Juan miingon nga siya gikapoy human siya mag-ul-ol sulod sa iyang kwarto.</t>
+          <t>Ang detalye sa imong presentation, ipanabi na sa clouds aron ma-access sa tanan bisan asa pa.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>mangayo og manghod</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>usa ka kaso sa bata nga nag-asuso o nag-agom sa iyang mga tudlo</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>['mangayo']</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ang mga bata nga mangayo og manghod kasagaran mga healthy nga bata.</t>
+          <t>Ang imong mga pangandoy, ipanabi na sa clouds aron matinuod.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ang magtiayon midesisyon nga mangayo og manghod kay gusto nila dungagan ang ilang pamilya.</t>
+          <t>Gusto nakong ipaabot ang akong mensahe sa mga higala ko nga naa sa layo, mao nga ipanabi na sa clouds pinaagi sa teknolohiya.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>duwa og panit</t>
+          <t>gi-indian</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>sa pag- masturba</t>
+          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>['duwa']</t>
+          <t>['gi-indian']</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Si Maria naglagot kay si Juan pirmi lang magduwa og panit bisan kinahanglanon siya.</t>
+          <t>Si Pedro gi-indian sa iyang uyab sa ilang sabot nga date.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Nagpraktis ang mga bata nga magduwa og panit para sa ilang teatro sa eskuwela.</t>
+          <t>Wala moabot si Miguel sa ila nahuman nga sabot, kay gi-indian man siya sa Mindanao para magtuon sa mga lumad nga Indian didto.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>hilawas</t>
+          <t>kapugngan pa ang baha, dili ang biga</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>coitus</t>
+          <t>dili mapugngan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['kapugngan']</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Ang hilawas nga kinabuhi kay wala'y klaro nga padulngan.</t>
+          <t>Ang iyang kalagot dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>"Nagkinahanglan ang bata og hilawas nga panginahanglanon arun maatiman ang iyang kalawasan."</t>
+          <t>Sa kadako sa kusog sa ulan, kapugngan pa ang baha, dili ang biga nga gihunahuna sa mga tao.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>tuslok baki</t>
+          <t>buotan ra og matulog</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>usa ka dula</t>
+          <t>malinong</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>['tuslok']</t>
+          <t>['matulog']</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ang mga bata nagpraktis sa tuslok baki aron mahimong champion sa dula.</t>
+          <t>Ang iyang anak buotan ra og matulog, kay pirmi lang mangaway sa mga silingan.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>"Nakit-an nako si Lito nga nagkuha og sungkod aron magtuslok baki sa daplin sa sapa."</t>
+          <t>Gabiina na kaayo ug buotan ra og matulog ang bata sa ilang kwarto.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>manakop og ligid</t>
+          <t>taliba</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>nga ang usa ka tawo naugtang sa usa ka sakyanan</t>
+          <t>ang mga genital sa babaye</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>['manakop', 'ligid']</t>
+          <t>['taliba']</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Si Pedro manakop og ligid kay nagdagan-dagan sa kalsada.</t>
+          <t>Ang mga pulis nag-taliba sa mga salida aron protektahan ang mga bisita.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nagdula mi og dakop-dakop sa plaza unya nakalingkod ko para mopahuway, apan kalit nga miingon ang akong amigo nga manakop og ligid mi sa mga sakyanan nga nag-agi atubangan sa balay.</t>
+          <t>Ang taliba nagsugod ug talagsaon nga lihok human sa pagkahuman sa operasyon.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kulang sa dukol</t>
+          <t>pasok, Luningning</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>usa ka buangbuang nga tawo</t>
+          <t>miingon sa kaugalingon sa dihang pag-poking sa usa sa iyang mga winnings sa usa ka dula sa mga kard</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>['dukol']</t>
+          <t>['pasok']</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Si Pedro kulang sa dukol, maong pirmi lang magbinuang.</t>
+          <t>Pasok, Luningning, ug paminawa ang mga instructions.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ang bata kulang sa dukol, mao nga ipatuli pa siya karong bulan para sakto ug kompleto.</t>
+          <t>"Pasok, Luningning, kay naghulat na ang imong amahan sa kusina."</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>hilawas</t>
+          <t>sabong</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>coitus</t>
+          <t>usa ka kompetisyon</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['sabong']</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ang hilawas nga relasyon sa diha nga walay commitment kay lisod.</t>
+          <t>Ang sabong sa mga manok kay paborito nga pastime sa mga kalalakin-an.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nagkinahanglan ko ug hilawas nga pagkaon aron magpabiling lig-on ug himsog ang lawas.</t>
+          <t>Nagbutang kog tubig ug sabong sa palanggana para sa laba.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>bahong biyuda</t>
+          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>adunay kusog nga baho nga musky o balsam</t>
+          <t>kitang tanan magkamali</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>['bahong', 'biyuda']</t>
+          <t>['naay', 'masipyat']</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Si Juan bahong biyuda kay wala gyud maligo ug maayo.</t>
+          <t>Si Pedro nasipyat sa exam, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ang akong silingan nga si Maria, nga dugay nang biyuda, miingon nga dili siya gusto og bahong biyuda sa iyang sinina.</t>
+          <t>Sa among bukid, nakita nako nga bisan ang kabaw nga naay upat ka tiil masipyat ug mulakaw diha sa dili patag nga dalan.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>pabuto</t>
+          <t>tuslok baki</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>usa ka patok</t>
+          <t>usa ka dula</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>['pabuto']</t>
+          <t>['tuslok']</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Ang mga bata malipay kaayo sa mga pabuto kada New Year.</t>
+          <t>Ang mga bata nagpraktis sa tuslok baki aron mahimong champion sa dula.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Nagpalit kami og daghang pabuto para sa pista sa baryo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>hilawas</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>coitus</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Ang mga tawo nga maghilawas kay kasagaran mahadlok magcommit.</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Ang lami sa hilawas nga prutas kay wala'y sama.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>paabang</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>pag-abang</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Gipahimutang ang iyang balay aron ipaabang sa mga bakasyonista.</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Nagpaabang sila og mga bisekleta alang sa mga bisita sa park.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>manakop og ligid</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>nga ang usa ka tawo naugtang sa usa ka sakyanan</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>['manakop', 'ligid']</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>"Manakop og ligid kaayo imong mga plano, walay klaro."</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Si Juan ug iyang mga amigo nagsabot nga manakop og ligid alang sa ilang bag-ong negosyo nga vulcanizing shop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>manglutasay</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>usa ka manunulak sa mga bukog</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>['manglutasay']</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Ang iyang kauban sa trabaho manglutasay sa mga kabataan.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Ang mga bata nagdula sa ilalom sa manglutasay aron magpa-uyog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>mag-ihaw og lata</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>sa pagluto sa mga pagkaon nga tinago</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>['mag-ihaw']</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Si Juan pirmi lang mag-ihaw og lata sa boarding house.</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Gikuha ni Pedro ang kalaha aron mag-ihaw og lata sa ilang umahan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Maglakaw sa paghisgot</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>['buhat', 'pasulti-on', 'sulti', 'pabuhaton']</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Si Pedro nagpakita nga maayo siya sa trabaho, buhat ang pasulti-on dili sulti ang pabuhaton.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Gisuwayan ni Juan nga i-assemble ang kabayo-kabayo nga laruan gamit ang manual, buhat ang pasulti-on dili sulti ang pabuhaton.</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>kitang tanan magkamali</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>['naay', 'masipyat']</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Si Ana nakasala sa iyang trabaho, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Naglakaw-lakaw ang kabaw sa uma, apan bisan ang kabaw nga naay upat ka tiil masipyat, natapilok siya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>makamala og sapa</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>ang usa ka tawo nga may dagkong tiil</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>['makamala']</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Si Maria nagkatawa kay ang iyang igsuon makamala og sapa sa kadako sa tiil.</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Ang mga trabahante nagkinahanglan og kahoy nga makamala og sapa aron makabalhin ang mga gamit ngadto sa pikas nga pampang.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>pangatulig luwag</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Ang iyang giingon kay murag pangatulig luwag, dili ko kasabot.</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Nag-uban mi sa kusina, ug gi-pangatulig luwag nako ang sinugba aron dili masunog.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>halinon og aping</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>maayo kaayo nga hitsura</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>['halinon']</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Ang mga artista kasagaran halinon og aping tungod sa ilang hitsura.</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Ang iring namo halinon og aping tungod kay kanunay kini gihapuhap sa among pamilya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>abot na sa dukot</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>pag-iskrabe sa ubos sa bariles</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>['abot', 'dukot']</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Ang iyang mga problema murag abot na sa dukot, grabe na kaayo.</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Nagkuha ko og sud-an sa kaldero, pero kinahanglan gyud nga aboton ang dukot aron mahurot ang kan-on.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>kuyog baboy</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>usa ka tagalong</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>['kuyog']</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Ang mga tawo nga kuyog baboy kasagaran magpalisod sa ilang mga kauban.</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Miadto sila sa umahan uban sa ilang kuyog baboy nga gihiktan sa usa ka pisi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>pabuto</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>usa ka patok</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>['pabuto']</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Ang iyang surprise party kay murag pabuto nga naka-shock sa tanan.</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Nagpalit mi ug daghang pabuto alang sa selebrasyon sa Bag-ong Tuig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>ang baka nisulod sa kulon</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>gigamit sa pagsulti sa usa nga siya usa ka bakak o ikaw mahimo sa pagsulti sa laing nagbuwa</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>['nisulod']</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Ang ilang proyekto nga walay direksyon mura'g baka nga nisulod sa kulon.</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Ang baka sa among uma nisulod sa dakong kulon sa kusina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>gidaman</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>sa pag-aturog o pag-aturog</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>['gidaman']</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>"Gidaman na ba ka? Daghan kaayo kag opinion."</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Pagka-buntag, iyang mama miingon nga kagabii, gidaman diay siya ug naglakaw-lakaw sa sulod sa kwarto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>hinaw</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>sa paghunaw sa kamot sa usa o sa uban</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>['hinaw']</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Si Pedro naghinaw sa iyang responsibilidad pagkahuman sa proyekto.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Si Maria naghinaw sa iyang mga kamot human mokaon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>bahong biyuda</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>adunay kusog nga baho nga musky o balsam</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>['bahong', 'biyuda']</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Si Pedro bahong biyuda kay bisan unsaon ug ligo, dili mawala ang baho.</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Ang silingan nagreklamo tungod kay ang tambong nga pagkahuman sa lamay sa hintungdan nga bahong biyuda pa gihapon hangtod karon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>baba sa atay</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>ang diaphragm</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>['baba']</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Ang pag-amping sa baba sa atay usa ka importante nga parte sa pag-atiman sa lawas.</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Gisuwayan ni Pedro pagkat-on ang posisyon sa baba sa atay sa klase sa anatomiya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>babayeng ikogan</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>transgender</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>['ikogan']</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Si Pedro kay permi magbuang sa mga babayeng ikogan.</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Ang mga sinuwaki nangga atong nakita kay babayeng ikogan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>ander de bunal</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>gi-squeeze</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>['bunal']</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Si Pedro kay ander de bunal, kay pirmi lang musunod sa iyang asawa bisan unsa pa.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Ang bata nakuyawan pagkahuman nga ander de bunal siya sa iyang amahan tungod sa iyang pagkabadlong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>gwapa kon magtalikod</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>['magtalikod']</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Si Maria pirmi lang ginatawgon nga gwapa kon magtalikod sa iyang mga amigo.</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Pag-gawas ni Ana sa kwarto, giingnan siya sa iyang igsoong nga gwapa kon magtalikod kay nindot ang pagkasul-ot sa iyang sanina.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>abot sa pikas bukid</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>usa ka tawo nga naghisgot nga makusog</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>['abot']</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Ang iyang reklamo abot sa pikas bukid, grabe kaayo ug kasaba.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Migawas si Ana kada buntag aron mananom, ug dal-on niya ang iyang mga produkto abot sa pikas bukid alang sa pagbaligya.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>kapugngan pa ang baha, dili ang biga</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>dili mapugngan</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Ang iyang determinasyon dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Nagbungkag ang dakong kusog sa biga sa panagdait sa baryo, kapugngan pa ang baha, dili ang biga nga nagdala og kagubot sa mga tawo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>ul-ol</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>sa pag- masturba Mga sinonim: batil</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>['ul-ol']</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Ang mga ul-ol nga tawo kasagaran dili makuha ang tinuod nga punto.</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Naghilum siya sa kwarto ug nag-ul-ol sa dihang walay tawo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>gigukod sa plansa</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>['gigukod']</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Ang iyang sinina pirmi lang gigukod sa plansa, maong bati tan-awon.</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Ang bata mikatawa samtang gigukod sa plansa ang eroplano nga iyang gihimo gikan sa papel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>gwapa kon magtalikod</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>['magtalikod']</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Ang mga tao nga gwapa kon magtalikod kasagaran maulaw kung mag-atubang.</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>"Si Ana gwapa kon magtalikod kay nindot ug straight ang iyang buhok."</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>dili tanang butang sili nga mohalang dayon</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Dili tanan mahitabo sa usa ka higayon</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>['butang', 'mohalang']</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Ang mga tawo nga dili tanang butang sili nga mohalang dayon kasagaran magmalampuson sa ilang mga plano.</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Nagpalit siya og daghang klase sa sili sa merkado, pero nakadiskubre siya nga dili tanang butang sili nga mohalang dayon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>kusog mokaon og gasolina</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>gas-gussing</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>['mokaon']</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Si Maria dili ganahan ug sakyanan nga kusog mokaon og gasolina kay mahal ang maintenance.</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Ang bag-ong makina nga gisulayan nila sa laboratoryo kusog mokaon og gasolina sa paspas nga dagan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>mag-ugbok og mohon</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>sa pagpakigsekso</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>['mag-ugbok']</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Ang magtiayon nagdecide nga mag-ugbok og mohon sa ilang honeymoon.</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Ang mga trabahante mag-ugbok og mohon para sa bag-ong balay nga tukoron.</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>murag namiya og tai</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Usa ka tawo nga mibiya sa dili-iasa nga walay iyang pulong</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>"Si Pedro murag namiya og tai, wala na gani nagpahibalo sa iyang mga kauban."</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Pagkahuman kaon sa iyang pamahaw, si Jun-jun murag namiya og tai kay dali-dali nga midagan paingon sa kasilyas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>kulang sa tagad</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>['tagad']</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Si Maria kulang sa tagad, pirmi lang magbinuang aron makuha ang atensyon sa iyang mga kauban.</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Ang balay ni Lolo ug Lola kulang sa tagad, mao nga hapit na mapapas ang ilang pintal ug nagkinahanglan na’g bag-ong kisame.</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>ang kalimot walay gahom</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Ang pagkalimtan dili makahatag kanimo ug wala ka kaayohan</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Ang mga estudyante nga malimot maglisod sa exam, ang kalimot walay gahom.</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Naa koy gipangita sa akong mga gamit, apan murag ang kalimot walay gahom, kay di man gihapon nako makita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>kuskos balungos</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>pag-awhag</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>['kuskos']</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Si Pedro pirmi lang kuskos balungos sa iyang trabaho.</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Nagkuhaan si Maria ug dali nga kuskos balungos aron limpyohan ang lamesa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>gidaman</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>sa pag-aturog o pag-aturog</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>['gidaman']</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>"Kung mangutana ka og ing-ana, murag gidaman ka."</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Pagmata nako sa buntag, nakita nako ang akong igsoon nga gidaman ug naglakaw-lakaw sa sala.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>basa og baba</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>mabangis</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>['baba']</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Si Juan basa og baba ug permi magdala ug kasaba sa opisina.</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Nagbasa og baba si Maria samtang nagbasa sa iyang paborito nga libro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>bibingkang liki</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>ang mga genital sa babaye</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>['liki']</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Ang bibingkang liki kay uso kaayo sa mga binuang ug katawa sa mga barkada.</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Gipalit nako ang bibingkang liki sa merkado kay paborito gyud ni nako nga pagkaon.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>magtumba og baka</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>sa pag-ihaw sa usa ka vaca</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>['magtumba']</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Ang ilang pamilya magtumba og baka kung naa’y dako nga celebration.</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Ang manggugubat magtumba og baka para sa karne nga ilang ipamaligya sa merkado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>walay mahay nga gauna</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>['mahay']</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>Si Pedro nakasabot nga walay mahay nga gauna, mao nga nagmatngon siya sa iyang mga desisyon.</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Nagbasa si Ana ug libro ug nakahuna-huna, "Walay mahay nga gauna," samtang nagtan-aw siya sa mga mahay sa mga bakante nga panid sa sinugdanan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>manira sa dalan</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>aron magpabilin nga magmata hangtod sa gabii</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>"Si Ana, sige lang manira sa dalan walay klaro."</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>"Ang mga estudyante manira sa dalan aron dili maligsan samtang nagduwa."</t>
+          <t>"Nakit-an nako si Lito nga nagkuha og sungkod aron magtuslok baki sa daplin sa sapa."</t>
         </is>
       </c>
     </row>

--- a/Dataset/Test_Set.xlsx
+++ b/Dataset/Test_Set.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,3294 +458,3240 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dula og panit</t>
+          <t>makabuhi og patay</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sa pag- masturba</t>
+          <t>usa ka makapatikod nga bakak o sugilanon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['dula']</t>
+          <t>['makabuhi', 'patay']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Si Maria nagbuot-buot kay gusto siya magdula og panit pirmi.</t>
+          <t>Ang mga tawo nga makabuhi og patay kasagaran maayo kaayo moistorya.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ang akong manghod nagdula og panit sa iyang baboy-baboy nga dulaan.</t>
+          <t>Ang gahum sa dios makaayo ug makabuhi og patay.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>murag gitilapan og iring</t>
+          <t>hangyo lubo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>walay sapayan</t>
+          <t>usa ka hangyo nga gihimo sa ingon nga paagi nga dili kini makalikay</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['gitilapan']</t>
+          <t>['hangyo', 'lubo']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>"Ang iyang mga gamit sa opisina murag gitilapan og iring, limpyo ug hapsay."</t>
+          <t>Ang mga tawo nga hangyo lubo kasagaran magmalampuson sa ilang mga plano.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>"Pagkakita nako sa lamisa, murag gitilapan og iring kay walay tanang bahaw nga niwangig."</t>
+          <t>"Ang bata miadtos sapa ug nangayo og hangyo lubo sa iyang amahan nga lumos siya sa tubig."</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>litik</t>
+          <t>molayag sa kalipay</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sa pag-aghat sa tudlo</t>
+          <t>sa pagpakigsekso</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['litik']</t>
+          <t>['molayag']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga naglitik sa ilang mga pangandoy kasagaran magmalampuson.</t>
+          <t>Ang mga kabatan-onan nagmolayag sa kalipay human sa ilang graduation.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Naglingkod si Juan sa lamisa ug kalit niyang gilitik ang botelya nga nagbarog.</t>
+          <t>Ang barko nagmolayag sa kalipay samtang musubang ang adlaw sa dagat.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gi-indian</t>
+          <t>ul-ol</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
+          <t>sa pag- masturba Mga sinonim: batil</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['gi-indian']</t>
+          <t>['ul-ol']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ang iyang kauban sa trabaho gi-indian siya sa ilang meeting.</t>
+          <t>Ang mga ul-ol nga tawo kasagaran dili makuha ang tinuod nga punto.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ang tribo nga among gi-adtoan sa bukid, gi-indian sa mga lumad.</t>
+          <t>Naghilum siya sa kwarto ug nag-ul-ol sa dihang walay tawo.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pangatulig luwag</t>
+          <t>kulang sa tagad</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['pangatulig']</t>
+          <t>['tagad']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"Ayaw pag pangatulig luwag, klaroha imong mga desisyon."</t>
+          <t>Ang iyang amiga kulang sa tagad, maong pirmi lang mag-agi-agi sa ilang lugar.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nagpangatulig luwag ang bata tungod kay busog kaayo siya human mikaon og daghang lugaw.</t>
+          <t>Gamay ra gyud si Juan og kahibalo sa pag-atiman, mao nga kulang siya sa tagad sa iyang mga tanom.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hatod og patay</t>
+          <t>makawat</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sa pagtambong sa usa ka paglubong o seremonya sa paghinumdom</t>
+          <t>mahimong ma-stolen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['hatod', 'patay']</t>
+          <t>['makawat']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga hatod og patay kasagaran nagpakita ug respeto sa namatay.</t>
+          <t>Ang anak ni Juan makawat, bisan kinsa ra magpadede niya.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ang drayber mihangyo nga tabangan siya sa paghatod og patay ngadto sa sementeryo.</t>
+          <t>Si Pedro nakamatikod nga ang iyang pitaka makawat sa mata sa kawatan.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hunaw</t>
+          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+          <t>gigamit nga isulti sa usa ka tawo nga imong gilimbongan sila sa pagtan-aw sa usa ka piho nga direksyon</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['hunaw']</t>
+          <t>['pagtan-aw, kitkit, paglingi']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ang iyang kauban naghunaw sa mga problema aron dili siya maapil.</t>
+          <t>paglingi, kitkit bungi sa kadaghan sa problema.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nagpareha sila paghuman sa trabaho ug naghunaw sa ilang kamot sa kusina aron limpyo.</t>
+          <t>Naglingi siya kay gusto niyang makita unsay iyang gipakita, apan pagtuyok, nakita ra diay niyang kitkit langaw ug bungi.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ul-ol</t>
+          <t>lamoy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sa pag- masturba Mga sinonim: batil</t>
+          <t>pag-abot</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['ul-ol']</t>
+          <t>['lamoy']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ang iyang buhat kay ul-ol kaayo, wala gyud maghunahuna.</t>
+          <t>"Lamoy kaayo ka, bisan asa nalang dapita."</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Migawas sa ilang klase, nag-ul-ol siya sa ilang balay alang sa pagkat-on sa leksyon.</t>
+          <t>"Gi-lamoy niya ang dagkong piraso sa lechon sa pista."</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nadakpan na</t>
+          <t>kulang sa dukol</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gisultihan sa usa ka tawo nga adunay bag-ong buhok</t>
+          <t>usa ka buangbuang nga tawo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['nadakpan']</t>
+          <t>['dukol']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nadakpan na si Pedro nga nagsige ug pangawat sa tindahan.</t>
+          <t>Si Pedro kulang sa dukol, maong pirmi lang magbinuang.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nadakpan na ang kawatan nga nisulod sa balay gabii.</t>
+          <t>Ang bata kulang sa dukol, mao nga ipatuli pa siya karong bulan para sakto ug kompleto.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>paabang</t>
+          <t>gisulod sa bulsa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pag-abang</t>
+          <t>sa paglimbong</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['paabang']</t>
+          <t>['gisulod']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ang mga kwartong ipaabang kay dali ra kaayo mahurot ug ma-book.</t>
+          <t>Ang mga tawo nga masaligan kasagaran dili gisulod sa bulsa.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>"Nagpaabang sila sa ilang balay samtang nagbakasyon."</t>
+          <t>Gisulod niya ang kaugalingon niyang kamot sa bulsa aron kuhaon ang iyang sinsilyo.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gigukod sa sudlay</t>
+          <t>ninja ray mopatay ninjo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nga walay buhok</t>
+          <t>usa ka pulong nga nag-aplay sa Leyte ug Boholano nga mga dialekto sa Cebuano</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['gigukod']</t>
+          <t>['mopatay']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Si Ana pirmi lang gigukod sa sudlay, kay dili siya ganahan mag-comb sa iyang buhok.</t>
+          <t>Sa kalit nga pag-agi, ninja ray mopatay ninjo nga wala moy kalibutan.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Si Maria naglupad-lupad ang buhok samtang gigukod sa sudlay sa iyang manghod.</t>
+          <t>Ang mga ninja sa karaang Hapon, matag pusil ug espada, ninja ray mopatay ninjo sa ilang kahanas ug kaisog.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
+          <t>abot sa dunggan ang ngisi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maglakaw sa paghisgot</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['pasulti-on, pabuhaton']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Si Juan giingnan nga buhat ang pasulti-on dili sulti ang pabuhaton sa iyang trabaho.</t>
+          <t>Abot sa dunggan ang ngisi ni Manang Ines pagkakita sa iyang mga apo.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>"Sa klase sa sining, gipahimo sa maestro ang mga estudyante ug kaugalingong mga proyekto aron buhat ang pasulti-on dili sulti ang pabuhaton."</t>
+          <t>Gani, abot sa dunggan ang ngisi ni Juan kay naputlan siya ug tabil sa iyang ngipon.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>abot sa pikas bukid</t>
+          <t>walay man kardaba mamunga og tundan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>usa ka tawo nga naghisgot nga makusog</t>
+          <t>ang mansanas dili mahulog nga layo sa kahoy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['abot']</t>
+          <t>['mamunga']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ang istorya ni Pedro abot sa pikas bukid bisan dili tinuod.</t>
+          <t>Ang mga tawo giingnan nga walay man kardaba mamunga og tundan, mao nga magmatngon sila sa ilang mga buhaton.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Naglakaw mi ug dugay hangtod nga among naabtan ang pikas bukid.</t>
+          <t>Sa among umahan, makita gyud nimo nga walay man kardaba mamunga og tundan bisan unsaon pa nimo pagsulay.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>miulbo ang kaspa</t>
+          <t>lapas na sa kalendaryo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sa pag-abli ngadto sa kasuko</t>
+          <t>usa ka tawo nga kapin sa 31 ka tuig ang edad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['miulbo']</t>
+          <t>['lapas']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Si Ana miulbo ang kaspa human nabal-an nga gilimbongan siya.</t>
+          <t>Si Juan lapas na sa kalendaryo, pero wala gihapon magtarong sa kinabuhi.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Human sa dugang duha ka adlaw nga walay ligo, si Pedro nakabantay nga miulbo ang kaspa sa iyang ulo.</t>
+          <t>Ang petsa sa among kasal karong tuiga lapas na sa kalendaryo, mao nga kinahanglan na gyud namo magsugod og plano.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>pangatulig luwag</t>
+          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+          <t>Maglakaw sa paghisgot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['pangatulig']</t>
+          <t>['pasulti-on, pabuhaton']</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"Pangatulig luwag kaayo imong mga istorya, walay klaro."</t>
+          <t>Ang mga estudyante giingnan nga buhat ang pasulti-on dili sulti ang pabuhaton sa ilang proyekto.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sa pagkahuman sa panihapon, gikuha ni Lola ang pangatulig luwag aron masimhot ang baho sa nilung-ag nga mais.</t>
+          <t>Ang maestro nag-ingon nga sa atong klase, buhat ang pasulti-on dili sulti ang pabuhaton, busa ginabarog kini sa iyang mga aksyon pinaagi sa pagpakita unsaon gyud kini pagtrabaho.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dili na mabalik ang baha paingon sa bukid</t>
+          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['dakpa']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ang mga estudyante nakabalo nga dili na mabalik ang baha paingon sa bukid, mao nga nagplano na sila pag-ayo.</t>
+          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, aron malingaw ka sa kinabuhi.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pagkahuman sa kusog nga ulan, ang mga taga-barangay nag-istorya nga bisan unsaon pa, dili na mabalik ang baha paingon sa bukid, kay daghan kaayo ang tubig nga midiretso sa dagat.</t>
+          <t>Pagmata nako sa buntag, nangutana akong igsoon kung unsa'y akong buhaton. Gisulti nako siya nga, "Kung wala kay lingaw sa kinabuhi, dakpa akong utot," kay lingaw man siya mangdakop.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>manira sa dalan</t>
+          <t>giprito sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>aron magpabilin nga magmata hangtod sa gabii</t>
+          <t>Alternatibo nga porma sa giluto sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['manira']</t>
+          <t>['giprito']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>"Ayaw pag manira sa dalan, klaroha imong mga desisyon."</t>
+          <t>Ang iyang kauban giprito sa kaugalingong mantika sa iyang mga sala.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>"Ang negosyante manira sa dalan aron duna sila'y halin bisan sa gabii."</t>
+          <t>Nag-andam si Maria sa isda ug giprito kini sa kaugalingong mantika.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>gilawog sa tirong</t>
+          <t>magpalapad og papel</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sa pagbutang sa peligro sa usa ka tawo, ilabina</t>
+          <t>aron magbaton ug dungog sa buhat sa uban</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['gilawog']</t>
+          <t>['magpalapad']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Si Juan gilawog sa tirong, bisan wala siya naghimo sa sayop.</t>
+          <t>Ang mga tawo nga magpalapad og papel kasagaran dili tinood nga maayong magtrabaho.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ang ilaga gilawog sa tirong aron kini dali madakop.</t>
+          <t>Ang mga bata sa klase nagpalapad og papel gamit ang pintal para sa ilang proyekto sa arte.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>murag namatyag iring</t>
+          <t>gwapo kon magtalikod</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gigamit sa paghulagway sa usa ka tawo nga nagtangis nga nagtangis o nagtangis nga nagtangis</t>
+          <t>nindot nga tan-awon gikan sa likod</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['namatyag']</t>
+          <t>['magtalikod']</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>"Ang bata murag namatyag iring, hilak kaayo pagnalaya."</t>
+          <t>Si Pedro pirmi lang ginatawgon nga gwapo kon magtalikod sa iyang barkada.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ang iring sa atop murag namatyag iring, kusog kaayo ang pangubog.</t>
+          <t>Naglingkod ko sa luyo ni Juan, ug nasurprisa ko kay gwapo kon magtalikod tungod sa iya maayong tindog.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>manglutasay</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>usa ka manunulak sa mga bukog</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['manglutasay']</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ang iyang kauban sa trabaho manglutasay sa mga kabataan.</t>
+          <t>Kung gusto ka maabot ang imong damgo, ipanabi na sa clouds.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ang mga bata nagdula sa ilalom sa manglutasay aron magpa-uyog.</t>
+          <t>"Ang mensahe gikan sa iyang email kay ipanabi na sa clouds para dali ra mag-access bisan asa."</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>habwa ang kinaon</t>
+          <t>sabong</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pag-awhag</t>
+          <t>usa ka kompetisyon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['habwa', 'kinaon']</t>
+          <t>['sabong']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Si Maria naghabwa ang kinaon kay nagkalibanga.</t>
+          <t>Ang mga sabong nagpakita sa abilidad sa mga magmamantala ug pag-atiman sa ilang mga manok.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Naghabwa ang bata sa kinaon gikan sa basket aron ipakaon sa mga iro.</t>
+          <t>Ang akong amahan ug ang iyang mga higala kanunay moadto sa sabungan matag Domingo aron mutan-aw og sabong.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gadalag ulan</t>
+          <t>kuyog baboy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>usa ka lalaki nga homoseksual</t>
+          <t>usa ka tagalong</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['nagdala']</t>
+          <t>['kuyog']</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga gadalag ulan kasagaran naglisod sa pagdawat sa uban.</t>
+          <t>Ang mga tawo nga kuyog baboy kasagaran magpalisod sa ilang mga kauban.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ang itom nga panganod sa langit gadalag ulan nga kusog kaayo.</t>
+          <t>Miadto sila sa umahan uban sa ilang kuyog baboy nga gihiktan sa usa ka pisi.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kuskos-balungos</t>
+          <t>kusog mokaon og gasolina</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>alternatibong pagsulat sa kuskos balungos</t>
+          <t>gas-gussing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['kuskos']</t>
+          <t>['mokaon']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Si Ana pirmi lang kuskos-balungos kung naay buhaton nga dili siya ganahan.</t>
+          <t>Ang sakyanan ni Juan kusog mokaon og gasolina, maong mahal kaayo ang gasto.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Gikuha ni Maria ang kutsilyo ug gigamit kini alang sa kuskos-balungos sa kinay sa isda.</t>
+          <t>Ang makina kusog mokaon og gasolina, dili na hinuon kini angay gamitan kay sayang kaayo.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>taliba</t>
+          <t>litik</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ang mga genital sa babaye</t>
+          <t>sa pag-aghat sa tudlo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['taliba']</t>
+          <t>['litik']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ang mga guwardiya nag-taliba sa building adlaw ug gabii.</t>
+          <t>Si Juan naglitik sa iyang mga kalagot sa iyang kauban.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ang taliba sa eskuylahan nagreport nga walay kakulian ang mga estudyante karong adlawa.</t>
+          <t>Si Ana naglitik sa abog sa lamesa gamit ang iyang tudlo.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>manakop og ligid</t>
+          <t>ayaw adto og gubat kon wala kay bala</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nga ang usa ka tawo naugtang sa usa ka sakyanan</t>
+          <t>ayaw pagbuhat ug dili-andam</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['manakop']</t>
+          <t>['adto']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Si Pedro manakop og ligid kay nagdagan-dagan sa kalsada.</t>
+          <t>Si Pedro giandam ang tanan sa pag-adto sa exam, ayaw adto og gubat kon wala kay bala.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Nagdula mi og dakop-dakop sa plaza unya nakalingkod ko para mopahuway, apan kalit nga miingon ang akong amigo nga manakop og ligid mi sa mga sakyanan nga nag-agi atubangan sa balay.</t>
+          <t>Nag-ingon si Tatay nga ayaw adto og gubat kon wala kay bala kay delikado kaayo.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>buhat ang pasulti-on dili sulti ang pabuhaton</t>
+          <t>nadakpan na ba ang nagtupi nimo</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Maglakaw sa paghisgot</t>
+          <t>gisultihan sa usa ka tawo nga adunay bag-ong buhok</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['pasulti-on, pabuhaton']</t>
+          <t>['nadakpan, nagtupi']</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga buhat ang pasulti-on dili sulti ang pabuhaton kasagaran magmalampuson.</t>
+          <t>Nadakpan na ba ang nagtupi nimo nga wala man nindot imong buhok?</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Si Mario ang nagtrabaho sa proyekto, mao nga buhat ang pasulti-on dili sulti ang pabuhaton aron klaro ang panabang.</t>
+          <t>Gidala dayon siya sa istasyon sa pulis ug giingnan nga "Nadakpan na ba ang nagtupi nimo nga wala man mangayo og permiso?"</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>lunod patay</t>
+          <t>magtumba og baka</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dihard</t>
+          <t>sa pag-ihaw sa usa ka vaca</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['lunod', 'patay']</t>
+          <t>['magtumba']</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ang iyang amigo lunod patay sa iyang pagtuo bisan pa sa mga pagsulay.</t>
+          <t>Si Juan nagplano nga magtumba og baka para sa birthday sa iyang anak.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ang sakayan ilang gisakyan nasangit sa dagkong balod, ug nahinumdom ko sa babaye nga lunod patay sa ubos sa dagat.</t>
+          <t>Sa dihang nasuko kaayo ang mga bata, ilang gipangbuhat nga magtumba og baka sa luyo sa duyan-duyan aron manabla sa ilang kalagot.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>manira sa dalan</t>
+          <t>toyi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>aron magpabilin nga magmata hangtod sa gabii</t>
+          <t>coitus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['manira']</t>
+          <t>['toyi']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi manira sa dalan kada gabii.</t>
+          <t>Ang mga istorya nila bahin sa toyi kay walay kinutuban nga katawa.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Si Juan manira sa dalan aron mabantayan ang kalihokan sa mga dumuloong.</t>
+          <t>Ang bata nangukab sa iyang tupperware ug nakita ang toyi nga giulan sa iyang bibingka.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gwapo kon magtalikod</t>
+          <t>mamalit og kaso</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
+          <t>aron mahimong usa ka ambulance chaser</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['magtalikod']</t>
+          <t>['mamalit']</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ang mga tao nga gwapo kon magtalikod kasagaran dili magdugay sa ilang relasyon.</t>
+          <t>Si Juan mamalit og kaso aron lang magka-daghan ang iyang kliyente.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Si Juan gwapo kon magtalikod, kay nindot ug porma ang iyang buhok ug likod.</t>
+          <t>Nagplano si Ana nga mamalit og kaso alang sa iyang koleksyon sa mga law books.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mangnukos</t>
+          <t>dili madala og rosaryo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sa pag-abli sa usa ka pista</t>
+          <t>usa ka hingpit nga walay paglaom nga kahimtang</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['mangnukos']</t>
+          <t>['madala']</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Si Juan giingnan nga dili mangnukos sa party sa iyang amiga.</t>
+          <t>Si Maria nag-antos sa mga butang nga dili madala og rosaryo.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ang iro misugod ug mangnukos sa iring nga mikarat sa atop.</t>
+          <t>Ang bata nagduwa sa altar, ug ang akong lola miingon nga ang iyang binuhatan dili madala og rosaryo.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>murag langaw nga nakatugdon sa kabaw</t>
+          <t>abot sa pikas bukid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nouveau riche</t>
+          <t>usa ka tawo nga naghisgot nga makusog</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['nakatugdon']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>"Ang mga bag-o rang nigraduate ug ni trabaho, murag langaw nga nakatugdon sa kabaw."</t>
+          <t>Ang mga away sa ilang pamilya abot sa pikas bukid, daghan nakahibalo.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Natagbaw ang langaw ug tuas siya sa likod sa kabaw, murag langaw nga nakatugdon sa kabaw nga nagpangita ug pahulay.</t>
+          <t>Pag-abot namo sa pikas bukid, kita mi sa nindot nga tan-awon nga mga bukid.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gidaman</t>
+          <t>abot sa dunggan ang ngisi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sa pag-aturog o pag-aturog</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['gidaman']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>"Kung mangutana ka og ing-ana, murag gidaman ka."</t>
+          <t>Abot sa dunggan ang ngisi ni Lito pagkakita sa iyang paboritong artista.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pagmata nako sa buntag, nakita nako ang akong igsoon nga gidaman ug naglakaw-lakaw sa sala.</t>
+          <t>Nagpanglingo si Ana kay abot sa dunggan ang iyang ngisi sa paglingaw sa sayop nga katawa ni Juan.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ang baka nisulod sa kulon</t>
+          <t>kapugngan pa ang baha, dili ang biga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa nga siya usa ka bakak o ikaw mahimo sa pagsulti sa laing nagbuwa</t>
+          <t>dili mapugngan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['nisulod']</t>
+          <t>['kapugngan']</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sa dihang nagluto siya, naay baka nisulod sa kulon nga nagkalata.</t>
+          <t>Si Pedro dili mapugngan sa iyang gusto, kapugngan pa ang baha, dili ang biga.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Naglibog ko pagtan-aw sa kusina kay ang baka gyud tinuod nga nisulod sa kulon.</t>
+          <t>Ang mga trabahante nagtrabaho dili sa pagpatigbabaw sa ilang gugma kondili sa paglimpyo ug pag-alsa sa mga debris tungod kay kapugngan pa ang baha, dili ang biga.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>walay aso makumkom</t>
+          <t>giluto sa kaugalingong mantika</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>walay sekreto nga magpabilin nga sekreto</t>
+          <t>sa pag-ukit sa kaugalingong lubnganan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['makumkom']</t>
+          <t>['giluto']</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Si Ana nakasabot nga walay aso makumkom, mao nga nagbantay siya sa iyang mga desisyon.</t>
+          <t>Ang iyang kauban giluto sa kaugalingong mantika tungod sa iyang binuhatan.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ang tinuod, bisan unsa ka kusog sa imong pagpaningkamot, walay aso makumkom basta maayo ang hangin.</t>
+          <t>Si Maria nagluto sa baboy, gamit ang kaugalingong mantika niini para mas lami.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ul-ol</t>
+          <t>lisod pukawon ang gamata</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sa pag- masturba Mga sinonim: batil</t>
+          <t>gigamit sa pagsulti sa nagmata o sa usa ka tawo nga dili magmata</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['ul-ol']</t>
+          <t>['pukawon']</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ang iyang mga ul-ol nga istorya kay naghatag ug kalibog sa tanan.</t>
+          <t>Ang mga estudyante nga late na matulog, lisod pukawon ang gamata.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juan miingon nga siya gikapoy human siya mag-ul-ol sulod sa iyang kwarto.</t>
+          <t>Pagmata na, Toto, lisod pukawon ang gamata kung naa pay iring nga nagkatulog sa imong tiyan.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>giprito sa kaugalingong mantika</t>
+          <t>nadakpan na ba ang nagtupi nimo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Alternatibo nga porma sa giluto sa kaugalingong mantika</t>
+          <t>gisultihan sa usa ka tawo nga adunay bag-ong buhok</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['giprito']</t>
+          <t>['nadakpan, nagtupi']</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Si Juan giprito sa kaugalingong mantika, kay nagpadayon sa iyang sayop.</t>
+          <t>Nadakpan na ba ang nagtupi nimo kay murag wa man nasunod imong gusto?</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nagluto si Maria ug isda nga giprito sa kaugalingong mantika aron mas lami ang timpla.</t>
+          <t>"Nadakpan na ba ang nagtupi nimo kay wala man gud siya'y lisensya sa pag-operate og barber shop?"</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>maghilak ang adlaw</t>
+          <t>ang masuya madeads</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>mabul-og</t>
+          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['maghilak']</t>
+          <t>['masuya']</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ang mga tawo nag-relax sa balay samtang naghilak ang adlaw.</t>
+          <t>Bisan unsaon nimo ug paningkamot, ang masuya madeads kay wala gyud ka nalipay.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ang mga bata nagdali og pauli pagkahuman nila makit-an nga maghilak ang adlaw tungod sa kusog nga ulan.</t>
+          <t>Pag-atiman gud sa imong kaugalingon kay ang masuya madeads gyud na makadaot sa imong kalusugan.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>higda sa lubi</t>
+          <t>pasok, Luningning</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pag-ula</t>
+          <t>miingon sa kaugalingon sa dihang pag-poking sa usa sa iyang mga winnings sa usa ka dula sa mga kard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['higda']</t>
+          <t>['pasok']</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Si Juan higda sa lubi, pirmi lang maghubog-hubog.</t>
+          <t>Pasok, Luningning, kay daghan pa ta ug buhaton.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ang bata nakatulog ug higda sa lubi human magdula sa daplin sa baybayon.</t>
+          <t>Nangabli si Luningning sa pultahan ug giingnan siya sa iyang mama, "Pasok, Luningning, kay ulan kaayo sa gawas."</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>pangatulig luwag</t>
+          <t>kulang sa tagad</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['pangatulig']</t>
+          <t>['tagad']</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>"Pangatulig luwag imong mga ideas, kinahanglan pa nimo ug focus."</t>
+          <t>Si Maria kulang sa tagad, pirmi lang magbinuang aron makuha ang atensyon sa iyang mga kauban.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>"Sa kalit nga pangatulig luwag, nawad-an siya ug gana sa iyang gipangluto nga lugaw."</t>
+          <t>Ang balay ni Lolo ug Lola kulang sa tagad, mao nga hapit na mapapas ang ilang pintal ug nagkinahanglan na’g bag-ong kisame.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>kirig</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['kirig']</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ang iyang mga istorya pirmi ipanabi na sa clouds kay dili tinuod.</t>
+          <t>Si Ana kirig sa iyang sakit nga epilepsy.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ang mga piloto nagplano nga ipanabi na sa clouds ang mensahe nga nahuman na ang misyon.</t>
+          <t>Ang bata misugod og kirig pagkakita sa ilaga nga kalit niagi sa ilang atubangan.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>lisod pukawon ang gamata</t>
+          <t>makabugto og bra</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa nagmata o sa usa ka tawo nga dili magmata</t>
+          <t>pisikal o seksuwal nga madanihon</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['pukawon']</t>
+          <t>['makabugto']</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bisan unsaon, lisod pukawon ang gamata kung kapoy ang lawas.</t>
+          <t>Ang artista nga iyang nakita sa TV makabugto og bra gyud.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Matag buntag, lisod pukawon ang gamata kay grabe ka duol ang ilang pagkatulog.</t>
+          <t>Nagkatawa sila nga nagtabi kay ang iyang kalit nga lihok makabugto og bra sa iyang gikoptan.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>abot sa dalunggan ang ngisi</t>
+          <t>gidaman</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nga dili gayod malipay</t>
+          <t>sa pag-aturog o pag-aturog</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['abot']</t>
+          <t>['gidaman']</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ang bata, abot sa dalunggan ang ngisi sa dihang gihatagan ug dako nga regalo.</t>
+          <t>"Ayaw ko gidam-i, klaro kaayo imong mga istorya."</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ang babaye, abot sa dalunggan ang ngisi tungod sa iyang katawa.</t>
+          <t>Pagmata nako sa buntag, nahibulong ko kay ako gidaman na diay kagabii.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>bukhad og palad</t>
+          <t>magpalapad og papel</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>mahinatagon Synonyms: manggihatagon</t>
+          <t>aron magbaton ug dungog sa buhat sa uban</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>['bukhad']</t>
+          <t>['magpalapad']</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ang mga tao nga bukhad og palad kasagaran daghan ug mga amigo.</t>
+          <t>Si Maria magpalapad og papel bisan dili siya ang nagtrabaho sa project.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Si Lola Juanita mihapit sa manghuhula aron pabasaon ang iyang bukhad nga palad.</t>
+          <t>Si Juan magpalapad og papel gamit ang iyang bagong makina.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>dili makaon og iro</t>
+          <t>mangayo og manghod</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>makalilisang</t>
+          <t>usa ka kaso sa bata nga nag-asuso o nag-agom sa iyang mga tudlo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>['makaon']</t>
+          <t>['mangayo']</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ang iyang batasan dili makaon og iro, maong walay ganahan makighangyo niya.</t>
+          <t>Si Juan nalipay kay ang iyang baby nakakat-on nga mangayo og manghod.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ang mga pagkaon nga gibutang sa lamesa dili makaon og iro kay peligroso kini sa ilang panglawas.</t>
+          <t>"Si Maria nangayo og manghod kay kini ang gipangita sa ilahang tapok."</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ayaw adto og gubat kon wala kay bala</t>
+          <t>magpalapad og papel</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ayaw pagbuhat ug dili-andam</t>
+          <t>aron magbaton ug dungog sa buhat sa uban</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['adto']</t>
+          <t>['magpalapad']</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ang mga negosyante giingnan nga ayaw adto og gubat kon wala kay bala sa kompetisyon.</t>
+          <t>Ang iyang kauban sa trabaho pirmi magpalapad og papel sa mga achievements sa uban.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ang mga sundalo giingnan sa ilang kumander, "Ayaw adto og gubat kon wala kay bala, kay delikado ang kahimtang diha."</t>
+          <t>Nagpalit siya og balayronon sa papel sa tindahan kay magpalapad siya og papel alang sa iyang project sa eskuwela.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>taga</t>
+          <t>hinaw</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pag-slash</t>
+          <t>sa paghunaw sa kamot sa usa o sa uban</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['hinaw']</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ang mga kawatan nahadlok kay basin mataga sila sa mga tag-iya sa balay.</t>
+          <t>Ang iyang kauban naghinaw sa problema kay dili siya gusto maapil.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ang mananagat mihawid ug isda ug gitaga kini gamit ang sundang.</t>
+          <t>"Naghugaw ang iyang mga kamot sa pintal busa siya mihunaw dayon sa gripo."</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>dili tanang butang sili nga mohalang dayon</t>
+          <t>dili madala og rosaryo</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dili tanan mahitabo sa usa ka higayon</t>
+          <t>usa ka hingpit nga walay paglaom nga kahimtang</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>['mohalang']</t>
+          <t>['madala']</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga dili tanang butang sili nga mohalang dayon kasagaran magmalampuson sa ilang mga plano.</t>
+          <t>Ang mga tawo nga naa sa kalisod kasagaran dili madala og rosaryo ilang mga problema.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nagpalit siya og daghang klase sa sili sa merkado, pero nakadiskubre siya nga dili tanang butang sili nga mohalang dayon.</t>
+          <t>Ang bata nagtuo nga ang manika dili madala og rosaryo sa simbahan.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>molayag sa kalipay</t>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>sa pagpakigsekso</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['molayag']</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ang mga amigo nagmolayag sa kalipay sa ilang road trip.</t>
+          <t>Ang mga tawo giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ang mga bata nagmolayag sa kalipay samtang nagdula sa dagat sa buntag.</t>
+          <t>Pag-abot sa panahon sa tig-ulan, diha ra jud sa patag magtapok ang tubig kay dili na mabalik ang baha paingon sa bukid.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ul-ol</t>
+          <t>mamalit og kaso</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>sa pag- masturba Mga sinonim: batil</t>
+          <t>aron mahimong usa ka ambulance chaser</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['ul-ol']</t>
+          <t>['mamalit']</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Dili maayo nga magsige ka ug ul-ol kay makadaot kini sa imong reputation.</t>
+          <t>Si Pedro mamalit og kaso aron makakwarta sa mga biktima sa aksidente.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>"Ang bata natapolan ug dili gusto magtuon, murag ul-ol gyud siya."</t>
+          <t>Nagplano si Maria nga mamalit og kaso alang sa eskuylahan.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gigukod sa plansa</t>
+          <t>ang masuya madeads</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
+          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['gigukod']</t>
+          <t>['masuya']</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ang mga tawo nga gigukod sa plansa kasagaran dili mag-atiman sa ilang kaugalingon.</t>
+          <t>Ayaw suya-suya kay ang masuya madeads.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ganiha buntag, nagdali ko ug gamay, maong ang akong kamiseta gigukod sa plansa aron mawala ang tupi.</t>
+          <t>Ang masuya madeads tungod kay nasuya siya sa bag-ong kotse sa iyang silingan ug naghinanok, naapsan siya sa sakuna.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>gwapa kon magtalikod</t>
+          <t>maghilak ang adlaw</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
+          <t>mabul-og</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>['magtalikod']</t>
+          <t>['maghilak']</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ang mga tao nga gwapa kon magtalikod kasagaran maulaw kung mag-atubang.</t>
+          <t>Ang mga tawo nag-relax sa balay samtang naghilak ang adlaw.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>"Si Ana gwapa kon magtalikod kay nindot ug straight ang iyang buhok."</t>
+          <t>Ang mga bata nagdali og pauli pagkahuman nila makit-an nga maghilak ang adlaw tungod sa kusog nga ulan.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>tuslok baki</t>
+          <t>kuyog baboy</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>usa ka dula</t>
+          <t>usa ka tagalong</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>['tuslok']</t>
+          <t>['kuyog']</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ang tuslok baki kay usa ka traditional nga dula nga gipasa-pasa sa mga henerasyon.</t>
+          <t>Si Juan pirmi lang kuyog baboy bisan unsa nga lakaw.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nagkagubot ang mga bata samtang nagtan-aw kung kinsa ang makatama sa baki sa ilang gipagawas nga tuslok.</t>
+          <t>Nagdala si Pedro ug iyahang kuyog baboy sa merkado para mamaligya.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kusog mokaon og gasolina</t>
+          <t>higda sa lubi</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>gas-gussing</t>
+          <t>pag-ula</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>['mokaon']</t>
+          <t>['higda']</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Ang iyang motor kusog mokaon og gasolina, pirmi lang magpailis.</t>
+          <t>Si Juan higda sa lubi, pirmi lang maghubog-hubog.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nag-obserbar si Juan nga kusog mokaon og gasolina ang ilang makinarya sa umahan tungod kay daghan kaayong trabaho sa ting-ani.</t>
+          <t>Ang bata nakatulog ug higda sa lubi human magdula sa daplin sa baybayon.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>magtumba og baka</t>
+          <t>lisod pukawon ang gamata</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>sa pag-ihaw sa usa ka vaca</t>
+          <t>gigamit sa pagsulti sa nagmata o sa usa ka tawo nga dili magmata</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['magtumba']</t>
+          <t>['pukawon']</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Si Maria nalipay kay magtumba og baka ang iyang pamilya para sa pasko.</t>
+          <t>Lisod pukawon ang gamata sa mga bata kung aduna'y bag-ong gadget.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ang mga trabahador sa uma magtumba og baka karong buntaga para sa karneng iprutos.</t>
+          <t>Nagmata na ang tanan apan lisod pukawon ang gamata nga natulog sa kilid sa iyang mamâ.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>hangyo lubo</t>
+          <t>makagisi og pitaka</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>usa ka hangyo nga gihimo sa ingon nga paagi nga dili kini makalikay</t>
+          <t>mahal kaayo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['hangyo', 'lubo']</t>
+          <t>['makagisi']</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Si Maria hangyo lubo, maong walay makatanggi sa iyang mga pangutana.</t>
+          <t>Ang restaurant nga ilang giadtoan makagisi og pitaka kaayo.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ang hangyo lubo ni Juan kay ang pagbahin sa iyang mga kalubian sa iyang mga silingan human sa bagyong miagi.</t>
+          <t>Ang bata nagduwa ug kaisog ug nakagisi og iyang pitaka samtang nangahulog ang mga coins.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kapugngan pa ang baha, dili ang biga</t>
+          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>dili mapugngan</t>
+          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['kapugngan']</t>
+          <t>['dakpa']</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Si Maria adunay dakong pangandoy nga dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
+          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, kay walay lain maka-entertain nimo.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pag-abot sa kusog nga ulan, kapugngan pa ang baha, dili ang biga sa yuta nga grabe kaayo ang pag-inilog ug pag-atake.</t>
+          <t>Naglain akong tiyan, mao nga kung wala kay lingaw sa kinabuhi, dakpa akong utot aron makita nato ug tinuod ba.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>buotan ra og matulog</t>
+          <t>kuyog baboy</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>malinong</t>
+          <t>usa ka tagalong</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>['matulog']</t>
+          <t>['kuyog']</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ang mga bata nga buotan ra og matulog kasagaran magdala ug kasamok sa balay.</t>
+          <t>Si Pedro dili ganahan ug kuyog baboy kay samok kaayo.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Si Lito, bisag buotan ra og matulog, abtik kaayo sa pagtrabaho kung alerto na.</t>
+          <t>Nagplano mi nga magdala ug kuyog baboy sa pamilya para sa pista sa baryo.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>magpalapad og papel</t>
+          <t>ipanabi na sa clouds</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>aron magbaton ug dungog sa buhat sa uban</t>
+          <t>Isulti kana sa mga marine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['magpalapad']</t>
+          <t>['ipanabi']</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ang iyang kauban sa trabaho pirmi magpalapad og papel sa mga achievements sa uban.</t>
+          <t>Bisan unsa ka lisod, ipanabi na sa clouds ang imong mga pag-ampo.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nagpalit siya og balayronon sa papel sa tindahan kay magpalapad siya og papel alang sa iyang project sa eskuwela.</t>
+          <t>Pagka gabii, among ipanabi na sa clouds ang among mga mensahe pinaagi sa drone nga adunay mga light display.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>sabong</t>
+          <t>abot sa dunggan ang ngisi</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>usa ka kompetisyon</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['sabong']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ang mga manok nga ipangsabong kay gipangandaman ug maayo.</t>
+          <t>Sa dihang gihatagan siya ug award, abot sa dunggan ang ngisi ni Carla.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ang akong amahan mopalit og sabon sa merkado kay nahutdan na mi sa among balay.</t>
+          <t>Nagkatawa kaayo ang bata nga abot sa dunggan ang ngisi niya.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>maabot sa luwa</t>
+          <t>higda sa lubi</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>duol dili layo</t>
+          <t>pag-ula</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['maabot']</t>
+          <t>['higda']</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ang lugar nga ilang giadtoan kay maabot ra sa luwa, dili layo.</t>
+          <t>Ang iyang mga kauban pirmi lang mag-higda sa lubi kung mag-party.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ang tubig nga akong gitilaw kay lami, hangtod maabot ra gyud sa luwa.</t>
+          <t>Ang bata nagdula ug higda sa lubi sa baybayon.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>agi sa bangag sa dagom</t>
+          <t>bantay pari</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
+          <t>aron sa pagbantay sa usa ka tawo/usa ka butang</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['agi']</t>
+          <t>['bantay']</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Ang iyang negosyo agi sa bangag sa dagom bago niyag napalambo.</t>
+          <t>Ang iyang bantay pari nga kinaiya nakapahimo nga malampuson ang ilang proyekto.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nagtan-aw siya unsaon pag-agi sa sinulid sa bangag sa dagom aron masugdan ang pagpanahi.</t>
+          <t>Ang bantay pari naglingkod sa daplin sa altar samtang nagsugod ang misa.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ang baka nisulod sa kulon</t>
+          <t>murag namiya og tai</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa nga siya usa ka bakak o ikaw mahimo sa pagsulti sa laing nagbuwa</t>
+          <t>Usa ka tawo nga mibiya sa dili-iasa nga walay iyang pulong</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['nisulod']</t>
+          <t>['namiya']</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sa dihang nag-away sila, mura'g baka nga nisulod sa kulon ang kasaba.</t>
+          <t>"Ang bata murag namiya og tai, kalit lang nawala."</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gikugang si Mama pagtan-aw niya nga ang baka tinuod gyud nga nisulod sa kulon.</t>
+          <t>Siya nagdali ug dagan paingon sa banyo kay murag namiya og tai.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ang masuya madeads</t>
+          <t>abot na sa dukot</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
+          <t>pag-iskrabe sa ubos sa bariles</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['masuya']</t>
+          <t>['abot', 'dukot']</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Si Juan kay permi masuya sa mga gadgets sa uban, pero ang masuya madeads.</t>
+          <t>Ang iyang mga problema murag abot na sa dukot, grabe na kaayo.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Siya miingon nga ang masuya madeads, og nagtuo gyud siya nga ang pagkamasuya makaresulta sa pagkamatay.</t>
+          <t>Nagkuha ko og sud-an sa kaldero, pero kinahanglan gyud nga aboton ang dukot aron mahurot ang kan-on.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>abot sa dunggan ang ngisi</t>
+          <t>buotan ra og matulog</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nga dili gayod malipay</t>
+          <t>malinong</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>['abot']</t>
+          <t>['matulog']</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Abot sa dunggan ang ngisi ni Manang Ines pagkakita sa iyang mga apo.</t>
+          <t>Si Pedro buotan ra og matulog, kay pirmi lang magbinuang sa klase.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gani, abot sa dunggan ang ngisi ni Juan kay naputlan siya ug tabil sa iyang ngipon.</t>
+          <t>Si Lola kung mahigda, buotan ra og matulog kay dili siya maglihok-lihok sa gabii.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>makabugto og bra</t>
+          <t>kuskos balungos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>pisikal o seksuwal nga madanihon</t>
+          <t>pag-awhag</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['makabugto']</t>
+          <t>['kuskos']</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Si Juan ganahan kaayo sa iyang uyab kay makabugto og bra.</t>
+          <t>Si Juan pirmi lang kuskos balungos sa mga problema nga walay solusyon.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>"Ayoa pag-atiman sa imong sinina kay basin makabugto og bra ang lig-ag sa washing machine."</t>
+          <t>Naglimpyo si Maria sa lamesa pinaagi sa kuskos balungos gamit ang spongha aron matangtang ang mga mantika.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kulang sa dukol</t>
+          <t>abot sa pikas bukid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>usa ka buangbuang nga tawo</t>
+          <t>usa ka tawo nga naghisgot nga makusog</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>['dukol']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Si Juan kulang sa dukol, pirmi lang magtambay sa kanto.</t>
+          <t>Ang istorya ni Pedro abot sa pikas bukid bisan dili tinuod.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Si bata kulang sa dukol kay walay nag-amuma sa iya kabuang.</t>
+          <t>Naglakaw mi ug dugay hangtod nga among naabtan ang pikas bukid.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>gi-indian</t>
+          <t>litik</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
+          <t>sa pag-aghat sa tudlo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>['gi-indian']</t>
+          <t>['litik']</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ang mga estudyante na gi-indian sa ilang maestra sa klase karon.</t>
+          <t>Si Maria naglitik sa iyang mga pangandoy sa kinabuhi.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Siya gi-indian ang hilaw nga manok gamit ang tradisyonal nga resipe sa tribu.</t>
+          <t>Si Juan naglitik sa papel aron ibutang ang mantika.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>habwa ang kinaon</t>
+          <t>alsa og balay</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>pag-awhag</t>
+          <t>gisulti sa kaugalingon o sa uban kon ang pagkaon naglakip sa mung beans</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>['habwa', 'kinaon']</t>
+          <t>['alsa']</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ang iyang amiga naghabwa ang kinaon kay nasubraan ug kaon.</t>
+          <t>Ang mga bata sa bukid kay alsa og balay para makapaeskwela.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ang bata naghabwa sa sudlanan aron makuha ang kinaon.</t>
+          <t>Gihangyo sa pamilya ang ilang mga silingan nga tabangan sila ug alsa og balay tungod kay kinahanglan nila mubalhin sa pikas baryo.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kulang sa dukol</t>
+          <t>sabong</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>usa ka buangbuang nga tawo</t>
+          <t>usa ka kompetisyon</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['dukol']</t>
+          <t>['sabong']</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ang iyang anak kulang sa dukol, dili gyud magtinarong sa pag-eskwela.</t>
+          <t>Ang mga sabong sa probinsya kasagaran ginadumog sa mga lokal nga residente.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ang bata kulang sa dukol, mao nga giingnan siya sa iyang ginikanan nga magmatngon sa sunod nga dulaan.</t>
+          <t>"Ang sabong nga gigamit nako sa pagpaligo humot ug daghan ug sabon."</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ayaw pagbuot kay lain-lain ta og lubot</t>
+          <t>makamala og sapa</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ayaw ako isulti kon unsay buhaton</t>
+          <t>ang usa ka tawo nga may dagkong tiil</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['pagbuot']</t>
+          <t>['makamala']</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Ayaw pagbuot kay lain-lain ta og lubot, respetaray lang ta sa atong mga opinion.</t>
+          <t>Ang mga tawo nga dagko ug tiil kasagaran makamala og sapa.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Pagmeeting sa klase, nananghid si Junjun nga dili siya makagymnastics kay ingon niya, "Ayaw pagbuot kay lain-lain ta og lubot," nagsakit iyang lubot paglingkod.</t>
+          <t>Ang mga bata nagdula sa daplin sa sapa ug kalit lang nga ang isa kanila makamala og sapa.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kuwang sa tagad</t>
+          <t>makawat</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+          <t>mahimong ma-stolen</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>['tagad']</t>
+          <t>['makawat']</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Si Juan pirmi lang magpakita sa mga tao kay kuwang sa tagad.</t>
+          <t>Ang bata ni Maria makawat kaayo, bisan kinsa lang pwede makagunit niya.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ang bata nga nahibilin sa balay gamay ra kaayo ang nadawat nga kalooy, kuwang sa tagad sa iyang mga ginikanan.</t>
+          <t>Ang akong pitaka nga gibutang sa lamisa makawat sa mga kawatan.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>gisulod sa bulsa</t>
+          <t>kuskos-balungos</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>sa paglimbong</t>
+          <t>alternatibong pagsulat sa kuskos balungos</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['gisulod']</t>
+          <t>['kuskos']</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Si Maria gisulod sa bulsa, maong nag-antos siya sa iyang mga desisyon.</t>
+          <t>Si Maria pirmi lang kuskos-balungos bisan unsa nga buhaton.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gisulod ni Juan ang sensilyo sa iyang bulsa aron dili kini mawala.</t>
+          <t>Nag-kuskos-balungos si Juan sa plato aron makatangtang sa hugaw nga pilit.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>gadalag uwan</t>
+          <t>nakalugsong</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>usa ka lalaki nga homoseksual</t>
+          <t>sa pag-adto gikan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['nagdala']</t>
+          <t>['nakalugsong']</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ang iyang silingan gadalag uwan, pero respetado gihapon sa ilang lugar.</t>
+          <t>Ang mga trabahante nakalugsong gikan sa taas ug giuli ang mga gamit.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Naglakaw kami sa kalsada ug nakita namo nga ang bata gadalag uwan aron dili mabasa sa kalit nga pag-abot sa ulan.</t>
+          <t>Ang bata nakalugsong sa bukid human magdula didto.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>maabot sa luwa</t>
+          <t>pasok, Luningning</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>duol dili layo</t>
+          <t>miingon sa kaugalingon sa dihang pag-poking sa usa sa iyang mga winnings sa usa ka dula sa mga kard</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['maabot']</t>
+          <t>['pasok']</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi lang maglakaw kay ang eskwelahan maabot ra sa luwa.</t>
+          <t>Pasok, Luningning, kay andam na ang tanan para nimo.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ang lamesa natapsingan sa luwa ni Karen samtang siya nagtabi-tabi.</t>
+          <t>"Pasok, Luningning, kay oras na sa klase."</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>walay aso makumkom</t>
+          <t>abot sa pikas bukid</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>walay sekreto nga magpabilin nga sekreto</t>
+          <t>usa ka tawo nga naghisgot nga makusog</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['makumkom']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Si Pedro nasayod nga walay aso makumkom, mao nga nagmatngon siya sa iyang mga lihok.</t>
+          <t>Bisan asa pa sila, abot sa pikas bukid ang ilang tingog.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nagpayong si Anna duol sa siga apan nag-ingon siya nga walay aso makumkom tungod kay ihipan kini sa hangin.</t>
+          <t>Nagbiyahe sila sa duol nga baryo ug miabot sila sa pikas bukid human sa duha ka oras nga paglakaw.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>hangyo kabayo</t>
+          <t>ul-ol</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>usa ka maalamon nga paagi sa pagbaton ug usa ka butang</t>
+          <t>sa pag- masturba Mga sinonim: batil</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>['hangyo']</t>
+          <t>['ul-ol']</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ang iyang amiga hangyo kabayo, bisan unsa nga butang iyang makuha.</t>
+          <t>Ayaw pag-ul-ol, kinahanglan naa kay respeto sa uban.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Paghangyo siya sa presyo sa kabayo nga iyang gustong paliton.</t>
+          <t>Gisul-ol ang usa ka ubo nga kahoy para gamiton sa una nga proyekto sa klase.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>awas og palad</t>
+          <t>ang masuya madeads</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>• awasan og palad</t>
+          <t>gigamit sa pagsulti sa usa nga dili magkritika o magdumot sa gibuhat sa usa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['awas']</t>
+          <t>['masuya']</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ang mga awas og palad kasagaran maglisod sa kinabuhi kay dili kabalo magtipid.</t>
+          <t>Si Juan kay permi masuya sa mga gadgets sa uban, pero ang masuya madeads.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Miuyog ko sa akong ulo nga dali ra kaayo nga awas ang palad sa baso.</t>
+          <t>Siya miingon nga ang masuya madeads, og nagtuo gyud siya nga ang pagkamasuya makaresulta sa pagkamatay.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>dili na nimo mabalik ang baha sa bukid</t>
+          <t>makagisi og pitaka</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ang nahimo nahimo na</t>
+          <t>mahal kaayo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['makagisi']</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Si Ana nakasabot nga dili na nimo mabalik ang baha sa bukid, mao nga nag-move on na siya.</t>
+          <t>Ang iyang bag-ong sapatos makagisi og pitaka tungod sa kamahal.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Nagbaha sa bukid tungod sa kusog nga ulan, ug bisan unsaon pa nimo og paningkamot, dili na nimo mabalik ang baha sa bukid nga ubos.</t>
+          <t>Nakita nako nga makagisi og pitaka ang sangko na lansang.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ang gaba dili magsaba</t>
+          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ang silot tungod sa iyang mga sayop o mga paglapas moabut sa wala damha</t>
+          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>['magsaba']</t>
+          <t>['dakpa']</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Si Pedro nabulabog kay nasuko ang iyang giilad, ang gaba dili magsaba.</t>
+          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot kay mao ra na akong ikahatag nimo.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sa kalit nga pagtandog sa kanal, nabali ang sungkod ni Lito ug nahangit siya, gipakita nga ang gaba dili magsaba.</t>
+          <t>Naglingkod si Juan sa sala ug niingon siya sa iyang igsoon nga si Pedro, "Kung wala kay lingaw sa kinabuhi, dakpa akong utot," samtang mihagok siya og makusog.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>kuyog baboy</t>
+          <t>gigukod sa plansa</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>usa ka tagalong</t>
+          <t>ang usa ka tawo nga nagsul-ob ug mga sinina</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>['kuyog']</t>
+          <t>['gigukod']</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Si Maria pirmi lang kuyog baboy, bisan asa moadto iyang best friend naa gyud.</t>
+          <t>Si Pedro pirmi lang gigukod sa plansa, bisan unsa nga sinina dili mahimutang.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Naglaag mi sa uma ug nagdala mi og kuyog baboy aron makalingaw ang mga bata.</t>
+          <t>Ang shirt ni Juan gigukod sa plansa human gilabhan.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>gwapo kon magtalikod</t>
+          <t>maabot sa luwa</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
+          <t>duol dili layo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['magtalikod']</t>
+          <t>['maabot']</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Ang iyang amigo gwapo kon magtalikod, pero bati diay pagtan-aw sa iyang nawong.</t>
+          <t>Si Pedro pirmi lang maglakaw kay ang eskwelahan maabot ra sa luwa.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nagpicture ko sa akong iro sa dagat, ug gwapo kon magtalikod kay nindot kaayo iyang itom nga balhibo sa likod.</t>
+          <t>Ang lamesa natapsingan sa luwa ni Karen samtang siya nagtabi-tabi.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>gi-indian</t>
+          <t>walay aso makumkom</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
+          <t>walay sekreto nga magpabilin nga sekreto</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>['gi-indian']</t>
+          <t>['makumkom']</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Si Juan gi-indian sa iyang kliyente sa ilang appointment.</t>
+          <t>Si Ana nakasabot nga walay aso makumkom, mao nga nagbantay siya sa iyang mga desisyon.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Siya gidala sa pagtuon ang mga katigulangan nga gi-indian ni Magellan sa Sugbo kaniadto.</t>
+          <t>Ang tinuod, bisan unsa ka kusog sa imong pagpaningkamot, walay aso makumkom basta maayo ang hangin.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ayaw pagbuot, lain-lain tag lubot</t>
+          <t>manglutasay</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ayaw ako isulti kon unsay buhaton</t>
+          <t>usa ka manunulak sa mga bukog</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>['pagbuot']</t>
+          <t>['manglutasay']</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lain-lain tag lubot, mao nga kinahanglan respetuhon ang desisyon sa uban.</t>
+          <t>Si Maria nalipay kay ang iyang kauban dili manglutasay.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sa klase sa Biology, gitun-an namo nga lain-lain og porma ang lubot sa matag matang sa hayop.</t>
+          <t>Nagtapok ang mga bata sa silong sa balay aron magduwa og mga luto-lutoan, ug makita nimo nga manglutasay sila ug mga puto't kutsara.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>kuwang sa tagad</t>
+          <t>gadalag uwan</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
+          <t>usa ka lalaki nga homoseksual</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>['tagad']</t>
+          <t>['nagdala']</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Si Pedro kuwang sa tagad, bisan unsa nga event ganahan magpakita.</t>
+          <t>Ang mga tao nga gadalag uwan kasagaran adunay mga pagsulay sa kinabuhi.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ang tanom nga wa matagda, nagpakita og mga sintomas nga kuwang sa tagad sama sa mga dili hapsay nga dahon.</t>
+          <t>Ang bata gadalag uwan samtang nagpadulong sa merkado.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>gigukod sa sudlay</t>
+          <t>paabang</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nga walay buhok</t>
+          <t>pag-abang</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>['gigukod']</t>
+          <t>['paabang']</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Si Pedro pirmi lang gigukod sa sudlay, bisan unsa nga event, dili mag-comb.</t>
+          <t>Ang ilang negosyo nga paabang og sakyanan kay booming na kaayo karon.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Anaa sa lamesa ang sudlay nga gigukod sa mga bata samtang nagdula sila.</t>
+          <t>Nagpaabang sila og kwarto sa ilang balay alang sa mga turista.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>makakutaw og utok</t>
+          <t>alsa og balay</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>makapalibog</t>
+          <t>gisulti sa kaugalingon o sa uban kon ang pagkaon naglakip sa mung beans</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['makakutaw']</t>
+          <t>['alsa']</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ang explanation sa iyang professor makakutaw og utok kaayo.</t>
+          <t>Ang mga magtiayon nag-alsa og balay para sa ilang bag-ong balay.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ang iyahang paghalo sa mainit nga supas makakutaw og utok kay wala pa man gud niupos ang kainit niini.</t>
+          <t>Nagkauban mi sa akong mga amigo aron alsa og balay nga gibalhin sa baryo.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>pangatulig luwag</t>
+          <t>mag-ihaw og lata</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+          <t>sa pagluto sa mga pagkaon nga tinago</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>['pangatulig']</t>
+          <t>['mag-ihaw']</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>"Pangatulig luwag imong mga plano, walay klaro."</t>
+          <t>Si Juan pirmi lang mag-ihaw og lata sa boarding house.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ang iyang pangatulig luwag kay naguba tungod sa karaan na kaayo nga kaldero.</t>
+          <t>Gikuha ni Pedro ang kalaha aron mag-ihaw og lata sa ilang umahan.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>pangatulig luwag</t>
+          <t>murag namatyag iring</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
+          <t>gigamit sa paghulagway sa usa ka tawo nga nagtangis nga nagtangis o nagtangis nga nagtangis</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>['pangatulig']</t>
+          <t>['namatyag']</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Ang iyang plano kay murag pangatulig luwag, walay klaro nga direksyon.</t>
+          <t>"Ang mga bata murag namatyag iring pagkahuman sa dula."</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>"Human sila pagkutaw sa sabaw, nag-pangatulig luwag dayon aron limpyo ang gamit."</t>
+          <t>Ang among iring murag namatyag iring nga naghilak pag-abot namo sa balay.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>gwapo kon magtalikod</t>
+          <t>lunod patay</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
+          <t>dihard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['magtalikod']</t>
+          <t>['lunod', 'patay']</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Si Juan gwapo kon magtalikod, pero dili na kaayo pag-atubang.</t>
+          <t>Ang mga tawo nga lunod patay kasagaran adunay baruganan nga dili matay-og.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nagkatawa si Ana kay ang iyang iro gwapo kon magtalikod sa iyang fluffy nga ikog.</t>
+          <t>Ang bata naglangoy-langoy sa dagat apan nawad-an og kusog ug hapit na siya lunod patay.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>mogawas ang pari nga walay ulo</t>
+          <t>abot sa dunggan ang ngisi</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>['mogawas']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mogawas ang pari nga walay ulo kuno kung aduna'y mamatay sa baryo.</t>
+          <t>Ang among boss, abot sa dunggan ang ngisi sa dihang nadawat ang dagkong proyekto.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sa halangdong sugilanon, kon malangan ang mga novena sa alas dose sa kagabhion, mosulod ang pari nga walay ulo sa simbahan ug mopahimangno sa mga tawo.</t>
+          <t>Ang bata napintalan og pulang lipstick nga abot sa dunggan ang ngisi, nagkatawa ang iyang mga ginikanan pagkakita niya.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>gibati og kaanyag</t>
+          <t>walay aso makumkom</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>prima donna</t>
+          <t>walay sekreto nga magpabilin nga sekreto</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>['gibati']</t>
+          <t>['makumkom']</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Si Ana gibati og kaanyag, maong pirmi siya nagbuot-buot.</t>
+          <t>Ang mga tawo giingnan nga walay aso makumkom, mao nga magmatngon sila sa ilang mga buhaton.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>"Gibati gyud ni Carla og kaanyag sa iyang bag-ong sinina, maong nagpakita siya sa iyang mga higala."</t>
+          <t>Nag-ihaw mi ug baboy kagahapon, apan lisod gyud makumkom ang aso sa kusina.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>murag langaw nga nakatugdon sa kabaw</t>
+          <t>dula og panit</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nouveau riche</t>
+          <t>sa pag- masturba</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>['nakatugdon']</t>
+          <t>['dula']</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>"Si Ana, gikan sa pagka-pobre, murag langaw nga nakatugdon sa kabaw karon."</t>
+          <t>Ang iyang barkada kay dula og panit, bisan unsa na lang nga kalipay ang gihimo.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>"Nagtan-aw ko sa uma ug nakita nako nga murag langaw nga nakatugdon sa kabaw."</t>
+          <t>Ang bata nagdula og panit sa daplin sa suba, gamit ang tanom nga iya nakuha gikan sa palibot.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kung wala kay lingaw sa kinabuhi, dakpa akong utot</t>
+          <t>pagtan-aw, kitkit langaw; paglingi, kitkit bungi</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>gigamit sa pag-undang sa usa ka nagpangita ug pagtagad</t>
+          <t>gigamit nga isulti sa usa ka tawo nga imong gilimbongan sila sa pagtan-aw sa usa ka piho nga direksyon</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>['dakpa']</t>
+          <t>['pagtan-aw, kitkit, paglingi']</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Kung wala kay lingaw sa kinabuhi, dakpa akong utot, tan-awon nato unsay imong mahimo.</t>
+          <t>Sa kadaghan sa imong giatubang, pagtan-aw, kitkit langaw</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Naglingkod siya sa sala, dayon gisulti niya, "Kung wala kay lingaw sa kinabuhi, dakpa akong utot," samtang nangipi siya paglingaw-lingaw.</t>
+          <t>Naglingkod si Ana sa gawas, ug sa dihang niingon siya 'tan-awa', pagtan-aw, kitkit langaw; paglingi sa pikas dapit, paglingi, kitkit bungi.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>dili na mabalik ang baha paingon sa bukid</t>
+          <t>taliba</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>ang mga genital sa babaye</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['taliba']</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ang mga tawo giingnan nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na.</t>
+          <t>Ang mga barangay tanod nag-taliba sa ilang mga area kada gabii.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pag-abot sa panahon sa tig-ulan, diha ra jud sa patag magtapok ang tubig kay dili na mabalik ang baha paingon sa bukid.</t>
+          <t>Ang taliba sa pultahan nagtabang sa pagpanalipod sa balay batok sa mga kawatan.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>murag namiya og tai</t>
+          <t>kusog mokaon og gasolina</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Usa ka tawo nga mibiya sa dili-iasa nga walay iyang pulong</t>
+          <t>gas-gussing</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>['namiya']</t>
+          <t>['mokaon']</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>"Si Ana murag namiya og tai, wala na gani nagpahibalo sa iyang mga plano."</t>
+          <t>Si Maria dili ganahan ug sakyanan nga kusog mokaon og gasolina kay mahal ang maintenance.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>"Nakita nako si Tomas nga nagdali-dali padung sa banyo, murag namiya og tai."</t>
+          <t>Ang bag-ong makina nga gisulayan nila sa laboratoryo kusog mokaon og gasolina sa paspas nga dagan.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>gilawog sa tirong</t>
+          <t>gadalag ulan</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>sa pagbutang sa peligro sa usa ka tawo, ilabina</t>
+          <t>usa ka lalaki nga homoseksual</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>['gilawog']</t>
+          <t>['nagdala']</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Si Pedro gilawog sa tirong sa iyang kauban, maong nasakpan sa ilang boss.</t>
+          <t>Si Juan kay gadalag ulan, maong daghan ang naglikay niya.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gibantayan namo ang iring samtang gilawog namo kini sa tirong diha sa suba.</t>
+          <t>Nag-andam si Maria ug payong kay ang langit kay gadalag ulan.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>mangayo og manghod</t>
+          <t>manakop og ligid</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>usa ka kaso sa bata nga nag-asuso o nag-agom sa iyang mga tudlo</t>
+          <t>nga ang usa ka tawo naugtang sa usa ka sakyanan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>['mangayo']</t>
+          <t>['manakop']</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Si Pedro nakakita sa iyang anak nga mangayo og manghod sa iyang tiil.</t>
+          <t>Si Pedro manakop og ligid kay nagdagan-dagan sa kalsada.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>"Mangayo og manghod si Maria kay gusto siya ug uska mubo nga bunal sa nakatigulang."</t>
+          <t>Nagdula mi og dakop-dakop sa plaza unya nakalingkod ko para mopahuway, apan kalit nga miingon ang akong amigo nga manakop og ligid mi sa mga sakyanan nga nag-agi atubangan sa balay.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>gwapa kon magtalikod</t>
+          <t>abot sa pikas bukid</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>nindot nga tan-awon gikan sa likod</t>
+          <t>usa ka tawo nga naghisgot nga makusog</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>['magtalikod']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ang iyang kauban sa trabaho gwapa kon magtalikod, pero pag-atubang, dili na diay.</t>
+          <t>Ang iyang reklamo abot sa pikas bukid, grabe kaayo ug kasaba.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sa daghan nilang mga selfie, gwapa kon magtalikod si Ana, apan mas gwapa pag-atubang.</t>
+          <t>Migawas si Ana kada buntag aron mananom, ug dal-on niya ang iyang mga produkto abot sa pikas bukid alang sa pagbaligya.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>mangayo og manghod</t>
+          <t>makamala og sapa</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>usa ka kaso sa bata nga nag-asuso o nag-agom sa iyang mga tudlo</t>
+          <t>ang usa ka tawo nga may dagkong tiil</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>['mangayo']</t>
+          <t>['makamala']</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Si Juan nalipay kay ang iyang baby nakakat-on nga mangayo og manghod.</t>
+          <t>Si Maria nagkatawa kay ang iyang igsuon makamala og sapa sa kadako sa tiil.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>"Si Maria nangayo og manghod kay kini ang gipangita sa ilahang tapok."</t>
+          <t>Ang mga trabahante nagkinahanglan og kahoy nga makamala og sapa aron makabalhin ang mga gamit ngadto sa pikas nga pampang.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>agi sa bangag sa dagom</t>
+          <t>molayag sa kalipay</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
+          <t>sa pagpakigsekso</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>['agi']</t>
+          <t>['molayag']</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Ang ilang relasyon agi sa bangag sa dagom sa daghang pagsulay.</t>
+          <t>Sa dihang nagmolayag sa kalipay ang grupo, nakalimot sila sa ilang mga problema.</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ang karayom wala pa maagi ug hilo kay gahi jud ang pag-agi sa bangag sa dagom.</t>
+          <t>Sa ilang bakasyon, ang barko molayag sa kalipay sa nag-aninaw nga dagat samtang ang mga pasahero nagringig.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>makabugto og panty</t>
+          <t>dili na mabalik ang baha paingon sa bukid</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>pisikal o seksuwal nga madanihon</t>
+          <t>Ang nahimo dili mahimong malikayan</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>['makabugto']</t>
+          <t>['mabalik']</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Si Pedro ganahan kaayo sa iyang uyab kay makabugto og panty.</t>
+          <t>Si Ana nakasabot nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na sa iyang kinabuhi.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Paglaba nako sa akong mga sinina, nasamad ang akong daliri tungod sa hugot nga elax na makabugto og panty.</t>
+          <t>Human sa kusog nga ulan, nasayod na ang mga residente nga dili na gyud mabalik ang baha paingon sa bukid, busa nanginahanglan gyud silang mag-andam sa umaabot nga panahon.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>paabang</t>
+          <t>manglutasay</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>pag-abang</t>
+          <t>usa ka manunulak sa mga bukog</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>['paabang']</t>
+          <t>['manglutasay']</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Ang ilang negosyo nga paabang og sakyanan kay booming na kaayo karon.</t>
+          <t>Si Juan giingnan nga manglutasay kay ang iyang uyab mas bata kaayo.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nagpaabang sila og kwarto sa ilang balay alang sa mga turista.</t>
+          <t>Ang mga bata sa baryo magdula-dula ug manglutasay sa tabing-suba.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>hunaw</t>
+          <t>dili makaon og iro</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>sa paghunaw sa kamot sa usa o sa uban</t>
+          <t>makalilisang</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>['hunaw']</t>
+          <t>['makaon']</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Si Maria naghunaw sa iyang mga sala aron dili siya mahatagan ug parusa.</t>
+          <t>Ang iyang batasan dili makaon og iro, maong walay ganahan makighangyo niya.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Gihunaw ni Juan ang iyang mga kamot human sa pagkaon.</t>
+          <t>Ang mga pagkaon nga gibutang sa lamesa dili makaon og iro kay peligroso kini sa ilang panglawas.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>lisod pukawon ang gamata</t>
+          <t>gi-indian</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa nagmata o sa usa ka tawo nga dili magmata</t>
+          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>['pukawon']</t>
+          <t>['gi-indian']</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Lisod pukawon ang gamata, labi na kung bugnaw ang panahon.</t>
+          <t>Si Maria nasuko kay gi-indian siya sa iyang amigo.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>"Nakita nako nga lisod pukawon ang gamata kay nagkatulog pa gyud siya ug maayo."</t>
+          <t>Ang dula nga lung-ag o gi-indian kay mao kini ang gihimo sa mga lumad sa ilang tradisyonal nga pamagi sa pagluto.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kirig</t>
+          <t>madala nimo ang baka sa suba apan dili nimo mainom</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>pag-awhag</t>
+          <t>Mahimo nimong pagdala ang kabayo ngadto sa tubig</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>['kirig']</t>
+          <t>['madala', 'mainom']</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Si Juan kirig sa kahadlok pagkakita sa aksidente.</t>
+          <t>Ang mga estudyante kinahanglan magtuon, madala nimo ang baka sa suba apan dili nimo mainom.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Si Maria kirig samtang gidalikyat siya sa ospital tungod sa iyang sakit.</t>
+          <t>Si Juan nagdala sa ilang baka sa suba aron painumon, apan dili kini moinom bisan unsaon niya og kumbinse.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ang baka nisulod sa kulon</t>
+          <t>kapugngan pa ang baha, dili ang biga</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>gigamit sa pagsulti sa usa nga siya usa ka bakak o ikaw mahimo sa pagsulti sa laing nagbuwa</t>
+          <t>dili mapugngan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>['nisulod']</t>
+          <t>['kapugngan']</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ang pagplano nila nga walay klaro mura'g baka nga nisulod sa kulon.</t>
+          <t>Ang iyang kalagot dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ang bata nalipay kay nakita niya nga ang baka nisulod sa kulon sa pagdula-dula.</t>
+          <t>Sa kadako sa kusog sa ulan, kapugngan pa ang baha, dili ang biga nga gihunahuna sa mga tao.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>mag-ugbok og mohon</t>
+          <t>abot sa dalunggan ang ngisi</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>sa pagpakigsekso</t>
+          <t>nga dili gayod malipay</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>['mag-ugbok']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Si Maria ug ang iyang bana mag-ugbok og mohon sa ilang balay.</t>
+          <t>Sa dihang nagkita sila, abot sa dalunggan ang ngisi ni Pedro ug Ana.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ang mga trabahante mag-ugbok og mohon aron masugdan na ang pagtukod sa bag-ong balay.</t>
+          <t>Nagpila si Jenny sa salon ug abot sa dalunggan ang ngisi nga gi-drawing sa face painting artist.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>mag-ugbok og mohon</t>
+          <t>ayaw pagbuot, tagsa-tagsa tag lubot</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>sa pagpakigsekso</t>
+          <t>ayaw ako isulti kon unsay buhaton</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>['mag-ugbok']</t>
+          <t>['pagbuot']</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Si Pedro nagplano nga mag-ugbok og mohon human sa kasal.</t>
+          <t>Ang matag usa lain-lain og gusto, mao nga ayaw pagbuot, tagsa-tagsa tag lubot.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ang mga mag-uuma mag-ugbok og mohon aron markahan ang yuta nga ilang bungahon.</t>
+          <t>Sa klase sa anatomy, gi-explain sa maestro nga ang lawas sa usa ka tawo nagkalainlain ug porma, nga mao nga "ayaw pagbuot, tagsa-tagsa tag lubot."</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ayaw pagbuot kay lain-lain ta og lubot</t>
+          <t>magtumba og baka</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ayaw ako isulti kon unsay buhaton</t>
+          <t>sa pag-ihaw sa usa ka vaca</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>['pagbuot']</t>
+          <t>['magtumba']</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Dili tanan magkauyon, kay lain-lain ta og lubot.</t>
+          <t>Si Pedro magtumba og baka para sa fiesta sa ilang baryo.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sa baki sa klase, si Ma'am Ana nagtudlo nga lain-lain ta og lubot depende sa atong klase sa pagkaon ug mga gawi.</t>
+          <t>Ang kalit nga hangin nakapamugna og kusog nga pag-uyog nga nakaresulta sa pag-tumba sa duha ka baka sa uma.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>agi sa bangag sa dagom</t>
+          <t>manakop og ligid</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>pag-antos sa mga kalisdanan sa pagkab-ot sa imong tumong o damgo</t>
+          <t>nga ang usa ka tawo naugtang sa usa ka sakyanan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>['agi']</t>
+          <t>['manakop']</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Si Pedro agi sa bangag sa dagom aron lang makapasar sa eksam.</t>
+          <t>Si Juan nakasulay nga manakop og ligid human nag-away sa iyang amigo.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Si Maria naglisod og pagsulod sa pisi agi sa bangag sa dagom samtang nagpanahi siya og sinina.</t>
+          <t>Nagdula ang mga bata sa kalsada ug nangandam nga manakop og ligid nga nagligid-ligid gikan sa bag-ong luwan nga awto.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>abot sa dunggan ang ngisi</t>
+          <t>pangatulig luwag</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nga dili gayod malipay</t>
+          <t>gigamit sa pag-undang sa usa ka tawo nga misquoted o misheard sa usa ka gisulti</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>['abot']</t>
+          <t>['pangatulig']</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Abot sa dunggan ang ngisi ni Lito pagkakita sa iyang paboritong artista.</t>
+          <t>Ang iyang plano kay murag pangatulig luwag, walay klaro nga direksyon.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Nagpanglingo si Ana kay abot sa dunggan ang iyang ngisi sa paglingaw sa sayop nga katawa ni Juan.</t>
+          <t>"Human sila pagkutaw sa sabaw, nag-pangatulig luwag dayon aron limpyo ang gamit."</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>dili na mabalik ang baha paingon sa bukid</t>
+          <t>abot sa pikas bukid</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ang nahimo dili mahimong malikayan</t>
+          <t>usa ka tawo nga naghisgot nga makusog</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>['mabalik']</t>
+          <t>['abot']</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Si Ana nakasabot nga dili na mabalik ang baha paingon sa bukid, mao nga nag-move on na sa iyang kinabuhi.</t>
+          <t>Ang mga chismosa abot sa pikas bukid ang ilang mga istorya.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Human sa kusog nga ulan, nasayod na ang mga residente nga dili na gyud mabalik ang baha paingon sa bukid, busa nanginahanglan gyud silang mag-andam sa umaabot nga panahon.</t>
+          <t>Nakita nako siya nga naglakaw padulong abot sa pikas bukid.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>dili tanang butang sili nga mohalang dayon</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>Dili tanan mahitabo sa usa ka higayon</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['mohalang']</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ang imong mga plano, ipanabi na sa clouds kay maabot ra na.</t>
+          <t>Si Maria giingnan nga dili tanang butang sili nga mohalang dayon, kinahanglan gyud og pagpaningkamot.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ang detalye sa imong presentation, ipanabi na sa clouds aron ma-access sa tanan bisan asa pa.</t>
+          <t>Nagbutang ko og sili sa sabaw, apan dili tanang butang sili nga mohalang dayon, kay naay uban nga klase nga dili kaayo halang.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ipanabi na sa clouds</t>
+          <t>makabuhi og patay</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Isulti kana sa mga marine</t>
+          <t>usa ka makapatikod nga bakak o sugilanon</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>['ipanabi']</t>
+          <t>['makabuhi', 'patay']</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ang imong mga pangandoy, ipanabi na sa clouds aron matinuod.</t>
+          <t>Ang iyang amigo makabuhi og patay kung mag-suggest ug ideas.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gusto nakong ipaabot ang akong mensahe sa mga higala ko nga naa sa layo, mao nga ipanabi na sa clouds pinaagi sa teknolohiya.</t>
+          <t>Si Aning nakakita og milagro diin ang maayong albularyo nakaayo ug masakiton nga murag makabuhi og patay.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>gi-indian</t>
+          <t>murag namatyag iring</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>sa tinuyo nga dili motuman sa usa ka appointment</t>
+          <t>gigamit sa paghulagway sa usa ka tawo nga nagtangis nga nagtangis o nagtangis nga nagtangis</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>['gi-indian']</t>
+          <t>['namatyag']</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Si Pedro gi-indian sa iyang uyab sa ilang sabot nga date.</t>
+          <t>"Ang bata murag namatyag iring, hilak kaayo pagnalaya."</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Wala moabot si Miguel sa ila nahuman nga sabot, kay gi-indian man siya sa Mindanao para magtuon sa mga lumad nga Indian didto.</t>
+          <t>Ang iring sa atop murag namatyag iring, kusog kaayo ang pangubog.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>kapugngan pa ang baha, dili ang biga</t>
+          <t>awas og palad</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>dili mapugngan</t>
+          <t>• awasan og palad</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>['kapugngan']</t>
+          <t>['awas']</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Ang iyang kalagot dili mapugngan, kapugngan pa ang baha, dili ang biga.</t>
+          <t>Ang mga awas og palad kasagaran maglisod sa kinabuhi kay dili kabalo magtipid.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sa kadako sa kusog sa ulan, kapugngan pa ang baha, dili ang biga nga gihunahuna sa mga tao.</t>
+          <t>Miuyog ko sa akong ulo nga dali ra kaayo nga awas ang palad sa baso.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>buotan ra og matulog</t>
+          <t>mogawas ang pari nga walay ulo</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>malinong</t>
+          <t>gigamit sa paghadlok sa mga bata gikan sa mga samad</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>['matulog']</t>
+          <t>['mogawas']</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Ang iyang anak buotan ra og matulog, kay pirmi lang mangaway sa mga silingan.</t>
+          <t>Sa dihang mag-istorya sila og mga horror stories, mogawas ang pari nga walay ulo ang giingon.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gabiina na kaayo ug buotan ra og matulog ang bata sa ilang kwarto.</t>
+          <t>Pag-abli sa karaang simbahan sa kagabhion, nakurat sila kay tinuod nga mogawas ang pari nga walay ulo sa altar.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>taliba</t>
+          <t>kulang sa tagad</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ang mga genital sa babaye</t>
+          <t>kinaiya sa usa ka nagpangita ug atensyon</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>['taliba']</t>
+          <t>['tagad']</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Ang mga pulis nag-taliba sa mga salida aron protektahan ang mga bisita.</t>
+          <t>Si Juan kulang sa tagad, pirmi lang magpasikat sa mga tao.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ang taliba nagsugod ug talagsaon nga lihok human sa pagkahuman sa operasyon.</t>
+          <t>Ang bata gibati nga siya kulang sa tagad sa ilang panimalay kay busy kaayo ang iyang ginikanan.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>pasok, Luningning</t>
+          <t>lapos sa pikas dunggan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>miingon sa kaugalingon sa dihang pag-poking sa usa sa iyang mga winnings sa usa ka dula sa mga kard</t>
+          <t>sa pagsulod sa usa ka dalunggan ug paggawas sa laing dalunggan</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>['pasok']</t>
+          <t>['lapos', 'dunggan']</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Pasok, Luningning, ug paminawa ang mga instructions.</t>
+          <t>Ang mga sugo sa iyang boss kay lapos ra sa pikas dunggan.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>"Pasok, Luningning, kay naghulat na ang imong amahan sa kusina."</t>
+          <t>Nag-iyos siya nga dunay makita nga alahas nga naglapos sa pikas dunggan.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>sabong</t>
+          <t>kakha tuka</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>usa ka kompetisyon</t>
+          <t>kamot-sa-lubong</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>['sabong']</t>
+          <t>['kakha', 'tuka']</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Ang sabong sa mga manok kay paborito nga pastime sa mga kalalakin-an.</t>
+          <t>Si Juan pirmi lang kakha tuka, walay nahabilin nga budget.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Nagbutang kog tubig ug sabong sa palanggana para sa laba.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>bisan ang kabaw nga naay upat ka tiil masipyat</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>kitang tanan magkamali</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>['naay', 'masipyat']</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Si Pedro nasipyat sa exam, bisan ang kabaw nga naay upat ka tiil masipyat.</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Sa among bukid, nakita nako nga bisan ang kabaw nga naay upat ka tiil masipyat ug mulakaw diha sa dili patag nga dalan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>tuslok baki</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>usa ka dula</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>['tuslok']</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Ang mga bata nagpraktis sa tuslok baki aron mahimong champion sa dula.</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>"Nakit-an nako si Lito nga nagkuha og sungkod aron magtuslok baki sa daplin sa sapa."</t>
+          <t>Ang maya nagkakha tuka sa nataran.</t>
         </is>
       </c>
     </row>
